--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3079,6 +3079,72 @@
       <c r="F122" s="5" t="inlineStr">
         <is>
           <t>Needs its own translation strategy — see Notes tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>login.tsx</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>starter_vocab_list_name</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>{language} Starter Vocab</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Auto-generated list name for the signup-seeded starter vocab list; template</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>login.tsx</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>i_already_know_reused</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>I already know</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Reuses language-picker.tsx wording — shown in signup mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>login.tsx</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>i_am_learning_reused</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>I'm learning</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Reuses language-picker.tsx wording — shown in signup mode</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3085,68 +3085,180 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>login.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>starter_vocab_list_name</t>
+          <t>sample_lists_title</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>{language} Starter Vocab</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Auto-generated list name for the signup-seeded starter vocab list; template</t>
-        </is>
-      </c>
+          <t>Sample Lists</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>login.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>i_already_know_reused</t>
+          <t>sample_lists_hint</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>I already know</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>Reuses language-picker.tsx wording — shown in signup mode</t>
-        </is>
-      </c>
+          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>login.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>i_am_learning_reused</t>
+          <t>sample_list_name_template</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>I'm learning</t>
+          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Reuses language-picker.tsx wording — shown in signup mode</t>
-        </is>
-      </c>
+          <t>Template — used as both display label and saved list name</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_type_vocab</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Vocab</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Reused label under each sample list row</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_type_verbs</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Verbs</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Reused label under each sample list row</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_add</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_adding</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Adding…</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_added</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>error_adding_sample</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Something went wrong adding that sample list.</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3259,6 +3259,208 @@
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>get_started</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Get Started</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>slide1_headline</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Build Your List</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>slide1_body</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>slide2_headline</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Practice With Adaptive Quizzes</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>slide2_body</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>slide3_headline</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Watch Your Progress</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>slide3_body</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>See your scores improve over time, list by list.</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>about_langreps_link</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>About LangReps</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Links to /onboarding to replay it manually</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3459,6 +3459,104 @@
       <c r="F142" s="5" t="inlineStr">
         <is>
           <t>Links to /onboarding to replay it manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>sort_by_label</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Sort by</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>sort_by_date</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>sort_by_name</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>last_uploaded_template</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Last uploaded: {date}</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_name_template_v2</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Superseded template — replaces the old arrow-notation naming</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3557,6 +3557,50 @@
       <c r="F147" s="5" t="inlineStr">
         <is>
           <t>Superseded template — replaces the old arrow-notation naming</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_card_title</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Vocab {count} / Verb {count}</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Sample-list catalog card title, replaces the old full name display</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>sample_list_card_flags</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>{flag} -&gt; {flag}</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -3493,7 +3493,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Last Uploaded</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Share a Picture</t>
+          <t>Upload a Photo</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Share a Picture</t>
+          <t>Upload a Photo</t>
         </is>
       </c>
       <c r="D43" s="2" t="n"/>
@@ -3603,6 +3603,24 @@
           <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>index.tsx</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>signup_incentive_hint</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Sign up to save your lists and track your progress over time</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="UI Strings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,41 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,20 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
@@ -499,3218 +461,3587 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>app_name</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>LangReps</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Proper name — may stay untranslated</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>home_subtitle</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Build a vocab list, then let AI generate an adaptive quiz for it.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="5" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>settings_link</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>log_out</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Log Out</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>delete_account</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Delete Account</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Also used as alert title</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>log_in_sign_up</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Log In / Sign Up</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>signed_in_as</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Signed in as {email}</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Template — {email} not translated</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>add_words_manually</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Add Words Manually</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>paste_vocab_list</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Paste Vocab List</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>upload_a_file</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Upload a File</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>share_a_picture</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Upload a Photo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>my_lists</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>my_quizzes</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>My Quizzes</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>delete_account_confirm</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>This permanently deletes your account and all your saved lists. This can't be undone.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Alert body</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Cancel</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Alert button — reused across screens</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>delete</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Delete</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Alert button — reused across screens</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>error_generic</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Something went wrong.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Fallback error — reused across screens</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>log_in</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Log In</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Screen title + button + toggle target</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>sign_up</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Sign Up</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Screen title + button + toggle target</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>email_placeholder</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>password_placeholder</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>please_wait</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Please wait…</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>switch_to_signup</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Don't have an account? Sign up</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>switch_to_login</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Already have an account? Log in</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>confirm_email_message</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Check your email to confirm, then log in below.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>account_created_message</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Account created — log in below.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>add_words_title</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Add Words</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>source_word_placeholder</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Source word</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>target_word_placeholder</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Target word</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>add_to_list</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Add to list</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Reused on paste-text.tsx</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>paste_vocab_list_title</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Paste Vocab List</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>paste_instructions</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>One pair per line — a tab, "-&gt;", ":", or similar between each word and its translation. e.g. hello -&gt; hola</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Contains a literal example — keep example untranslated or localize it</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>paste_placeholder</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Paste your vocab list here</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>parsing_ellipsis</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Parsing…</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Reused on upload-file.tsx</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>couldnt_parse_lines</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Couldn't parse {n} line(s): {list}</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Template with pluralization (1 line vs N lines)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>error_parsing_text</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Something went wrong parsing that text.</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>upload_a_file_title</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Upload a File</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="5" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>upload_file_instructions</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>A plain text or CSV file, one pair per line — a tab, "-&gt;", ":", or similar between each word and its translation.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>choose_file</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Choose File</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>last_file</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Last file: {name}</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Template — filename not translated</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>error_parsing_file</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Something went wrong parsing that file.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>share_a_picture_title</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Upload a Photo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="5" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>share_picture_instructions</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>A photo or screenshot of word pairs (e.g. "house -&gt; casa") — AI will read the pairs out of it.</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Contains a literal example</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>take_photo</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Take Photo</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="5" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>choose_from_library</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Choose from Library</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>reading_ellipsis</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Reading…</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>error_camera_permission</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Camera access is needed to take a photo.</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>error_library_permission</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Photo library access is needed to choose an image.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>error_reading_image</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Something went wrong reading that image.</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>generate_quiz_title</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Generate Quiz</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Also reused as button label</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>unsaved_list</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Unsaved list</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Fallback when no list name</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>min_words_warning</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>You need at least 3 words to generate a quiz.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="5" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>words_in_list</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>{n} words in this list.</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Template with pluralization</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>how_many_questions</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>How many questions?</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="5" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>tense_label</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Tense</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="5" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>mixed_tense</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Dropdown option meaning vary tense freely</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>flip_toggle_label</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Flip: translate {target} → {source}</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Template — language names not translated here</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>generating_quiz</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Generating your quiz…</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="5" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>target_my_mistakes</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Target My Mistakes</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="5" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>generate_similar_quiz</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Generate Similar Quiz</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="5" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>error_generating_quiz</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Something went wrong generating your quiz.</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="5" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>my_lists_title</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="5" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>no_saved_lists</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>No saved lists yet.</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="5" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>progress_link</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Row action label</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>delete_list_alert_title</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Delete List</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="5" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>delete_list_confirm</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Delete "{name}"? This can't be undone.</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>error_loading_lists</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Something went wrong loading your lists.</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="5" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>error_loading_list</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Something went wrong loading that list.</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="5" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>error_deleting_list</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Something went wrong deleting that list.</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="5" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>my_quizzes_title</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>My Quizzes</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="5" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>no_quizzes_in_progress</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>No quizzes in progress.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="5" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>quiz_in_progress_fallback</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Quiz in progress</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="5" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>question_n_of_total</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Question {n} of {total}</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Template — also used in quiz.tsx</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>delete_quiz_alert_title</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Delete Quiz</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="5" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>delete_quiz_confirm</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Delete this quiz for "{name}"? This can't be undone.</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>error_loading_quizzes</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Something went wrong loading your quizzes.</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="5" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>error_deleting_quiz</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Something went wrong deleting that quiz.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="5" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>progress_title</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Title fallback + subtitle label</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>no_completed_quizzes</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>No completed quizzes for this list yet.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="5" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>score_fraction_pct</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>{correct}/{total} ({pct}%)</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Number formatting conventions vary by locale</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>error_loading_history</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Something went wrong loading quiz history.</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="5" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>settings_title</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="5" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>default_level_hint</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Default level for new quizzes — you can still change it for any single quiz when generating it.</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="5" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>auto_delete_toggle</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Auto-delete completed quizzes after 30 days</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="5" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>adaptive_quizzes_toggle</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="5" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>your_answer_placeholder</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="5" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>submit</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Submit</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="5" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>skip_question</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Skip this question</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="5" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>hide_word_list</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Hide word list</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="5" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>stuck_see_word_list</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Stuck? See the word list</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="5" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>your_answer_was</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Your answer: {answer}</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>correct_feedback</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>That's correct!</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
-      <c r="F93" s="5" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>incorrect_feedback</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Sorry, that's incorrect. The answer was: {answer}</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>finish_quiz</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Finish Quiz</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="5" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>next_question</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Next Question</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="5" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>quiz_complete_title</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Quiz Complete!</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="5" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>score_correct</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>{n} / {total} correct</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>back_to_home</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Back to Home</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="n"/>
-      <c r="F99" s="5" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>undo_last</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Undo last</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="5" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>clear_list</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Clear list</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="5" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>no_words_added</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>No words added yet.</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="5" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>list_name_update_placeholder</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>List name (saving updates it)</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="5" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>list_name_placeholder</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>List name</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="5" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>saving_ellipsis</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Saving…</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="n"/>
-      <c r="F105" s="5" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>save_list</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Save List</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="5" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>saved_message</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Saved!</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="5" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>error_saving</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Something went wrong saving.</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="5" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>add_more_words_to_quiz</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Add {n} more word(s) to generate a quiz</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Template with pluralization</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>generate_quiz_button</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Generate Quiz</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="5" t="inlineStr">
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Reused label</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>my_lists_link</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Reused label</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>level_label</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
         <is>
           <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>language-picker.tsx</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>i_already_know</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>I already know</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
-      <c r="F113" s="5" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>language-picker.tsx</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>i_am_learning</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>I'm learning</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="5" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>language-picker.tsx</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>language_names</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>English / Spanish / French</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Design decision: show in UI language or always native form (Español, Français)?</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>parsing-warning.tsx</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>parsing_warning_text</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Contains an inline link to Share a Picture</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>trend_improving_a_lot</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>5 message variants — 'Great progress! Your scores are climbing fast...' etc.</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
         <is>
           <t>See file directly, too long to list individually</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>trend_improving</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>5 message variants — 'You're improving steadily on this list.' etc.</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>trend_steady</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>5 message variants — 'Your scores are holding steady...' etc.</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>trend_declining</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>5 message variants — 'Your scores dipped a bit recently...' etc.</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>trend_declining_a_lot</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>5 message variants — 'Your scores dropped noticeably...' etc.</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>backend (api errors)</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>backend_error_text</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Needs its own translation strategy — see Notes tab</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>sample_lists_title</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Sample Lists</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>sample_lists_hint</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>sample_list_name_template</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Template — used as both display label and saved list name</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>sample_list_type_vocab</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Vocab</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Reused label under each sample list row</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>sample_list_type_verbs</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Verbs</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Reused label under each sample list row</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>sample_list_add</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>sample_list_adding</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Adding…</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>sample_list_added</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>error_adding_sample</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>back</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Next</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>get_started</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Get Started</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>slide1_headline</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Build Your List</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>slide1_body</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>slide2_headline</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
-      <c r="F138" s="5" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>slide2_body</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>slide3_headline</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Watch Your Progress</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>slide3_body</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>about_langreps_link</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>About LangReps</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Links to /onboarding to replay it manually</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>sort_by_label</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Sort by</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>sort_by_date</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Last Uploaded</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>sort_by_name</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>last_uploaded_template</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Last uploaded: {date}</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr">
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>sample_list_name_template_v2</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Superseded template — replaces the old arrow-notation naming</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>sample_list_card_title</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr">
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Sample-list catalog card title, replaces the old full name display</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>sample_list_card_flags</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>signup_incentive_hint</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Inventory of every hardcoded, user-facing string in the LangReps app (frontend UI chrome only — not vocab/quiz content, which is already language-flexible).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Key column</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>A proposed snake_case translation key for src/lib/translations/{en,es,fr}.ts (see project_langreps_localization memory note for the planned i18n architecture).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Templates</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Strings with {placeholders} are template strings — translate the surrounding text, keep the placeholder names as-is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Spanish / French columns</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Left blank for translation — fill in when the i18n pass begins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Backend error text</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Some error messages shown via e.message originate from the FastAPI backend (HTTPException details), not the frontend. These need either their own backend-side translation, or the frontend should map known error patterns to translated strings instead of showing raw backend text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Not included</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Generated content (quiz questions, vocab list names, user emails) — these are inherently already in whatever language the user is studying or typed, not part of the app's UI chrome.</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>default_level_title</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Default Level</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>New section title for Settings redesign (bold title + description layout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>auto_delete_title</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Auto-Delete Old Quizzes</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>New section title</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>auto_delete_desc</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Completed quizzes are removed after 30 days</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Description moved under the bold title</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>adaptive_quizzes_title</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Adaptive Quizzes</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>New section title</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>adaptive_quizzes_desc</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Get feedback on patterns you struggle with, and an option to target them</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Description moved under the bold title</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>require_accents_title</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Require Accents</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>New toggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>require_accents_desc</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Off accepts "cafe" for "café"</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>your_lists_section_title</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Your Lists</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>New section title alongside bulk-select controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>bulk_select_toggle</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Select / Cancel</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Toggles bulk-select mode (shared pattern, My Lists and My Quizzes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>bulk_select_all</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Select All / Deselect All</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Shared pattern</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>bulk_delete_selected_template</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Delete Selected ({count})</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Shared pattern</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>bulk_deleting</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Deleting…</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Shared pattern</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>bulk_delete_lists_alert_title</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Delete Lists</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>bulk_delete_lists_alert_message_template</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Delete {count} list(s)? This can't be undone.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>quizzes_in_progress_count_template</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>{count} in progress</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>bulk_delete_quizzes_alert_title</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Delete Quizzes</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>bulk_delete_quizzes_alert_message_template</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Delete {count} quiz(zes)? This can't be undone.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -3845,14 +3845,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Select / Cancel</t>
+          <t>Select / Done</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Toggles bulk-select mode (shared pattern, My Lists and My Quizzes)</t>
+          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Delete Selected ({count})</t>
+          <t>Delete ({count})</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4043,6 +4043,54 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>sort_by_last_updated</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>last_updated_template</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Last updated: {date}</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4091,6 +4091,54 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>quiz_type_badge_vocab</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Vocab</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>quiz_type_badge_verb</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Small badge next to the quiz row title</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4139,6 +4139,102 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>quiz-complete.tsx</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>canned_feedback_perfect</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Perfect score! This list is looking solid.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Shown when there's not yet enough history for an AI pattern insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>quiz-complete.tsx</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>canned_feedback_great</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Great work — you know this list well.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>80-99% correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>quiz-complete.tsx</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>canned_feedback_keep_going</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Keep at it — repetition is what makes this stick.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>50-79% correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>quiz-complete.tsx</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>canned_feedback_tough</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>This one's tough. A few more passes and it'll click.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Below 50% correct</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -4147,19 +4147,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>canned_feedback_perfect</t>
+          <t>canned_feedback_mastery</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Perfect score! This list is looking solid.</t>
+          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Shown when there's not yet enough history for an AI pattern insight</t>
+          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
         </is>
       </c>
     </row>
@@ -4171,19 +4171,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>canned_feedback_great</t>
+          <t>canned_feedback_solid</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Great work — you know this list well.</t>
+          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>80-99% correct</t>
+          <t>70-89% correct</t>
         </is>
       </c>
     </row>
@@ -4195,19 +4195,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>canned_feedback_keep_going</t>
+          <t>canned_feedback_building</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Keep at it — repetition is what makes this stick.</t>
+          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>50-79% correct</t>
+          <t>40-69% correct</t>
         </is>
       </c>
     </row>
@@ -4219,19 +4219,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>canned_feedback_tough</t>
+          <t>canned_feedback_struggling</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>This one's tough. A few more passes and it'll click.</t>
+          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Below 50% correct</t>
+          <t>Below 40% correct</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4235,6 +4235,150 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>cefr_info_alert_title</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CEFR Levels</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Alert title triggered by new info icon next to the Level label</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>cefr_a1_explanation</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Breakthrough — basic words and phrases for everyday needs.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>cefr_a2_explanation</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>cefr_b1_explanation</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>cefr_b2_explanation</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>cefr_c1_explanation</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>cefr-level-picker.tsx</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>cefr_c2_explanation</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -3773,14 +3773,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Require Accents</t>
+          <t>Require Diacritics</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>New toggle</t>
+          <t>New toggle — renamed from "Require Accents"</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4379,6 +4379,99 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>welcome.tsx</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>welcome_title</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>LangReps</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>New branded first screen shown before onboarding slides — proper name</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> may stay untranslated</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>welcome.tsx</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>welcome_tagline</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Language reps that stick.</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>welcome.tsx</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>get_started</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Get Started</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>welcome.tsx</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>copyright</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>© 2026 MarApps Development</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Pinned bottom-right corner</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4382,12 +4382,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>welcome.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>welcome_title</t>
+          <t>splash_title</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4399,24 +4399,19 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>New branded first screen shown before onboarding slides — proper name</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> may stay untranslated</t>
+          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>welcome.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>welcome_tagline</t>
+          <t>splash_tagline</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4431,42 +4426,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>welcome.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>get_started</t>
+          <t>splash_copyright</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Get Started</t>
+          <t>© 2026 MarApps Development</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>welcome.tsx</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>copyright</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>© 2026 MarApps Development</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Pinned bottom-right corner</t>
         </is>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4447,6 +4447,158 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>quiz-complete.tsx</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>see_full_results</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>See Full Results</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>quiz-results.tsx</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>full_results_title</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Full Results</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>quiz-results.tsx</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>no_recorded_answers</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>No recorded answers for this quiz.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>quiz-results.tsx</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>your_answer_label</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Your answer:</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>quiz-results.tsx</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>correct_answer_label</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Correct answer:</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Shown only for incorrect rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>quiz-results.tsx</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>blank_answer_fallback</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Shown when a skipped/empty answer was recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>quiz-results.tsx</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>error_loading_results</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Something went wrong loading results.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4599,6 +4599,70 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>list_type_info_alert_title</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>List Types</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>New info icon next to the List type label</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>list_type_info_vocab</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>list_type_info_verb</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4663,6 +4663,83 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>save_label_new</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Name this list to save it</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>New persistent label above the name field, was placeholder-only before</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>save_label_update</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>List name (saving updates it)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Moved from placeholder to a persistent label above the field</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>save_input_placeholder</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>e.g. Spanish Verbs</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>New example placeholder</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> replaces the old "List name" placeholder now that a persistent label exists</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>save_label_new</t>
+          <t>save_input_placeholder_new</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4683,7 +4683,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>New persistent label above the name field, was placeholder-only before</t>
+          <t>Placeholder text (reverted from a separate label above the field — felt too busy)</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>save_label_update</t>
+          <t>save_input_placeholder_update</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4707,36 +4707,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Moved from placeholder to a persistent label above the field</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>pairs-review.tsx</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>save_input_placeholder</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>e.g. Spanish Verbs</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>New example placeholder</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> replaces the old "List name" placeholder now that a persistent label exists</t>
+          <t>Placeholder shown once the list is already saved</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Name this list to save it</t>
+          <t>Name this list</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Placeholder text (reverted from a separate label above the field — felt too busy)</t>
+          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
         </is>
       </c>
     </row>
@@ -4700,14 +4700,34 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>List name (saving updates it)</t>
+          <t>List name (updates it)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Placeholder shown once the list is already saved</t>
+          <t>Placeholder shown once the list is already saved — shortened to fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>constants/styles.ts</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>placeholder_color_note</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Not a UI string — new colors.placeholder token (#8C7F63) applied via placeholderTextColor to every TextInput app-wide; RN's default placeholder gray had poor contrast on the parchment background and was nearly invisible</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4731,6 +4731,54 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>edit_list_link</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>remove_word_icon</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4779,6 +4779,119 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>translate-skipped-lines.tsx</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>translate_prompt_template</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>{n} line(s) looked like single word(s)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> not pairs — translate into:</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>translate-skipped-lines.tsx</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>translate_button</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Translate</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>translate-skipped-lines.tsx</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>translating_ellipsis</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Translating…</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>translate-skipped-lines.tsx</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>error_translating</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Something went wrong translating those words.</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>slide1_body_updated</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4892,6 +4892,26 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>saved_list_heading</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Not new text — shows the list's own saved name prominently at the top of PairsReview once saved (Edit flow especially), styled like Generate Quiz's list-name heading</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4912,6 +4912,122 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>rename_link</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>New — separates renaming an already-saved list from saving its pairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>rename_save_button</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Inline rename confirm button</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>rename_cancel_button</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Inline rename cancel button</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>error_renaming</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Something went wrong renaming.</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>save_changes_button</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Save Changes</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5028,6 +5028,54 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>list_type_locked_label</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>List type (locked)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Appended to the label once a list is saved — type can't change after first save</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>list_type_locked_explanation</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Appended to the existing List Types info alert once locked</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G213"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5076,6 +5076,103 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>past_quizzes_section_title</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Past Quizzes</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>New section showing completed quiz history</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> fetched from GET /quiz-sessions/completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>no_completed_quizzes</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>No completed quizzes yet.</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>past_quiz_score_template</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>{correct}/{total} correct ({pct}%)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>deleted_list_fallback</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Deleted list</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Shown when a past quiz's list no longer exists</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G217"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5173,6 +5173,74 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>back-button.tsx</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>discard_unsaved_alert_title</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Discard unsaved words?</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>back-button.tsx</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>discard_unsaved_alert_message</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>back-button.tsx</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>leave_without_saving</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Leave Without Saving</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Destructive confirm action</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -423,8 +423,8 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -500,8 +500,16 @@
           <t>Build a vocab list, then let AI generate an adaptive quiz for it.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Crea una lista de vocabulario y deja que la IA genere un cuestionario adaptativo para ti.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Crée une liste de vocabulaire, puis laisse l'IA générer un quiz adaptatif pour toi.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -520,8 +528,16 @@
           <t>Settings</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Paramètres</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -540,8 +556,16 @@
           <t>Log Out</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cerrar sesión</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Se déconnecter</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -560,8 +584,16 @@
           <t>Delete Account</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Eliminar cuenta</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supprimer le compte</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Also used as alert title</t>
@@ -584,8 +616,16 @@
           <t>Log In / Sign Up</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Iniciar sesión / Registrarse</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Se connecter / S'inscrire</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -604,8 +644,16 @@
           <t>Signed in as {email}</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sesión iniciada como {email}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Connecté en tant que {email}</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Template — {email} not translated</t>
@@ -628,8 +676,16 @@
           <t>Add Words Manually</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Añadir palabras manualmente</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ajouter des mots manuellement</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -648,8 +704,16 @@
           <t>Paste Vocab List</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pegar lista de vocabulario</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Coller une liste de vocabulaire</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -668,8 +732,16 @@
           <t>Upload a File</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Subir un archivo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Importer un fichier</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -688,8 +760,16 @@
           <t>Upload a Photo</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Subir una foto</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Importer une photo</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -708,8 +788,16 @@
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mis listas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mes listes</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -728,8 +816,16 @@
           <t>My Quizzes</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mis cuestionarios</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mes quiz</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -748,8 +844,16 @@
           <t>This permanently deletes your account and all your saved lists. This can't be undone.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Esto elimina permanentemente tu cuenta y todas tus listas guardadas. Esta acción no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cela supprime définitivement ton compte et toutes tes listes enregistrées. Cette action est irréversible.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Alert body</t>
@@ -772,8 +876,16 @@
           <t>Cancel</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cancelar</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Annuler</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Alert button — reused across screens</t>
@@ -796,8 +908,16 @@
           <t>Delete</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Eliminar</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Supprimer</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Alert button — reused across screens</t>
@@ -820,8 +940,16 @@
           <t>Something went wrong.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Algo salió mal.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite.</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Fallback error — reused across screens</t>
@@ -844,8 +972,16 @@
           <t>Log In</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Se connecter</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Screen title + button + toggle target</t>
@@ -868,8 +1004,16 @@
           <t>Sign Up</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Registrarse</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S'inscrire</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Screen title + button + toggle target</t>
@@ -892,8 +1036,16 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Correo electrónico</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -912,8 +1064,16 @@
           <t>Password</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Contraseña</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mot de passe</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -932,8 +1092,16 @@
           <t>Please wait…</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Espera, por favor…</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Veuillez patienter…</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -952,8 +1120,16 @@
           <t>Don't have an account? Sign up</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>¿No tienes una cuenta? Regístrate</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pas de compte ? Inscris-toi</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -972,8 +1148,16 @@
           <t>Already have an account? Log in</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>¿Ya tienes una cuenta? Inicia sesión</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tu as déjà un compte ? Connecte-toi</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -992,8 +1176,16 @@
           <t>Check your email to confirm, then log in below.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Revisa tu correo para confirmar y luego inicia sesión abajo.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vérifie tes e-mails pour confirmer, puis connecte-toi ci-dessous.</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1012,8 +1204,16 @@
           <t>Account created — log in below.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cuenta creada — inicia sesión abajo.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Compte créé — connecte-toi ci-dessous.</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1032,8 +1232,16 @@
           <t>Add Words</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Añadir palabras</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ajouter des mots</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1052,8 +1260,16 @@
           <t>Source word</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Palabra de origen</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mot source</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1072,8 +1288,16 @@
           <t>Target word</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Palabra de destino</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mot cible</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1092,8 +1316,16 @@
           <t>Add to list</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Añadir a la lista</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ajouter à la liste</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Reused on paste-text.tsx</t>
@@ -1116,8 +1348,16 @@
           <t>Paste Vocab List</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pegar lista de vocabulario</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Coller une liste de vocabulaire</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1136,8 +1376,16 @@
           <t>One pair per line — a tab, "-&gt;", ":", or similar between each word and its translation. e.g. hello -&gt; hola</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción. p. ej. hello -&gt; hola</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction. ex. hello -&gt; hola</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Contains a literal example — keep example untranslated or localize it</t>
@@ -1160,8 +1408,16 @@
           <t>Paste your vocab list here</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pega aquí tu lista de vocabulario</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Colle ici ta liste de vocabulaire</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1180,8 +1436,16 @@
           <t>Parsing…</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Analizando…</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Analyse en cours…</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Reused on upload-file.tsx</t>
@@ -1204,8 +1468,16 @@
           <t>Couldn't parse {n} line(s): {list}</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No se pudieron leer {n} línea(s): {list}</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Impossible d'analyser {n} ligne(s) : {list}</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Template with pluralization (1 line vs N lines)</t>
@@ -1228,8 +1500,16 @@
           <t>Something went wrong parsing that text.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Algo salió mal al analizar ese texto.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de l'analyse de ce texte.</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1248,8 +1528,16 @@
           <t>Upload a File</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Subir un archivo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Importer un fichier</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1268,8 +1556,16 @@
           <t>A plain text or CSV file, one pair per line — a tab, "-&gt;", ":", or similar between each word and its translation.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Un archivo de texto plano o CSV, un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Un fichier texte brut ou CSV, une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction.</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1288,8 +1584,16 @@
           <t>Choose File</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Elegir archivo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Choisir un fichier</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1308,8 +1612,16 @@
           <t>Last file: {name}</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Último archivo: {name}</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dernier fichier : {name}</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>Template — filename not translated</t>
@@ -1332,8 +1644,16 @@
           <t>Something went wrong parsing that file.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Algo salió mal al analizar ese archivo.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de l'analyse de ce fichier.</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1352,8 +1672,16 @@
           <t>Upload a Photo</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Subir una foto</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Importer une photo</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1372,8 +1700,16 @@
           <t>A photo or screenshot of word pairs (e.g. "house -&gt; casa") — AI will read the pairs out of it.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Una foto o captura de pantalla de pares de palabras (p. ej. "house -&gt; casa") — la IA leerá los pares.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Une photo ou capture d'écran de paires de mots (ex. "house -&gt; casa") — l'IA en extraira les paires.</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>Contains a literal example</t>
@@ -1396,8 +1732,16 @@
           <t>Take Photo</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tomar foto</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prendre une photo</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1416,8 +1760,16 @@
           <t>Choose from Library</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Elegir de la galería</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Choisir depuis la galerie</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1436,8 +1788,16 @@
           <t>Reading…</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Leyendo…</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Lecture en cours…</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1456,8 +1816,16 @@
           <t>Camera access is needed to take a photo.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Se necesita acceso a la cámara para tomar una foto.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>L'accès à l'appareil photo est nécessaire pour prendre une photo.</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1476,8 +1844,16 @@
           <t>Photo library access is needed to choose an image.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Se necesita acceso a la galería de fotos para elegir una imagen.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>L'accès à la photothèque est nécessaire pour choisir une image.</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1496,8 +1872,16 @@
           <t>Something went wrong reading that image.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Algo salió mal al leer esa imagen.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la lecture de cette image.</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1516,8 +1900,16 @@
           <t>Generate Quiz</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Generar cuestionario</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Générer un quiz</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Also reused as button label</t>
@@ -1540,8 +1932,16 @@
           <t>Unsaved list</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lista sin guardar</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Liste non enregistrée</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>Fallback when no list name</t>
@@ -1564,8 +1964,16 @@
           <t>You need at least 3 words to generate a quiz.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Necesitas al menos 3 palabras para generar un cuestionario.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Il te faut au moins 3 mots pour générer un quiz.</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1584,8 +1992,16 @@
           <t>{n} words in this list.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{n} palabras en esta lista.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>{n} mots dans cette liste.</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Template with pluralization</t>
@@ -1608,8 +2024,16 @@
           <t>How many questions?</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>¿Cuántas preguntas?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Combien de questions ?</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1628,8 +2052,16 @@
           <t>Tense</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Tiempo verbal</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Temps</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -1648,8 +2080,16 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Mixte</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>Dropdown option meaning vary tense freely</t>
@@ -1672,8 +2112,16 @@
           <t>Flip: translate {target} → {source}</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Invertir: traducir de {target} a {source}</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Inverser : traduire de {target} vers {source}</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>Template — language names not translated here</t>
@@ -1696,8 +2144,16 @@
           <t>Generating your quiz…</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Generando tu cuestionario…</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Génération de ton quiz…</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -1716,8 +2172,16 @@
           <t>Target My Mistakes</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Enfocarme en mis errores</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cibler mes erreurs</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -1736,8 +2200,16 @@
           <t>Generate Similar Quiz</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Generar cuestionario similar</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Générer un quiz similaire</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -1756,8 +2228,16 @@
           <t>Something went wrong generating your quiz.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Algo salió mal al generar tu cuestionario.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la génération de ton quiz.</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -1776,8 +2256,16 @@
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mis listas</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Mes listes</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -1796,8 +2284,16 @@
           <t>No saved lists yet.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Aún no tienes listas guardadas.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aucune liste enregistrée pour l'instant.</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -1816,8 +2312,16 @@
           <t>Progress</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Progrès</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>Row action label</t>
@@ -1840,8 +2344,16 @@
           <t>Delete List</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Eliminar lista</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Supprimer la liste</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -1860,8 +2372,16 @@
           <t>Delete "{name}"? This can't be undone.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>¿Eliminar "{name}"? Esta acción no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Supprimer « {name} » ? Cette action est irréversible.</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Template</t>
@@ -1884,8 +2404,16 @@
           <t>Something went wrong loading your lists.</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cargar tus listas.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du chargement de tes listes.</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -1904,8 +2432,16 @@
           <t>Something went wrong loading that list.</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cargar esa lista.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du chargement de cette liste.</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -1924,8 +2460,16 @@
           <t>Something went wrong deleting that list.</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Algo salió mal al eliminar esa lista.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la suppression de cette liste.</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -1944,8 +2488,16 @@
           <t>My Quizzes</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mis cuestionarios</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Mes quiz</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -1964,8 +2516,16 @@
           <t>No quizzes in progress.</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>No hay cuestionarios en curso.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aucun quiz en cours.</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -1984,8 +2544,16 @@
           <t>Quiz in progress</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Cuestionario en curso</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Quiz en cours</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -2004,8 +2572,16 @@
           <t>Question {n} of {total}</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pregunta {n} de {total}</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Question {n} sur {total}</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>Template — also used in quiz.tsx</t>
@@ -2028,8 +2604,16 @@
           <t>Delete Quiz</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Eliminar cuestionario</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Supprimer le quiz</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -2048,8 +2632,16 @@
           <t>Delete this quiz for "{name}"? This can't be undone.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>¿Eliminar este cuestionario de "{name}"? Esta acción no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Supprimer ce quiz pour « {name} » ? Cette action est irréversible.</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Template</t>
@@ -2072,8 +2664,16 @@
           <t>Something went wrong loading your quizzes.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cargar tus cuestionarios.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du chargement de tes quiz.</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -2092,8 +2692,16 @@
           <t>Something went wrong deleting that quiz.</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Algo salió mal al eliminar ese cuestionario.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la suppression de ce quiz.</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -2112,8 +2720,16 @@
           <t>Progress</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Progrès</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>Title fallback + subtitle label</t>
@@ -2136,8 +2752,16 @@
           <t>No completed quizzes for this list yet.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Aún no hay cuestionarios completados.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aucun quiz terminé pour l'instant.</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -2156,8 +2780,16 @@
           <t>{correct}/{total} ({pct}%)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{correct}/{total} ({pct}%)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>{correct}/{total} ({pct} %)</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Number formatting conventions vary by locale</t>
@@ -2180,8 +2812,16 @@
           <t>Something went wrong loading quiz history.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cargar el historial del cuestionario.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du chargement de l'historique du quiz.</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -2200,8 +2840,16 @@
           <t>Settings</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Paramètres</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2220,8 +2868,16 @@
           <t>Default level for new quizzes — you can still change it for any single quiz when generating it.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Nivel predeterminado para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Niveau par défaut pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -2240,8 +2896,16 @@
           <t>Auto-delete completed quizzes after 30 days</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Eliminar automáticamente los cuestionarios completados después de 30 días</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -2260,8 +2924,16 @@
           <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Cuestionarios adaptativos — comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
@@ -2280,8 +2952,16 @@
           <t>Your answer</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tu respuesta</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ta réponse</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -2300,8 +2980,16 @@
           <t>Submit</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Enviar</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Valider</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -2320,8 +3008,16 @@
           <t>Skip this question</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Saltar esta pregunta</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Passer cette question</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -2340,8 +3036,16 @@
           <t>Hide word list</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ocultar lista de palabras</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Masquer la liste de mots</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -2360,8 +3064,16 @@
           <t>Stuck? See the word list</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>¿Atascado? Consulta la lista de palabras</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Bloqué ? Consulte la liste de mots</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -2380,8 +3092,16 @@
           <t>Your answer: {answer}</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Tu respuesta: {answer}</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ta réponse : {answer}</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>Template</t>
@@ -2404,8 +3124,16 @@
           <t>That's correct!</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>¡Correcto!</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>C'est correct !</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
@@ -2424,8 +3152,16 @@
           <t>Sorry, that's incorrect. The answer was: {answer}</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lo siento, es incorrecto. La respuesta era: {answer}</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Désolé, c'est incorrect. La réponse était : {answer}</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>Template</t>
@@ -2448,8 +3184,16 @@
           <t>Finish Quiz</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Finalizar cuestionario</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Terminer le quiz</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -2468,8 +3212,16 @@
           <t>Next Question</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Siguiente pregunta</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Question suivante</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
@@ -2488,8 +3240,16 @@
           <t>Quiz Complete!</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>¡Cuestionario completado!</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Quiz terminé !</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -2508,8 +3268,16 @@
           <t>{n} / {total} correct</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{n} / {total} correctas</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>{n} / {total} correctes</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>Template</t>
@@ -2532,8 +3300,16 @@
           <t>Back to Home</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Volver al inicio</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Retour à l'accueil</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -2552,8 +3328,16 @@
           <t>Undo last</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Deshacer última</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Annuler le dernier</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
@@ -2572,8 +3356,16 @@
           <t>Clear list</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Vaciar lista</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Vider la liste</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
@@ -2592,8 +3384,16 @@
           <t>No words added yet.</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Aún no has añadido palabras.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aucun mot ajouté pour l'instant.</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
@@ -2612,8 +3412,16 @@
           <t>List name (saving updates it)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Nombre de la lista (al guardar se actualiza)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Nom de la liste (l'enregistrement la met à jour)</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
@@ -2632,8 +3440,16 @@
           <t>List name</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Nombre de la lista</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Nom de la liste</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -2652,8 +3468,16 @@
           <t>Saving…</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Guardando…</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Enregistrement…</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
@@ -2672,8 +3496,16 @@
           <t>Save List</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Guardar lista</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Enregistrer la liste</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
@@ -2692,8 +3524,16 @@
           <t>Saved!</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>¡Guardado!</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Enregistré !</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
@@ -2712,8 +3552,16 @@
           <t>Something went wrong saving.</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Algo salió mal al guardar.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de l'enregistrement.</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
@@ -2732,8 +3580,16 @@
           <t>Add {n} more word(s) to generate a quiz</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Añade {n} palabra(s) más para generar un cuestionario</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Ajoute {n} mot(s) de plus pour générer un quiz</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>Template with pluralization</t>
@@ -2756,8 +3612,16 @@
           <t>Generate Quiz</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Generar cuestionario</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Générer un quiz</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>Reused label</t>
@@ -2780,8 +3644,16 @@
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mis listas</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Mes listes</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>Reused label</t>
@@ -2804,8 +3676,16 @@
           <t>Level</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Niveau</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
@@ -2828,8 +3708,16 @@
           <t>I already know</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Ya sé</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Je connais déjà</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
@@ -2848,8 +3736,16 @@
           <t>I'm learning</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Estoy aprendiendo</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>J'apprends</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
@@ -2892,8 +3788,16 @@
           <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>El análisis puede cometer errores con formatos inusuales. Para mejores resultados, prueba subir una foto en su lugar.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>L'analyse peut faire des erreurs avec une mise en forme inhabituelle. Pour de meilleurs résultats, essaie plutôt d'importer une photo.</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>Contains an inline link to Share a Picture</t>
@@ -3060,8 +3964,16 @@
           <t>Sample Lists</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Listas de ejemplo</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Listes types</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
@@ -3080,8 +3992,16 @@
           <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
@@ -3100,8 +4020,16 @@
           <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>Template — used as both display label and saved list name</t>
@@ -3124,8 +4052,16 @@
           <t>Vocab</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Vocabulario</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Vocabulaire</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>Reused label under each sample list row</t>
@@ -3148,8 +4084,16 @@
           <t>Verbs</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Verbos</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Verbes</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>Reused label under each sample list row</t>
@@ -3172,8 +4116,16 @@
           <t>Add</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Añadir</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ajouter</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
@@ -3192,8 +4144,16 @@
           <t>Adding…</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Añadiendo…</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ajout en cours…</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
@@ -3212,8 +4172,16 @@
           <t>Added</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Añadido</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Ajouté</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
@@ -3236,8 +4204,16 @@
           <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
@@ -3256,8 +4232,16 @@
           <t>Skip</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Omitir</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Passer</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
@@ -3276,8 +4260,16 @@
           <t>Back</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Atrás</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Retour</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
@@ -3296,8 +4288,16 @@
           <t>Next</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Siguiente</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Suivant</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
@@ -3316,8 +4316,16 @@
           <t>Get Started</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Empezar</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Commencer</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
@@ -3336,8 +4344,16 @@
           <t>Build Your List</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Crea tu lista</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Crée ta liste</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
@@ -3356,8 +4372,16 @@
           <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
@@ -3376,8 +4400,16 @@
           <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Practica con cuestionarios adaptativos</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Entraîne-toi avec des quiz adaptatifs</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
@@ -3396,8 +4428,16 @@
           <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
@@ -3416,8 +4456,16 @@
           <t>Watch Your Progress</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Observa tu progreso</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Suis ta progression</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
@@ -3436,8 +4484,16 @@
           <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
@@ -3456,8 +4512,16 @@
           <t>About LangReps</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Acerca de LangReps</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>À propos de LangReps</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Links to /onboarding to replay it manually</t>
@@ -3480,8 +4544,16 @@
           <t>Sort by</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ordenar por</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Trier par</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
@@ -3500,8 +4572,16 @@
           <t>Last Uploaded</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Última subida</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Dernier import</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
@@ -3520,8 +4600,16 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
@@ -3540,8 +4628,16 @@
           <t>Last uploaded: {date}</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Última subida: {date}</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Dernier import : {date}</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
@@ -3564,8 +4660,16 @@
           <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>Superseded template — replaces the old arrow-notation naming</t>
@@ -3588,8 +4692,16 @@
           <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Vocabulario {count} / Verbo {count}</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Vocabulaire {count} / Verbe {count}</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>Sample-list catalog card title, replaces the old full name display</t>
@@ -3612,8 +4724,16 @@
           <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{flag} -&gt; {flag}</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>{flag} -&gt; {flag}</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
@@ -3636,8 +4756,16 @@
           <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
@@ -3656,8 +4784,16 @@
           <t>Default Level</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Nivel predeterminado</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Niveau par défaut</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>New section title for Settings redesign (bold title + description layout)</t>
@@ -3680,8 +4816,16 @@
           <t>Auto-Delete Old Quizzes</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Eliminar automáticamente cuestionarios antiguos</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Suppression automatique des anciens quiz</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>New section title</t>
@@ -3704,8 +4848,16 @@
           <t>Completed quizzes are removed after 30 days</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Los cuestionarios completados se eliminan después de 30 días</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Les quiz terminés sont supprimés après 30 jours</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>Description moved under the bold title</t>
@@ -3728,8 +4880,16 @@
           <t>Adaptive Quizzes</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cuestionarios adaptativos</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Quiz adaptatifs</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>New section title</t>
@@ -3752,8 +4912,16 @@
           <t>Get feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>Description moved under the bold title</t>
@@ -3776,8 +4944,16 @@
           <t>Require Diacritics</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Exigir diacríticos</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Exiger les diacritiques</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>New toggle — renamed from "Require Accents"</t>
@@ -3800,8 +4976,16 @@
           <t>Off accepts "cafe" for "café"</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Desactivado acepta "cafe" en lugar de "café"</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Désactivé accepte "cafe" pour "café"</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
@@ -3824,8 +5008,16 @@
           <t>Your Lists</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tus listas</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Tes listes</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>New section title alongside bulk-select controls</t>
@@ -3848,8 +5040,16 @@
           <t>Select / Done</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Seleccionar / Listo</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sélectionner / Terminé</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
@@ -3872,8 +5072,16 @@
           <t>Select All / Deselect All</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Seleccionar todo / Deseleccionar todo</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Tout sélectionner / Tout désélectionner</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>Shared pattern</t>
@@ -3901,8 +5109,16 @@
           <t>Delete ({count})</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Eliminar ({count})</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Supprimer ({count})</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>Shared pattern</t>
@@ -3930,8 +5146,16 @@
           <t>Deleting…</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Eliminando…</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Suppression…</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>Shared pattern</t>
@@ -3959,8 +5183,16 @@
           <t>Delete Lists</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Eliminar listas</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Supprimer les listes</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -3979,8 +5211,16 @@
           <t>Delete {count} list(s)? This can't be undone.</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
@@ -3999,8 +5239,16 @@
           <t>{count} in progress</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{count} en curso</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>{count} en cours</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
@@ -4019,8 +5267,16 @@
           <t>Delete Quizzes</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Eliminar cuestionarios</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Supprimer les quiz</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
@@ -4039,8 +5295,16 @@
           <t>Delete {count} quiz(zes)? This can't be undone.</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -4059,8 +5323,16 @@
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Dernière mise à jour</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
@@ -4083,8 +5355,16 @@
           <t>Last updated: {date}</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Última actualización: {date}</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Dernière mise à jour : {date}</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
@@ -4107,8 +5387,16 @@
           <t>Vocab</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Vocabulario</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Vocabulaire</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
@@ -4131,8 +5419,16 @@
           <t>Verb</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Verbo</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Verbe</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
           <t>Small badge next to the quiz row title</t>
@@ -4155,8 +5451,16 @@
           <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
           <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
@@ -4179,8 +5483,16 @@
           <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
           <t>70-89% correct</t>
@@ -4203,8 +5515,16 @@
           <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>40-69% correct</t>
@@ -4227,8 +5547,16 @@
           <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>Below 40% correct</t>
@@ -4251,8 +5579,16 @@
           <t>CEFR Levels</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Niveles del MCER</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Niveaux du CECR</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>Alert title triggered by new info icon next to the Level label</t>
@@ -4275,8 +5611,16 @@
           <t>Breakthrough — basic words and phrases for everyday needs.</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -4295,8 +5639,16 @@
           <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -4315,8 +5667,16 @@
           <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
@@ -4335,8 +5695,16 @@
           <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -4355,8 +5723,16 @@
           <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -4375,8 +5751,16 @@
           <t>Mastery — near-native fluency with precise, nuanced expression.</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -4419,8 +5803,16 @@
           <t>Language reps that stick.</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Repeticiones de idiomas que se quedan.</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Des répétitions de langue qui restent.</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -4463,8 +5855,16 @@
           <t>See Full Results</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Ver resultados completos</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Voir les résultats complets</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
@@ -4487,8 +5887,16 @@
           <t>Full Results</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Resultados completos</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Résultats complets</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -4507,8 +5915,16 @@
           <t>No recorded answers for this quiz.</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>No hay respuestas registradas para este cuestionario.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Aucune réponse enregistrée pour ce quiz.</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -4527,8 +5943,16 @@
           <t>Your answer:</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tu respuesta:</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Ta réponse :</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -4547,8 +5971,16 @@
           <t>Correct answer:</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Respuesta correcta:</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Bonne réponse :</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>Shown only for incorrect rows</t>
@@ -4571,8 +6003,16 @@
           <t>(blank)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>(en blanco)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>(vide)</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr">
         <is>
           <t>Shown when a skipped/empty answer was recorded</t>
@@ -4595,8 +6035,16 @@
           <t>Something went wrong loading results.</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cargar los resultados.</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -4615,8 +6063,16 @@
           <t>List Types</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tipos de lista</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Types de liste</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
           <t>New info icon next to the List type label</t>
@@ -4639,8 +6095,16 @@
           <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -4659,8 +6123,16 @@
           <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -4679,8 +6151,16 @@
           <t>Name this list</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Nombra esta lista</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Nomme cette liste</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
           <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
@@ -4703,8 +6183,16 @@
           <t>List name (updates it)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Nombre de la lista (la actualiza)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Nom de la liste (la met à jour)</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr">
         <is>
           <t>Placeholder shown once the list is already saved — shortened to fit</t>
@@ -4747,8 +6235,16 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Editar</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
@@ -4771,11 +6267,19 @@
           <t>✕</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before</t>
+          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
         </is>
       </c>
     </row>
@@ -4797,10 +6301,14 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> not pairs — translate into:</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
+          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
@@ -4824,8 +6332,16 @@
           <t>Translate</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Traducir</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Traduire</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -4844,8 +6360,16 @@
           <t>Translating…</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Traduciendo…</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Traduction en cours…</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -4864,8 +6388,16 @@
           <t>Something went wrong translating those words.</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Algo salió mal al traducir esas palabras.</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
@@ -4884,8 +6416,16 @@
           <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
@@ -4928,8 +6468,16 @@
           <t>Rename</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Cambiar nombre</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Renommer</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
           <t>New — separates renaming an already-saved list from saving its pairs</t>
@@ -4952,8 +6500,16 @@
           <t>Save</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Guardar</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Enregistrer</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>Inline rename confirm button</t>
@@ -4976,8 +6532,16 @@
           <t>Cancel</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Cancelar</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Annuler</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
           <t>Inline rename cancel button</t>
@@ -5000,8 +6564,16 @@
           <t>Something went wrong renaming.</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cambiar el nombre.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du renommage.</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -5020,8 +6592,16 @@
           <t>Save Changes</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Guardar cambios</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Enregistrer les modifications</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
@@ -5044,8 +6624,16 @@
           <t>List type (locked)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Tipo de lista (bloqueado)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Type de liste (verrouillé)</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>Appended to the label once a list is saved — type can't change after first save</t>
@@ -5068,8 +6656,16 @@
           <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>Appended to the existing List Types info alert once locked</t>
@@ -5092,8 +6688,16 @@
           <t>Past Quizzes</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Cuestionarios anteriores</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Quiz précédents</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>New section showing completed quiz history</t>
@@ -5121,8 +6725,16 @@
           <t>No completed quizzes yet.</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Aún no hay cuestionarios completados.</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Aucun quiz terminé pour l'instant.</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -5141,8 +6753,16 @@
           <t>{correct}/{total} correct ({pct}%)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>{correct}/{total} correctas ({pct}%)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>{correct}/{total} correctes ({pct} %)</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>Template</t>
@@ -5165,8 +6785,16 @@
           <t>Deleted list</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Lista eliminada</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Liste supprimée</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>Shown when a past quiz's list no longer exists</t>
@@ -5189,8 +6817,16 @@
           <t>Discard unsaved words?</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>¿Descartar palabras sin guardar?</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Abandonner les mots non enregistrés ?</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
@@ -5213,8 +6849,16 @@
           <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
@@ -5233,8 +6877,16 @@
           <t>Leave Without Saving</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Salir sin guardar</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Quitter sans enregistrer</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>Destructive confirm action</t>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1260,17 +1260,13 @@
           <t>Source word</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Palabra de origen</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Mot source</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Superseded by source_word_placeholder_dynamic — was static, replaced with actual language name + known/learning framing</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1288,17 +1284,13 @@
           <t>Target word</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Palabra de destino</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Mot cible</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Superseded by target_word_placeholder_dynamic</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6893,6 +6885,139 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>language-order-confirm.tsx</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>order_confirm_prompt_template</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Detected {first} and {second}. Which one do you already know?</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>language-order-confirm.tsx</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>order_confirm_option_template</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>I know {language}</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Ya sé {language}</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Je connais déjà {language}</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Two buttons</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> one per detected language</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>add-words.tsx</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>source_word_placeholder_dynamic</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Word in {language} (known)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Palabra en {language} (conocido)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Mot en {language} (connu)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Replaces static "Source word" placeholder — shows actual selected language + known/learning framing instead of source/target jargon</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>add-words.tsx</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>target_word_placeholder_dynamic</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Word in {language} (learning)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Palabra en {language} (aprendiendo)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Mot en {language} (en apprentissage)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Replaces static "Target word" placeholder</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -1264,7 +1264,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Superseded by source_word_placeholder_dynamic — was static, replaced with actual language name + known/learning framing</t>
+          <t>Superseded by source_word_placeholder_dynamic — was static</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> replaced with actual language name</t>
         </is>
       </c>
     </row>
@@ -3692,25 +3697,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>i_already_know</t>
+          <t>from_label</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>I already know</t>
+          <t>From</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Ya sé</t>
+          <t>Desde</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Je connais déjà</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>Depuis</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Replaces "I already know" — short label translates cleanly, standard in translation-app pickers (Google Translate, Duolingo-style)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3720,25 +3729,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>i_am_learning</t>
+          <t>to_label</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>I'm learning</t>
+          <t>To</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Estoy aprendiendo</t>
+          <t>Hacia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>J'apprends</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
+          <t>Vers</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Replaces "I'm learning" — same reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6967,22 +6980,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Word in {language} (known)</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Palabra en {language} (conocido)</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Mot en {language} (connu)</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Replaces static "Source word" placeholder — shows actual selected language + known/learning framing instead of source/target jargon</t>
+          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
         </is>
       </c>
     </row>
@@ -6999,22 +7012,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Word in {language} (learning)</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Palabra en {language} (aprendiendo)</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Mot en {language} (en apprentissage)</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Replaces static "Target word" placeholder</t>
+          <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,44 +417,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:H224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>File / Component</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>English (source)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Spanish</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>French</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -463,22 +469,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>app_name</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>LangReps</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Proper name — may stay untranslated</t>
         </is>
@@ -487,114 +498,134 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>home_subtitle</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Build a vocab list, then let AI generate an adaptive quiz for it.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Crea una lista de vocabulario y deja que la IA genere un cuestionario adaptativo para ti.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Crée une liste de vocabulaire, puis laisse l'IA générer un quiz adaptatif pour toi.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>settings_link</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Configuración</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Paramètres</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>log_out</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Log Out</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Cerrar sesión</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Se déconnecter</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>delete_account</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Delete Account</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Eliminar cuenta</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Supprimer le compte</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Also used as alert title</t>
         </is>
@@ -603,58 +634,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>log_in_sign_up</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Log In / Sign Up</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Iniciar sesión / Registrarse</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Se connecter / S'inscrire</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>signed_in_as</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Signed in as {email}</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Sesión iniciada como {email}</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Connecté en tant que {email}</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Template — {email} not translated</t>
         </is>
@@ -663,198 +704,233 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>add_words_manually</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Add Words Manually</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Añadir palabras manualmente</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Ajouter des mots manuellement</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>paste_vocab_list</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Paste Vocab List</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Pegar lista de vocabulario</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Coller une liste de vocabulaire</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>upload_a_file</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Upload a File</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Subir un archivo</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Importer un fichier</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>share_a_picture</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Upload a Photo</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Subir una foto</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Importer une photo</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>my_lists</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Mis listas</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Mes listes</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>my_quizzes</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>My Quizzes</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Mis cuestionarios</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Mes quiz</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>delete_account_confirm</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>This permanently deletes your account and all your saved lists. This can't be undone.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Esto elimina permanentemente tu cuenta y todas tus listas guardadas. Esta acción no se puede deshacer.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Cela supprime définitivement ton compte et toutes tes listes enregistrées. Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Alert body</t>
         </is>
@@ -863,30 +939,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Cancel</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Cancelar</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Annuler</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Alert button — reused across screens</t>
         </is>
@@ -895,30 +976,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>delete</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Delete</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Eliminar</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Supprimer</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Alert button — reused across screens</t>
         </is>
@@ -927,30 +1013,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>error_generic</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Something went wrong.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Algo salió mal.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Une erreur s'est produite.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Fallback error — reused across screens</t>
         </is>
@@ -959,30 +1050,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>log_in</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Log In</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Iniciar sesión</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Se connecter</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Screen title + button + toggle target</t>
         </is>
@@ -991,30 +1087,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>sign_up</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Sign Up</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Registrarse</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>S'inscrire</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Screen title + button + toggle target</t>
         </is>
@@ -1023,251 +1124,296 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>email_placeholder</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Correo electrónico</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>password_placeholder</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Contraseña</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Mot de passe</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>please_wait</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Please wait…</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Espera, por favor…</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Veuillez patienter…</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>switch_to_signup</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Don't have an account? Sign up</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>¿No tienes una cuenta? Regístrate</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Pas de compte ? Inscris-toi</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>switch_to_login</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Already have an account? Log in</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>¿Ya tienes una cuenta? Inicia sesión</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Tu as déjà un compte ? Connecte-toi</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>confirm_email_message</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Check your email to confirm, then log in below.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Revisa tu correo para confirmar y luego inicia sesión abajo.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Vérifie tes e-mails pour confirmer, puis connecte-toi ci-dessous.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>login.tsx</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>account_created_message</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Account created — log in below.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Cuenta creada — inicia sesión abajo.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Compte créé — connecte-toi ci-dessous.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>add_words_title</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Add Words</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Añadir palabras</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Ajouter des mots</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>source_word_placeholder</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Source word</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Superseded by source_word_placeholder_dynamic — was static</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve"> replaced with actual language name</t>
         </is>
@@ -1276,22 +1422,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>target_word_placeholder</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Target word</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Superseded by target_word_placeholder_dynamic</t>
         </is>
@@ -1300,30 +1451,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>add_to_list</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Add to list</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Añadir a la lista</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Ajouter à la liste</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Reused on paste-text.tsx</t>
         </is>
@@ -1332,58 +1488,68 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>paste_vocab_list_title</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Paste Vocab List</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Pegar lista de vocabulario</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Coller une liste de vocabulaire</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>paste_instructions</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>One pair per line — a tab, "-&gt;", ":", or similar between each word and its translation. e.g. hello -&gt; hola</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción. p. ej. hello -&gt; hola</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction. ex. hello -&gt; hola</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Contains a literal example — keep example untranslated or localize it</t>
         </is>
@@ -1392,58 +1558,68 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>paste_placeholder</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Paste your vocab list here</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Pega aquí tu lista de vocabulario</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Colle ici ta liste de vocabulaire</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>parsing_ellipsis</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Parsing…</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Analizando…</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Analyse en cours…</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Reused on upload-file.tsx</t>
         </is>
@@ -1452,30 +1628,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>couldnt_parse_lines</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Couldn't parse {n} line(s): {list}</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>No se pudieron leer {n} línea(s): {list}</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Impossible d'analyser {n} ligne(s) : {list}</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Template with pluralization (1 line vs N lines)</t>
         </is>
@@ -1484,142 +1665,167 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>paste-text.tsx</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>error_parsing_text</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Something went wrong parsing that text.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Algo salió mal al analizar ese texto.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de l'analyse de ce texte.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>upload_a_file_title</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Upload a File</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Subir un archivo</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Importer un fichier</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>upload_file_instructions</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>A plain text or CSV file, one pair per line — a tab, "-&gt;", ":", or similar between each word and its translation.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Un archivo de texto plano o CSV, un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Un fichier texte brut ou CSV, une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>choose_file</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Choose File</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Elegir archivo</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Choisir un fichier</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>last_file</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Last file: {name}</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Último archivo: {name}</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Dernier fichier : {name}</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Template — filename not translated</t>
         </is>
@@ -1628,86 +1834,101 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>upload-file.tsx</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>error_parsing_file</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Something went wrong parsing that file.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Algo salió mal al analizar ese archivo.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de l'analyse de ce fichier.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>share_a_picture_title</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Upload a Photo</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Subir una foto</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Importer une photo</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>share_picture_instructions</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>A photo or screenshot of word pairs (e.g. "house -&gt; casa") — AI will read the pairs out of it.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Una foto o captura de pantalla de pares de palabras (p. ej. "house -&gt; casa") — la IA leerá los pares.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Une photo ou capture d'écran de paires de mots (ex. "house -&gt; casa") — l'IA en extraira les paires.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Contains a literal example</t>
         </is>
@@ -1716,198 +1937,233 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>take_photo</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Take Photo</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Tomar foto</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Prendre une photo</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>choose_from_library</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Choose from Library</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Elegir de la galería</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Choisir depuis la galerie</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>reading_ellipsis</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Reading…</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Leyendo…</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Lecture en cours…</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>error_camera_permission</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Camera access is needed to take a photo.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Se necesita acceso a la cámara para tomar una foto.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>L'accès à l'appareil photo est nécessaire pour prendre une photo.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>error_library_permission</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Photo library access is needed to choose an image.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Se necesita acceso a la galería de fotos para elegir una imagen.</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>L'accès à la photothèque est nécessaire pour choisir une image.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>upload-picture.tsx</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>error_reading_image</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Something went wrong reading that image.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Algo salió mal al leer esa imagen.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de la lecture de cette image.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>generate_quiz_title</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Generate Quiz</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Generar cuestionario</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Générer un quiz</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Also reused as button label</t>
         </is>
@@ -1916,30 +2172,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>unsaved_list</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Unsaved list</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Lista sin guardar</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Liste non enregistrée</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Fallback when no list name</t>
         </is>
@@ -1948,58 +2209,68 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>min_words_warning</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>You need at least 3 words to generate a quiz.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Necesitas al menos 3 palabras para generar un cuestionario.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Il te faut au moins 3 mots pour générer un quiz.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>words_in_list</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>{n} words in this list.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>{n} palabras en esta lista.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>{n} mots dans cette liste.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Template with pluralization</t>
         </is>
@@ -2008,86 +2279,101 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>how_many_questions</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>How many questions?</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>¿Cuántas preguntas?</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Combien de questions ?</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>tense_label</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Tense</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Tiempo verbal</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Temps</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>mixed_tense</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Mixte</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Dropdown option meaning vary tense freely</t>
         </is>
@@ -2096,30 +2382,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>flip_toggle_label</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Flip: translate {target} → {source}</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Invertir: traducir de {target} a {source}</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Inverser : traduire de {target} vers {source}</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Template — language names not translated here</t>
         </is>
@@ -2128,198 +2419,233 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>generating_quiz</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Generating your quiz…</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Generando tu cuestionario…</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Génération de ton quiz…</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>target_my_mistakes</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Target My Mistakes</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Enfocarme en mis errores</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Cibler mes erreurs</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>generate_similar_quiz</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Generate Similar Quiz</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Generar cuestionario similar</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Générer un quiz similaire</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>generate-quiz.tsx</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>error_generating_quiz</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Something went wrong generating your quiz.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Algo salió mal al generar tu cuestionario.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de la génération de ton quiz.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>my_lists_title</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Mis listas</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Mes listes</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>no_saved_lists</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>No saved lists yet.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Aún no tienes listas guardadas.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Aucune liste enregistrée pour l'instant.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>progress_link</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Progreso</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Progrès</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Row action label</t>
         </is>
@@ -2328,58 +2654,68 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>delete_list_alert_title</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Delete List</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Eliminar lista</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Supprimer la liste</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>delete_list_confirm</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Delete "{name}"? This can't be undone.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>¿Eliminar "{name}"? Esta acción no se puede deshacer.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Supprimer « {name} » ? Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
@@ -2388,198 +2724,233 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>error_loading_lists</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Something went wrong loading your lists.</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Algo salió mal al cargar tus listas.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors du chargement de tes listes.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>error_loading_list</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Something went wrong loading that list.</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Algo salió mal al cargar esa lista.</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors du chargement de cette liste.</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>error_deleting_list</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Something went wrong deleting that list.</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Algo salió mal al eliminar esa lista.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de la suppression de cette liste.</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>my_quizzes_title</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>My Quizzes</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Mis cuestionarios</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Mes quiz</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>no_quizzes_in_progress</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>No quizzes in progress.</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>No hay cuestionarios en curso.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Aucun quiz en cours.</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>quiz_in_progress_fallback</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Quiz in progress</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Cuestionario en curso</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Quiz en cours</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>question_n_of_total</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Question {n} of {total}</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Pregunta {n} de {total}</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Question {n} sur {total}</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Template — also used in quiz.tsx</t>
         </is>
@@ -2588,58 +2959,68 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>delete_quiz_alert_title</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Delete Quiz</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Eliminar cuestionario</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Supprimer le quiz</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>delete_quiz_confirm</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Delete this quiz for "{name}"? This can't be undone.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>¿Eliminar este cuestionario de "{name}"? Esta acción no se puede deshacer.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Supprimer ce quiz pour « {name} » ? Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
@@ -2648,86 +3029,101 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>error_loading_quizzes</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Something went wrong loading your quizzes.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Algo salió mal al cargar tus cuestionarios.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors du chargement de tes quiz.</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>error_deleting_quiz</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Something went wrong deleting that quiz.</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Algo salió mal al eliminar ese cuestionario.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de la suppression de ce quiz.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>progress_title</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Progreso</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Progrès</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Title fallback + subtitle label</t>
         </is>
@@ -2736,58 +3132,68 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>no_completed_quizzes</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>No completed quizzes for this list yet.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Aún no hay cuestionarios completados.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Aucun quiz terminé pour l'instant.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>score_fraction_pct</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>{correct}/{total} ({pct}%)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>{correct}/{total} ({pct}%)</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>{correct}/{total} ({pct} %)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Number formatting conventions vary by locale</t>
         </is>
@@ -2796,310 +3202,365 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>list-history.tsx</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>error_loading_history</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Something went wrong loading quiz history.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Algo salió mal al cargar el historial del cuestionario.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors du chargement de l'historique du quiz.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>settings_title</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Configuración</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Paramètres</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>default_level_hint</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Default level for new quizzes — you can still change it for any single quiz when generating it.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Nivel predeterminado para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Niveau par défaut pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>auto_delete_toggle</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Auto-delete completed quizzes after 30 days</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Eliminar automáticamente los cuestionarios completados después de 30 días</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>adaptive_quizzes_toggle</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Cuestionarios adaptativos — comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>your_answer_placeholder</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Your answer</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Tu respuesta</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Ta réponse</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>submit</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Submit</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Enviar</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Valider</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>skip_question</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Skip this question</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Saltar esta pregunta</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Passer cette question</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>hide_word_list</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Hide word list</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Ocultar lista de palabras</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Masquer la liste de mots</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>stuck_see_word_list</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Stuck? See the word list</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>¿Atascado? Consulta la lista de palabras</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Bloqué ? Consulte la liste de mots</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>your_answer_was</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Your answer: {answer}</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Tu respuesta: {answer}</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Ta réponse : {answer}</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
@@ -3108,58 +3569,68 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>correct_feedback</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>That's correct!</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>¡Correcto!</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>C'est correct !</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>incorrect_feedback</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Sorry, that's incorrect. The answer was: {answer}</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Lo siento, es incorrecto. La respuesta era: {answer}</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Désolé, c'est incorrect. La réponse était : {answer}</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
@@ -3168,114 +3639,134 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>finish_quiz</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Finish Quiz</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Finalizar cuestionario</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Terminer le quiz</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>quiz.tsx</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>next_question</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Next Question</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Siguiente pregunta</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Question suivante</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>quiz_complete_title</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Quiz Complete!</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>¡Cuestionario completado!</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Quiz terminé !</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>score_correct</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>{n} / {total} correct</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>{n} / {total} correctas</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>{n} / {total} correctes</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
@@ -3284,310 +3775,365 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>back_to_home</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Back to Home</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Volver al inicio</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Retour à l'accueil</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>undo_last</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Undo last</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Deshacer última</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Annuler le dernier</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>clear_list</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Clear list</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Vaciar lista</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Vider la liste</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>no_words_added</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>No words added yet.</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Aún no has añadido palabras.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Aucun mot ajouté pour l'instant.</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>list_name_update_placeholder</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>List name (saving updates it)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Nombre de la lista (al guardar se actualiza)</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Nom de la liste (l'enregistrement la met à jour)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>list_name_placeholder</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>List name</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Nombre de la lista</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Nom de la liste</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>saving_ellipsis</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>Saving…</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Guardando…</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Enregistrement…</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>save_list</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Save List</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Guardar lista</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Enregistrer la liste</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>saved_message</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Saved!</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>¡Guardado!</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Enregistré !</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>error_saving</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Something went wrong saving.</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>Algo salió mal al guardar.</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de l'enregistrement.</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>add_more_words_to_quiz</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Add {n} more word(s) to generate a quiz</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>Añade {n} palabra(s) más para generar un cuestionario</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Ajoute {n} mot(s) de plus pour générer un quiz</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Template with pluralization</t>
         </is>
@@ -3596,30 +4142,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>generate_quiz_button</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Generate Quiz</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>Generar cuestionario</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Générer un quiz</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Reused label</t>
         </is>
@@ -3628,30 +4179,35 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>my_lists_link</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>My Lists</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>Mis listas</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Mes listes</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>Reused label</t>
         </is>
@@ -3660,30 +4216,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>level_label</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Niveau</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
         </is>
@@ -3692,30 +4253,35 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>language-picker.tsx</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>from_label</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>Desde</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Depuis</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>Replaces "I already know" — short label translates cleanly, standard in translation-app pickers (Google Translate, Duolingo-style)</t>
         </is>
@@ -3724,30 +4290,35 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>language-picker.tsx</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>to_label</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>Hacia</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Vers</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>Replaces "I'm learning" — same reasoning</t>
         </is>
@@ -3756,22 +4327,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>language-picker.tsx</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>language_names</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>English / Spanish / French</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
         <is>
           <t>Design decision: show in UI language or always native form (Español, Français)?</t>
         </is>
@@ -3780,30 +4356,35 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>parsing-warning.tsx</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>parsing_warning_text</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>El análisis puede cometer errores con formatos inusuales. Para mejores resultados, prueba subir una foto en su lugar.</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>L'analyse peut faire des erreurs avec une mise en forme inhabituelle. Pour de meilleurs résultats, essaie plutôt d'importer une photo.</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>Contains an inline link to Share a Picture</t>
         </is>
@@ -3812,22 +4393,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>trend_improving_a_lot</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>5 message variants — 'Great progress! Your scores are climbing fast...' etc.</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
         <is>
           <t>See file directly, too long to list individually</t>
         </is>
@@ -3836,22 +4422,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>trend_improving</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>5 message variants — 'You're improving steadily on this list.' etc.</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
@@ -3860,22 +4451,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>trend_steady</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>5 message variants — 'Your scores are holding steady...' etc.</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
@@ -3884,22 +4480,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>trend_declining</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>5 message variants — 'Your scores dipped a bit recently...' etc.</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
@@ -3908,22 +4509,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>quiz-feedback.ts</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>trend_declining_a_lot</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>5 message variants — 'Your scores dropped noticeably...' etc.</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
         <is>
           <t>See file directly</t>
         </is>
@@ -3932,22 +4538,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>backend (api errors)</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>backend_error_text</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
         <is>
           <t>Needs its own translation strategy — see Notes tab</t>
         </is>
@@ -3956,86 +4567,101 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>sample_lists_title</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Sample Lists</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>Listas de ejemplo</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Listes types</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>sample_lists_hint</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>sample_list_name_template</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>Template — used as both display label and saved list name</t>
         </is>
@@ -4044,30 +4670,35 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>sample_list_type_vocab</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>Vocab</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>Vocabulario</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Vocabulaire</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>Reused label under each sample list row</t>
         </is>
@@ -4076,30 +4707,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>sample_list_type_verbs</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>Verbs</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Verbes</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Reused label under each sample list row</t>
         </is>
@@ -4108,86 +4744,101 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>sample_list_add</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Add</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>Añadir</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Ajouter</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>sample_list_adding</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Adding…</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>Añadiendo…</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Ajout en cours…</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>sample_list_added</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Añadido</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Ajouté</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
         </is>
@@ -4196,338 +4847,398 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>error_adding_sample</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Algo salió mal al añadir esa lista de ejemplo.</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Omitir</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Passer</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>back</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>Atrás</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Retour</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Next</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Siguiente</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Suivant</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>get_started</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Get Started</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Empezar</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Commencer</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>slide1_headline</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>Build Your List</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>Crea tu lista</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>Crée ta liste</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>slide1_body</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>slide2_headline</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>Practica con cuestionarios adaptativos</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Entraîne-toi avec des quiz adaptatifs</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>slide2_body</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>slide3_headline</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>Watch Your Progress</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>Observa tu progreso</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Suis ta progression</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>slide3_body</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>about_langreps_link</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>About LangReps</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>Acerca de LangReps</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>À propos de LangReps</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>Links to /onboarding to replay it manually</t>
         </is>
@@ -4536,114 +5247,134 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>sort_by_label</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Sort by</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>Ordenar por</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Trier par</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>sort_by_date</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>Last Uploaded</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Última subida</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Dernier import</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>sort_by_name</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>Nom</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>last_uploaded_template</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Last uploaded: {date}</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>Última subida: {date}</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>Dernier import : {date}</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
         </is>
@@ -4652,30 +5383,35 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>sample_list_name_template_v2</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Superseded template — replaces the old arrow-notation naming</t>
         </is>
@@ -4684,30 +5420,35 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>sample_list_card_title</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>Vocabulario {count} / Verbo {count}</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Vocabulaire {count} / Verbe {count}</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>Sample-list catalog card title, replaces the old full name display</t>
         </is>
@@ -4716,30 +5457,35 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>sample_list_card_flags</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
@@ -4748,58 +5494,68 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
           <t>index.tsx</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>signup_incentive_hint</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>default_level_title</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Default Level</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>Nivel predeterminado</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Niveau par défaut</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>New section title for Settings redesign (bold title + description layout)</t>
         </is>
@@ -4808,30 +5564,35 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>auto_delete_title</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Auto-Delete Old Quizzes</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>Eliminar automáticamente cuestionarios antiguos</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Suppression automatique des anciens quiz</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>New section title</t>
         </is>
@@ -4840,30 +5601,35 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>auto_delete_desc</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>Completed quizzes are removed after 30 days</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>Los cuestionarios completados se eliminan después de 30 días</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Les quiz terminés sont supprimés après 30 jours</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>Description moved under the bold title</t>
         </is>
@@ -4872,30 +5638,35 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>adaptive_quizzes_title</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>Adaptive Quizzes</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Cuestionarios adaptativos</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Quiz adaptatifs</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>New section title</t>
         </is>
@@ -4904,30 +5675,35 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>adaptive_quizzes_desc</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>Get feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>Description moved under the bold title</t>
         </is>
@@ -4936,30 +5712,35 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>require_accents_title</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>Require Diacritics</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>Exigir diacríticos</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Exiger les diacritiques</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>New toggle — renamed from "Require Accents"</t>
         </is>
@@ -4968,30 +5749,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>settings.tsx</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>require_accents_desc</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>Off accepts "cafe" for "café"</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>Desactivado acepta "cafe" en lugar de "café"</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Désactivé accepte "cafe" pour "café"</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
         </is>
@@ -5000,30 +5786,35 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>your_lists_section_title</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Your Lists</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>Tus listas</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Tes listes</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>New section title alongside bulk-select controls</t>
         </is>
@@ -5032,30 +5823,35 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>bulk_select_toggle</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Select / Done</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>Seleccionar / Listo</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Sélectionner / Terminé</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
         </is>
@@ -5064,35 +5860,40 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>bulk_select_all</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Select All / Deselect All</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>Seleccionar todo / Deseleccionar todo</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Tout sélectionner / Tout désélectionner</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>Shared pattern</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t xml:space="preserve"> My Lists and My Quizzes</t>
         </is>
@@ -5101,35 +5902,40 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>bulk_delete_selected_template</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Delete ({count})</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>Eliminar ({count})</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Supprimer ({count})</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>Shared pattern</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t xml:space="preserve"> My Lists and My Quizzes</t>
         </is>
@@ -5138,35 +5944,40 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>bulk_deleting</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Deleting…</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>Eliminando…</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Suppression…</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>Shared pattern</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t xml:space="preserve"> My Lists and My Quizzes</t>
         </is>
@@ -5175,170 +5986,200 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>bulk_delete_lists_alert_title</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Delete Lists</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>Eliminar listas</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Supprimer les listes</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>bulk_delete_lists_alert_message_template</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Delete {count} list(s)? This can't be undone.</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>quizzes_in_progress_count_template</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>{count} in progress</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>{count} en curso</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>{count} en cours</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>bulk_delete_quizzes_alert_title</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>Delete Quizzes</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>Eliminar cuestionarios</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Supprimer les quiz</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>bulk_delete_quizzes_alert_message_template</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>Delete {count} quiz(zes)? This can't be undone.</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>sort_by_last_updated</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Dernière mise à jour</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
         </is>
@@ -5347,30 +6188,35 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>last_updated_template</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>Last updated: {date}</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>Última actualización: {date}</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Dernière mise à jour : {date}</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
         </is>
@@ -5379,30 +6225,35 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>quiz_type_badge_vocab</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>Vocab</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="E170" t="inlineStr">
         <is>
           <t>Vocabulario</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Vocabulaire</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
         </is>
@@ -5411,30 +6262,35 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>quiz_type_badge_verb</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>Verb</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>Verbo</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>Verbe</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>Small badge next to the quiz row title</t>
         </is>
@@ -5443,30 +6299,35 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>canned_feedback_mastery</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
         </is>
@@ -5475,30 +6336,35 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>canned_feedback_solid</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>70-89% correct</t>
         </is>
@@ -5507,30 +6373,35 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>canned_feedback_building</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>40-69% correct</t>
         </is>
@@ -5539,30 +6410,35 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>canned_feedback_struggling</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>Below 40% correct</t>
         </is>
@@ -5571,30 +6447,35 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>cefr_info_alert_title</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>CEFR Levels</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>Niveles del MCER</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Niveaux du CECR</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>Alert title triggered by new info icon next to the Level label</t>
         </is>
@@ -5603,190 +6484,225 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>cefr_a1_explanation</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Breakthrough — basic words and phrases for everyday needs.</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>cefr_a2_explanation</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>cefr_b1_explanation</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>cefr_b2_explanation</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>cefr_c1_explanation</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
           <t>cefr-level-picker.tsx</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>cefr_c2_explanation</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Mastery — near-native fluency with precise, nuanced expression.</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
           <t>app-splash.tsx</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>splash_title</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>LangReps</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
         <is>
           <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
         </is>
@@ -5795,50 +6711,60 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
           <t>app-splash.tsx</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>splash_tagline</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>Language reps that stick.</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>Repeticiones de idiomas que se quedan.</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Des répétitions de langue qui restent.</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>app-splash.tsx</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>splash_copyright</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>© 2026 MarApps Development</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
         <is>
           <t>Pinned bottom-right corner</t>
         </is>
@@ -5847,30 +6773,35 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>quiz-complete.tsx</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>see_full_results</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>See Full Results</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t>Ver resultados completos</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Voir les résultats complets</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
         </is>
@@ -5879,114 +6810,134 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
           <t>quiz-results.tsx</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>full_results_title</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Full Results</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>Resultados completos</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Résultats complets</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
           <t>quiz-results.tsx</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>no_recorded_answers</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>No recorded answers for this quiz.</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>No hay respuestas registradas para este cuestionario.</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Aucune réponse enregistrée pour ce quiz.</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
           <t>quiz-results.tsx</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>your_answer_label</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Your answer:</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>Tu respuesta:</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Ta réponse :</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
           <t>quiz-results.tsx</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>correct_answer_label</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>Correct answer:</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>Respuesta correcta:</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Bonne réponse :</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>Shown only for incorrect rows</t>
         </is>
@@ -5995,30 +6946,35 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
           <t>quiz-results.tsx</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>blank_answer_fallback</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t>(en blanco)</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>(vide)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>Shown when a skipped/empty answer was recorded</t>
         </is>
@@ -6027,58 +6983,68 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
           <t>quiz-results.tsx</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>error_loading_results</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>Something went wrong loading results.</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>Algo salió mal al cargar los resultados.</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors du chargement des résultats.</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>list_type_info_alert_title</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>List Types</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>Tipos de lista</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>Types de liste</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>New info icon next to the List type label</t>
         </is>
@@ -6087,86 +7053,101 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>list_type_info_vocab</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>list_type_info_verb</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>save_input_placeholder_new</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>Name this list</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t>Nombra esta lista</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Nomme cette liste</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="G196" t="inlineStr">
         <is>
           <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
         </is>
@@ -6175,30 +7156,35 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>save_input_placeholder_update</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>List name (updates it)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>Nombre de la lista (la actualiza)</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Nom de la liste (la met à jour)</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>Placeholder shown once the list is already saved — shortened to fit</t>
         </is>
@@ -6207,18 +7193,23 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
           <t>constants/styles.ts</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>placeholder_color_note</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
         <is>
           <t>Not a UI string — new colors.placeholder token (#8C7F63) applied via placeholderTextColor to every TextInput app-wide; RN's default placeholder gray had poor contrast on the parchment background and was nearly invisible</t>
         </is>
@@ -6227,30 +7218,35 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
           <t>my-lists.tsx</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>edit_list_link</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Edit</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>Editar</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>Modifier</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
         </is>
@@ -6259,30 +7255,35 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>remove_word_icon</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>✕</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
         </is>
@@ -6291,31 +7292,36 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
           <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>translate_prompt_template</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>{n} line(s) looked like single word(s)</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
         <is>
           <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
         </is>
@@ -6324,114 +7330,134 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
           <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>translate_button</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>Translate</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t>Traducir</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>Traduire</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
           <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>translating_ellipsis</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Translating…</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>Traduciendo…</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>Traduction en cours…</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
           <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>error_translating</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Something went wrong translating those words.</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>Algo salió mal al traducir esas palabras.</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
           <t>onboarding.tsx</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>slide1_body_updated</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
         </is>
@@ -6440,18 +7466,23 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>saved_list_heading</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
         <is>
           <t>Not new text — shows the list's own saved name prominently at the top of PairsReview once saved (Edit flow especially), styled like Generate Quiz's list-name heading</t>
         </is>
@@ -6460,30 +7491,35 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>rename_link</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Rename</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>Cambiar nombre</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>Renommer</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>New — separates renaming an already-saved list from saving its pairs</t>
         </is>
@@ -6492,30 +7528,35 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>rename_save_button</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>Save</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>Guardar</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Enregistrer</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>Inline rename confirm button</t>
         </is>
@@ -6524,30 +7565,35 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>rename_cancel_button</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Cancel</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>Cancelar</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>Annuler</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>Inline rename cancel button</t>
         </is>
@@ -6556,58 +7602,68 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>error_renaming</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Something went wrong renaming.</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>Algo salió mal al cambiar el nombre.</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Une erreur s'est produite lors du renommage.</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>save_changes_button</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>Save Changes</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>Guardar cambios</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>Enregistrer les modifications</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
         </is>
@@ -6616,30 +7672,35 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>list_type_locked_label</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>List type (locked)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>Tipo de lista (bloqueado)</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Type de liste (verrouillé)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>Appended to the label once a list is saved — type can't change after first save</t>
         </is>
@@ -6648,30 +7709,35 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
           <t>pairs-review.tsx</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>list_type_locked_explanation</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>Appended to the existing List Types info alert once locked</t>
         </is>
@@ -6680,35 +7746,40 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>past_quizzes_section_title</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>Past Quizzes</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>Cuestionarios anteriores</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Quiz précédents</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>New section showing completed quiz history</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="H214" t="inlineStr">
         <is>
           <t xml:space="preserve"> fetched from GET /quiz-sessions/completed</t>
         </is>
@@ -6717,58 +7788,68 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>no_completed_quizzes</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>No completed quizzes yet.</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>Aún no hay cuestionarios completados.</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Aucun quiz terminé pour l'instant.</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>past_quiz_score_template</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>{correct}/{total} correct ({pct}%)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>{correct}/{total} correctas ({pct}%)</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>{correct}/{total} correctes ({pct} %)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>Template</t>
         </is>
@@ -6777,30 +7858,35 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
           <t>my-quizzes.tsx</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>deleted_list_fallback</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>Deleted list</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>Lista eliminada</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="F217" t="inlineStr">
         <is>
           <t>Liste supprimée</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="G217" t="inlineStr">
         <is>
           <t>Shown when a past quiz's list no longer exists</t>
         </is>
@@ -6809,30 +7895,35 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
           <t>back-button.tsx</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>discard_unsaved_alert_title</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>Discard unsaved words?</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>¿Descartar palabras sin guardar?</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>Abandonner les mots non enregistrés ?</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
         </is>
@@ -6841,58 +7932,68 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
           <t>back-button.tsx</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>discard_unsaved_alert_message</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
           <t>back-button.tsx</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>leave_without_saving</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>Leave Without Saving</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>Salir sin guardar</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>Quitter sans enregistrer</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>Destructive confirm action</t>
         </is>
@@ -6901,30 +8002,35 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t>language-order-confirm.tsx</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>order_confirm_prompt_template</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Detected {first} and {second}. Which one do you already know?</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
         </is>
@@ -6933,35 +8039,40 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
           <t>language-order-confirm.tsx</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>order_confirm_option_template</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>I know {language}</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>Ya sé {language}</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>Je connais déjà {language}</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="G222" t="inlineStr">
         <is>
           <t>Two buttons</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="H222" t="inlineStr">
         <is>
           <t xml:space="preserve"> one per detected language</t>
         </is>
@@ -6970,30 +8081,35 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>source_word_placeholder_dynamic</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Word in {language}</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>Palabra en {language}</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>Mot en {language}</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
         </is>
@@ -7002,30 +8118,35 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>target_word_placeholder_dynamic</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>Word in {language}</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>Palabra en {language}</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>Mot en {language}</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="G224" t="inlineStr">
         <is>
           <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
         </is>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1398,24 +1398,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>source_word_placeholder</t>
+          <t>add_to_list</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Source word</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>Add to list</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Añadir a la lista</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ajouter à la liste</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Superseded by source_word_placeholder_dynamic — was static</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> replaced with actual language name</t>
+          <t>Reused on paste-text.tsx</t>
         </is>
       </c>
     </row>
@@ -1427,26 +1430,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>paste-text.tsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>target_word_placeholder</t>
+          <t>paste_vocab_list_title</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Target word</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Superseded by target_word_placeholder_dynamic</t>
-        </is>
-      </c>
+          <t>Paste Vocab List</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pegar lista de vocabulario</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Coller une liste de vocabulaire</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1456,32 +1463,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>paste-text.tsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>add_to_list</t>
+          <t>paste_instructions</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Add to list</t>
+          <t>One pair per line — a tab, "-&gt;", ":", or similar between each word and its translation. e.g. hello -&gt; hola</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Añadir a la lista</t>
+          <t>Un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción. p. ej. hello -&gt; hola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajouter à la liste</t>
+          <t>Une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction. ex. hello -&gt; hola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Reused on paste-text.tsx</t>
+          <t>Contains a literal example — keep example untranslated or localize it</t>
         </is>
       </c>
     </row>
@@ -1498,22 +1505,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>paste_vocab_list_title</t>
+          <t>paste_placeholder</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paste Vocab List</t>
+          <t>Paste your vocab list here</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pegar lista de vocabulario</t>
+          <t>Pega aquí tu lista de vocabulario</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coller une liste de vocabulaire</t>
+          <t>Colle ici ta liste de vocabulaire</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1531,27 +1538,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>paste_instructions</t>
+          <t>parsing_ellipsis</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>One pair per line — a tab, "-&gt;", ":", or similar between each word and its translation. e.g. hello -&gt; hola</t>
+          <t>Parsing…</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción. p. ej. hello -&gt; hola</t>
+          <t>Analizando…</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction. ex. hello -&gt; hola</t>
+          <t>Analyse en cours…</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Contains a literal example — keep example untranslated or localize it</t>
+          <t>Reused on upload-file.tsx</t>
         </is>
       </c>
     </row>
@@ -1568,25 +1575,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>paste_placeholder</t>
+          <t>couldnt_parse_lines</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paste your vocab list here</t>
+          <t>Couldn't parse {n} line(s): {list}</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pega aquí tu lista de vocabulario</t>
+          <t>No se pudieron leer {n} línea(s): {list}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colle ici ta liste de vocabulaire</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Impossible d'analyser {n} ligne(s) : {list}</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Template with pluralization (1 line vs N lines)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1601,29 +1612,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>parsing_ellipsis</t>
+          <t>error_parsing_text</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Parsing…</t>
+          <t>Something went wrong parsing that text.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Analizando…</t>
+          <t>Algo salió mal al analizar ese texto.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Analyse en cours…</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Reused on upload-file.tsx</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de l'analyse de ce texte.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1633,34 +1640,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>paste-text.tsx</t>
+          <t>upload-file.tsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>couldnt_parse_lines</t>
+          <t>upload_a_file_title</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Couldn't parse {n} line(s): {list}</t>
+          <t>Upload a File</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No se pudieron leer {n} línea(s): {list}</t>
+          <t>Subir un archivo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Impossible d'analyser {n} ligne(s) : {list}</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Template with pluralization (1 line vs N lines)</t>
-        </is>
-      </c>
+          <t>Importer un fichier</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1670,27 +1673,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>paste-text.tsx</t>
+          <t>upload-file.tsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>error_parsing_text</t>
+          <t>upload_file_instructions</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Something went wrong parsing that text.</t>
+          <t>A plain text or CSV file, one pair per line — a tab, "-&gt;", ":", or similar between each word and its translation.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Algo salió mal al analizar ese texto.</t>
+          <t>Un archivo de texto plano o CSV, un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'analyse de ce texte.</t>
+          <t>Un fichier texte brut ou CSV, une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1708,22 +1711,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>upload_a_file_title</t>
+          <t>choose_file</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Upload a File</t>
+          <t>Choose File</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Subir un archivo</t>
+          <t>Elegir archivo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Importer un fichier</t>
+          <t>Choisir un fichier</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -1741,25 +1744,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>upload_file_instructions</t>
+          <t>last_file</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A plain text or CSV file, one pair per line — a tab, "-&gt;", ":", or similar between each word and its translation.</t>
+          <t>Last file: {name}</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Un archivo de texto plano o CSV, un par por línea — un tabulador, "-&gt;", ":", o algo similar entre cada palabra y su traducción.</t>
+          <t>Último archivo: {name}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Un fichier texte brut ou CSV, une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction.</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Dernier fichier : {name}</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Template — filename not translated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1774,22 +1781,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>choose_file</t>
+          <t>error_parsing_file</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Choose File</t>
+          <t>Something went wrong parsing that file.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elegir archivo</t>
+          <t>Algo salió mal al analizar ese archivo.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Choisir un fichier</t>
+          <t>Une erreur s'est produite lors de l'analyse de ce fichier.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -1802,34 +1809,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>upload-file.tsx</t>
+          <t>upload-picture.tsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>last_file</t>
+          <t>share_a_picture_title</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Last file: {name}</t>
+          <t>Upload a Photo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Último archivo: {name}</t>
+          <t>Subir una foto</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dernier fichier : {name}</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Template — filename not translated</t>
-        </is>
-      </c>
+          <t>Importer une photo</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1839,30 +1842,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>upload-file.tsx</t>
+          <t>upload-picture.tsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>error_parsing_file</t>
+          <t>share_picture_instructions</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Something went wrong parsing that file.</t>
+          <t>A photo or screenshot of word pairs (e.g. "house -&gt; casa") — AI will read the pairs out of it.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Algo salió mal al analizar ese archivo.</t>
+          <t>Una foto o captura de pantalla de pares de palabras (p. ej. "house -&gt; casa") — la IA leerá los pares.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'analyse de ce fichier.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Une photo ou capture d'écran de paires de mots (ex. "house -&gt; casa") — l'IA en extraira les paires.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Contains a literal example</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1877,22 +1884,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>share_a_picture_title</t>
+          <t>take_photo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Upload a Photo</t>
+          <t>Take Photo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Subir una foto</t>
+          <t>Tomar foto</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Importer une photo</t>
+          <t>Prendre une photo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -1910,29 +1917,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>share_picture_instructions</t>
+          <t>choose_from_library</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A photo or screenshot of word pairs (e.g. "house -&gt; casa") — AI will read the pairs out of it.</t>
+          <t>Choose from Library</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Una foto o captura de pantalla de pares de palabras (p. ej. "house -&gt; casa") — la IA leerá los pares.</t>
+          <t>Elegir de la galería</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Une photo ou capture d'écran de paires de mots (ex. "house -&gt; casa") — l'IA en extraira les paires.</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Contains a literal example</t>
-        </is>
-      </c>
+          <t>Choisir depuis la galerie</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1947,22 +1950,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>take_photo</t>
+          <t>reading_ellipsis</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Take Photo</t>
+          <t>Reading…</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tomar foto</t>
+          <t>Leyendo…</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Prendre une photo</t>
+          <t>Lecture en cours…</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -1980,22 +1983,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>choose_from_library</t>
+          <t>error_camera_permission</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Choose from Library</t>
+          <t>Camera access is needed to take a photo.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elegir de la galería</t>
+          <t>Se necesita acceso a la cámara para tomar una foto.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Choisir depuis la galerie</t>
+          <t>L'accès à l'appareil photo est nécessaire pour prendre une photo.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2013,22 +2016,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>reading_ellipsis</t>
+          <t>error_library_permission</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Reading…</t>
+          <t>Photo library access is needed to choose an image.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leyendo…</t>
+          <t>Se necesita acceso a la galería de fotos para elegir una imagen.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lecture en cours…</t>
+          <t>L'accès à la photothèque est nécessaire pour choisir une image.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2046,22 +2049,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>error_camera_permission</t>
+          <t>error_reading_image</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Camera access is needed to take a photo.</t>
+          <t>Something went wrong reading that image.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Se necesita acceso a la cámara para tomar una foto.</t>
+          <t>Algo salió mal al leer esa imagen.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>L'accès à l'appareil photo est nécessaire pour prendre une photo.</t>
+          <t>Une erreur s'est produite lors de la lecture de cette image.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2074,30 +2077,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>upload-picture.tsx</t>
+          <t>generate-quiz.tsx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>error_library_permission</t>
+          <t>generate_quiz_title</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Photo library access is needed to choose an image.</t>
+          <t>Generate Quiz</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Se necesita acceso a la galería de fotos para elegir una imagen.</t>
+          <t>Generar cuestionario</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>L'accès à la photothèque est nécessaire pour choisir une image.</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Générer un quiz</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Also reused as button label</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2107,30 +2114,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>upload-picture.tsx</t>
+          <t>generate-quiz.tsx</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>error_reading_image</t>
+          <t>unsaved_list</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Something went wrong reading that image.</t>
+          <t>Unsaved list</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Algo salió mal al leer esa imagen.</t>
+          <t>Lista sin guardar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la lecture de cette image.</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Liste non enregistrée</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fallback when no list name</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2145,29 +2156,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>generate_quiz_title</t>
+          <t>min_words_warning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Generate Quiz</t>
+          <t>You need at least 3 words to generate a quiz.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Generar cuestionario</t>
+          <t>Necesitas al menos 3 palabras para generar un cuestionario.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Générer un quiz</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Also reused as button label</t>
-        </is>
-      </c>
+          <t>Il te faut au moins 3 mots pour générer un quiz.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2182,27 +2189,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unsaved_list</t>
+          <t>words_in_list</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Unsaved list</t>
+          <t>{n} words in this list.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lista sin guardar</t>
+          <t>{n} palabras en esta lista.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liste non enregistrée</t>
+          <t>{n} mots dans cette liste.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fallback when no list name</t>
+          <t>Template with pluralization</t>
         </is>
       </c>
     </row>
@@ -2219,22 +2226,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>min_words_warning</t>
+          <t>how_many_questions</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>You need at least 3 words to generate a quiz.</t>
+          <t>How many questions?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Necesitas al menos 3 palabras para generar un cuestionario.</t>
+          <t>¿Cuántas preguntas?</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Il te faut au moins 3 mots pour générer un quiz.</t>
+          <t>Combien de questions ?</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2252,29 +2259,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>words_in_list</t>
+          <t>tense_label</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{n} words in this list.</t>
+          <t>Tense</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>{n} palabras en esta lista.</t>
+          <t>Tiempo verbal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{n} mots dans cette liste.</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Template with pluralization</t>
-        </is>
-      </c>
+          <t>Temps</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2289,25 +2292,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>how_many_questions</t>
+          <t>mixed_tense</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How many questions?</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>¿Cuántas preguntas?</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Combien de questions ?</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>Mixte</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dropdown option meaning vary tense freely</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2322,25 +2329,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tense_label</t>
+          <t>flip_toggle_label</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tense</t>
+          <t>Flip: translate {target} → {source}</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tiempo verbal</t>
+          <t>Invertir: traducir de {target} a {source}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Temps</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Inverser : traduire de {target} vers {source}</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Template — language names not translated here</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2355,29 +2366,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mixed_tense</t>
+          <t>generating_quiz</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Generating your quiz…</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Generando tu cuestionario…</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mixte</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Dropdown option meaning vary tense freely</t>
-        </is>
-      </c>
+          <t>Génération de ton quiz…</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2392,29 +2399,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>flip_toggle_label</t>
+          <t>target_my_mistakes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Flip: translate {target} → {source}</t>
+          <t>Target My Mistakes</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Invertir: traducir de {target} a {source}</t>
+          <t>Enfocarme en mis errores</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inverser : traduire de {target} vers {source}</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Template — language names not translated here</t>
-        </is>
-      </c>
+          <t>Cibler mes erreurs</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2429,22 +2432,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>generating_quiz</t>
+          <t>generate_similar_quiz</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Generating your quiz…</t>
+          <t>Generate Similar Quiz</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Generando tu cuestionario…</t>
+          <t>Generar cuestionario similar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Génération de ton quiz…</t>
+          <t>Générer un quiz similaire</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2462,22 +2465,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>target_my_mistakes</t>
+          <t>error_generating_quiz</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Target My Mistakes</t>
+          <t>Something went wrong generating your quiz.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Enfocarme en mis errores</t>
+          <t>Algo salió mal al generar tu cuestionario.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cibler mes erreurs</t>
+          <t>Une erreur s'est produite lors de la génération de ton quiz.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2490,27 +2493,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>generate-quiz.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>generate_similar_quiz</t>
+          <t>my_lists_title</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Generate Similar Quiz</t>
+          <t>My Lists</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Generar cuestionario similar</t>
+          <t>Mis listas</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Générer un quiz similaire</t>
+          <t>Mes listes</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2523,27 +2526,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>generate-quiz.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>error_generating_quiz</t>
+          <t>no_saved_lists</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Something went wrong generating your quiz.</t>
+          <t>No saved lists yet.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Algo salió mal al generar tu cuestionario.</t>
+          <t>Aún no tienes listas guardadas.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la génération de ton quiz.</t>
+          <t>Aucune liste enregistrée pour l'instant.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -2561,25 +2564,29 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>my_lists_title</t>
+          <t>progress_link</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>My Lists</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mis listas</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mes listes</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Progrès</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Row action label</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2594,22 +2601,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>no_saved_lists</t>
+          <t>delete_list_alert_title</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No saved lists yet.</t>
+          <t>Delete List</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aún no tienes listas guardadas.</t>
+          <t>Eliminar lista</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aucune liste enregistrée pour l'instant.</t>
+          <t>Supprimer la liste</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -2627,27 +2634,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>progress_link</t>
+          <t>delete_list_confirm</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Delete "{name}"? This can't be undone.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>¿Eliminar "{name}"? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Progrès</t>
+          <t>Supprimer « {name} » ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Row action label</t>
+          <t>Template</t>
         </is>
       </c>
     </row>
@@ -2664,22 +2671,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>delete_list_alert_title</t>
+          <t>error_loading_lists</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Delete List</t>
+          <t>Something went wrong loading your lists.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eliminar lista</t>
+          <t>Algo salió mal al cargar tus listas.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Supprimer la liste</t>
+          <t>Une erreur s'est produite lors du chargement de tes listes.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2697,29 +2704,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>delete_list_confirm</t>
+          <t>error_loading_list</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Delete "{name}"? This can't be undone.</t>
+          <t>Something went wrong loading that list.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>¿Eliminar "{name}"? Esta acción no se puede deshacer.</t>
+          <t>Algo salió mal al cargar esa lista.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Supprimer « {name} » ? Cette action est irréversible.</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du chargement de cette liste.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2734,22 +2737,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>error_loading_lists</t>
+          <t>error_deleting_list</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Something went wrong loading your lists.</t>
+          <t>Something went wrong deleting that list.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar tus listas.</t>
+          <t>Algo salió mal al eliminar esa lista.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement de tes listes.</t>
+          <t>Une erreur s'est produite lors de la suppression de cette liste.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2762,27 +2765,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>error_loading_list</t>
+          <t>my_quizzes_title</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Something went wrong loading that list.</t>
+          <t>My Quizzes</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar esa lista.</t>
+          <t>Mis cuestionarios</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement de cette liste.</t>
+          <t>Mes quiz</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2795,27 +2798,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>error_deleting_list</t>
+          <t>no_quizzes_in_progress</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Something went wrong deleting that list.</t>
+          <t>No quizzes in progress.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esa lista.</t>
+          <t>No hay cuestionarios en curso.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de cette liste.</t>
+          <t>Aucun quiz en cours.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2833,22 +2836,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>my_quizzes_title</t>
+          <t>quiz_in_progress_fallback</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>My Quizzes</t>
+          <t>Quiz in progress</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mis cuestionarios</t>
+          <t>Cuestionario en curso</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mes quiz</t>
+          <t>Quiz en cours</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2866,25 +2869,29 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>no_quizzes_in_progress</t>
+          <t>question_n_of_total</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No quizzes in progress.</t>
+          <t>Question {n} of {total}</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>No hay cuestionarios en curso.</t>
+          <t>Pregunta {n} de {total}</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aucun quiz en cours.</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Question {n} sur {total}</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Template — also used in quiz.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2899,22 +2906,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>quiz_in_progress_fallback</t>
+          <t>delete_quiz_alert_title</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Quiz in progress</t>
+          <t>Delete Quiz</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cuestionario en curso</t>
+          <t>Eliminar cuestionario</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Quiz en cours</t>
+          <t>Supprimer le quiz</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2932,27 +2939,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>question_n_of_total</t>
+          <t>delete_quiz_confirm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Question {n} of {total}</t>
+          <t>Delete this quiz for "{name}"? This can't be undone.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pregunta {n} de {total}</t>
+          <t>¿Eliminar este cuestionario de "{name}"? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Question {n} sur {total}</t>
+          <t>Supprimer ce quiz pour « {name} » ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Template — also used in quiz.tsx</t>
+          <t>Template</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2976,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>delete_quiz_alert_title</t>
+          <t>error_loading_quizzes</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Delete Quiz</t>
+          <t>Something went wrong loading your quizzes.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eliminar cuestionario</t>
+          <t>Algo salió mal al cargar tus cuestionarios.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Supprimer le quiz</t>
+          <t>Une erreur s'est produite lors du chargement de tes quiz.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -3002,29 +3009,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>delete_quiz_confirm</t>
+          <t>error_deleting_quiz</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Delete this quiz for "{name}"? This can't be undone.</t>
+          <t>Something went wrong deleting that quiz.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>¿Eliminar este cuestionario de "{name}"? Esta acción no se puede deshacer.</t>
+          <t>Algo salió mal al eliminar ese cuestionario.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Supprimer ce quiz pour « {name} » ? Cette action est irréversible.</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de la suppression de ce quiz.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3034,30 +3037,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>list-history.tsx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>error_loading_quizzes</t>
+          <t>progress_title</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Something went wrong loading your quizzes.</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar tus cuestionarios.</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement de tes quiz.</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>Progrès</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Title fallback + subtitle label</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3067,27 +3074,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>list-history.tsx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>error_deleting_quiz</t>
+          <t>no_completed_quizzes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Something went wrong deleting that quiz.</t>
+          <t>No completed quizzes for this list yet.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar ese cuestionario.</t>
+          <t>Aún no hay cuestionarios completados.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ce quiz.</t>
+          <t>Aucun quiz terminé pour l'instant.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -3105,27 +3112,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>progress_title</t>
+          <t>score_fraction_pct</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>{correct}/{total} ({pct}%)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>{correct}/{total} ({pct}%)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Progrès</t>
+          <t>{correct}/{total} ({pct} %)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Title fallback + subtitle label</t>
+          <t>Number formatting conventions vary by locale</t>
         </is>
       </c>
     </row>
@@ -3142,22 +3149,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>no_completed_quizzes</t>
+          <t>error_loading_history</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No completed quizzes for this list yet.</t>
+          <t>Something went wrong loading quiz history.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aún no hay cuestionarios completados.</t>
+          <t>Algo salió mal al cargar el historial del cuestionario.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aucun quiz terminé pour l'instant.</t>
+          <t>Une erreur s'est produite lors du chargement de l'historique du quiz.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -3170,34 +3177,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>list-history.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>score_fraction_pct</t>
+          <t>settings_title</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{correct}/{total} ({pct}%)</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>{correct}/{total} ({pct}%)</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{correct}/{total} ({pct} %)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Number formatting conventions vary by locale</t>
-        </is>
-      </c>
+          <t>Paramètres</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3207,27 +3210,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>list-history.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>error_loading_history</t>
+          <t>default_level_hint</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Something went wrong loading quiz history.</t>
+          <t>Default level for new quizzes — you can still change it for any single quiz when generating it.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar el historial del cuestionario.</t>
+          <t>Nivel predeterminado para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement de l'historique du quiz.</t>
+          <t>Niveau par défaut pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3245,22 +3248,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>settings_title</t>
+          <t>auto_delete_toggle</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Auto-delete completed quizzes after 30 days</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Eliminar automáticamente los cuestionarios completados después de 30 días</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paramètres</t>
+          <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -3278,22 +3281,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>default_level_hint</t>
+          <t>adaptive_quizzes_toggle</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Default level for new quizzes — you can still change it for any single quiz when generating it.</t>
+          <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nivel predeterminado para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
+          <t>Cuestionarios adaptativos — comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Niveau par défaut pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
+          <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3306,27 +3309,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>quiz.tsx</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>auto_delete_toggle</t>
+          <t>your_answer_placeholder</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Auto-delete completed quizzes after 30 days</t>
+          <t>Your answer</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eliminar automáticamente los cuestionarios completados después de 30 días</t>
+          <t>Tu respuesta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
+          <t>Ta réponse</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3339,27 +3342,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>quiz.tsx</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_toggle</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cuestionarios adaptativos — comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+          <t>Enviar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+          <t>Valider</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3377,22 +3380,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>your_answer_placeholder</t>
+          <t>skip_question</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Your answer</t>
+          <t>Skip this question</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tu respuesta</t>
+          <t>Saltar esta pregunta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ta réponse</t>
+          <t>Passer cette question</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3410,22 +3413,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>hide_word_list</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Hide word list</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Enviar</t>
+          <t>Ocultar lista de palabras</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Valider</t>
+          <t>Masquer la liste de mots</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -3443,22 +3446,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>skip_question</t>
+          <t>stuck_see_word_list</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Skip this question</t>
+          <t>Stuck? See the word list</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saltar esta pregunta</t>
+          <t>¿Atascado? Consulta la lista de palabras</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Passer cette question</t>
+          <t>Bloqué ? Consulte la liste de mots</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -3476,25 +3479,29 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>hide_word_list</t>
+          <t>your_answer_was</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Hide word list</t>
+          <t>Your answer: {answer}</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ocultar lista de palabras</t>
+          <t>Tu respuesta: {answer}</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Masquer la liste de mots</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>Ta réponse : {answer}</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3509,22 +3516,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>stuck_see_word_list</t>
+          <t>correct_feedback</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Stuck? See the word list</t>
+          <t>That's correct!</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>¿Atascado? Consulta la lista de palabras</t>
+          <t>¡Correcto!</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bloqué ? Consulte la liste de mots</t>
+          <t>C'est correct !</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3542,22 +3549,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>your_answer_was</t>
+          <t>incorrect_feedback</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Your answer: {answer}</t>
+          <t>Sorry, that's incorrect. The answer was: {answer}</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tu respuesta: {answer}</t>
+          <t>Lo siento, es incorrecto. La respuesta era: {answer}</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ta réponse : {answer}</t>
+          <t>Désolé, c'est incorrect. La réponse était : {answer}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3579,22 +3586,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>correct_feedback</t>
+          <t>finish_quiz</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>That's correct!</t>
+          <t>Finish Quiz</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>¡Correcto!</t>
+          <t>Finalizar cuestionario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C'est correct !</t>
+          <t>Terminer le quiz</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -3612,29 +3619,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>incorrect_feedback</t>
+          <t>next_question</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sorry, that's incorrect. The answer was: {answer}</t>
+          <t>Next Question</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lo siento, es incorrecto. La respuesta era: {answer}</t>
+          <t>Siguiente pregunta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Désolé, c'est incorrect. La réponse était : {answer}</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Question suivante</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3644,27 +3647,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>quiz.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>finish_quiz</t>
+          <t>quiz_complete_title</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Finish Quiz</t>
+          <t>Quiz Complete!</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finalizar cuestionario</t>
+          <t>¡Cuestionario completado!</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Terminer le quiz</t>
+          <t>Quiz terminé !</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -3677,30 +3680,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>quiz.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>next_question</t>
+          <t>score_correct</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Next Question</t>
+          <t>{n} / {total} correct</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Siguiente pregunta</t>
+          <t>{n} / {total} correctas</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Question suivante</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>{n} / {total} correctes</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3715,22 +3722,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>quiz_complete_title</t>
+          <t>back_to_home</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Quiz Complete!</t>
+          <t>Back to Home</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>¡Cuestionario completado!</t>
+          <t>Volver al inicio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Quiz terminé !</t>
+          <t>Retour à l'accueil</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -3743,34 +3750,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>score_correct</t>
+          <t>undo_last</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{n} / {total} correct</t>
+          <t>Undo last</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>{n} / {total} correctas</t>
+          <t>Deshacer última</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{n} / {total} correctes</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Annuler le dernier</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3780,27 +3783,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>back_to_home</t>
+          <t>clear_list</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Back to Home</t>
+          <t>Clear list</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Volver al inicio</t>
+          <t>Vaciar lista</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Retour à l'accueil</t>
+          <t>Vider la liste</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -3818,22 +3821,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>undo_last</t>
+          <t>no_words_added</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Undo last</t>
+          <t>No words added yet.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deshacer última</t>
+          <t>Aún no has añadido palabras.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Annuler le dernier</t>
+          <t>Aucun mot ajouté pour l'instant.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -3851,22 +3854,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>clear_list</t>
+          <t>list_name_update_placeholder</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Clear list</t>
+          <t>List name (saving updates it)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vaciar lista</t>
+          <t>Nombre de la lista (al guardar se actualiza)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vider la liste</t>
+          <t>Nom de la liste (l'enregistrement la met à jour)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -3884,22 +3887,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>no_words_added</t>
+          <t>list_name_placeholder</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>No words added yet.</t>
+          <t>List name</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aún no has añadido palabras.</t>
+          <t>Nombre de la lista</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Aucun mot ajouté pour l'instant.</t>
+          <t>Nom de la liste</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -3917,22 +3920,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>list_name_update_placeholder</t>
+          <t>saving_ellipsis</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>List name (saving updates it)</t>
+          <t>Saving…</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nombre de la lista (al guardar se actualiza)</t>
+          <t>Guardando…</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nom de la liste (l'enregistrement la met à jour)</t>
+          <t>Enregistrement…</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -3950,22 +3953,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>list_name_placeholder</t>
+          <t>save_list</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>List name</t>
+          <t>Save List</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nombre de la lista</t>
+          <t>Guardar lista</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nom de la liste</t>
+          <t>Enregistrer la liste</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -3983,22 +3986,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>saving_ellipsis</t>
+          <t>saved_message</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Saving…</t>
+          <t>Saved!</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Guardando…</t>
+          <t>¡Guardado!</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Enregistrement…</t>
+          <t>Enregistré !</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -4016,22 +4019,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>save_list</t>
+          <t>error_saving</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Save List</t>
+          <t>Something went wrong saving.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Guardar lista</t>
+          <t>Algo salió mal al guardar.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Enregistrer la liste</t>
+          <t>Une erreur s'est produite lors de l'enregistrement.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -4049,25 +4052,29 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>saved_message</t>
+          <t>add_more_words_to_quiz</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Saved!</t>
+          <t>Add {n} more word(s) to generate a quiz</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>¡Guardado!</t>
+          <t>Añade {n} palabra(s) más para generar un cuestionario</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Enregistré !</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
+          <t>Ajoute {n} mot(s) de plus pour générer un quiz</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Template with pluralization</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4082,25 +4089,29 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>error_saving</t>
+          <t>generate_quiz_button</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Something went wrong saving.</t>
+          <t>Generate Quiz</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Algo salió mal al guardar.</t>
+          <t>Generar cuestionario</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'enregistrement.</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
+          <t>Générer un quiz</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Reused label</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4115,27 +4126,27 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>add_more_words_to_quiz</t>
+          <t>my_lists_link</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Add {n} more word(s) to generate a quiz</t>
+          <t>My Lists</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Añade {n} palabra(s) más para generar un cuestionario</t>
+          <t>Mis listas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ajoute {n} mot(s) de plus pour générer un quiz</t>
+          <t>Mes listes</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Template with pluralization</t>
+          <t>Reused label</t>
         </is>
       </c>
     </row>
@@ -4147,32 +4158,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>generate_quiz_button</t>
+          <t>level_label</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Generate Quiz</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Generar cuestionario</t>
+          <t>Nivel</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Générer un quiz</t>
+          <t>Niveau</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Reused label</t>
+          <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
         </is>
       </c>
     </row>
@@ -4184,32 +4195,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>language-picker.tsx</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>my_lists_link</t>
+          <t>from_label</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>My Lists</t>
+          <t>From</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mis listas</t>
+          <t>Desde</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mes listes</t>
+          <t>Depuis</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Reused label</t>
+          <t>Replaces "I already know" — short label translates cleanly, standard in translation-app pickers (Google Translate, Duolingo-style)</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4232,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>language-picker.tsx</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>level_label</t>
+          <t>to_label</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>To</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nivel</t>
+          <t>Hacia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Niveau</t>
+          <t>Vers</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
+          <t>Replaces "I'm learning" — same reasoning</t>
         </is>
       </c>
     </row>
@@ -4263,27 +4274,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>from_label</t>
+          <t>language_names</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Desde</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Depuis</t>
-        </is>
-      </c>
+          <t>English / Spanish / French</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Replaces "I already know" — short label translates cleanly, standard in translation-app pickers (Google Translate, Duolingo-style)</t>
+          <t>Design decision: show in UI language or always native form (Español, Français)?</t>
         </is>
       </c>
     </row>
@@ -4295,32 +4298,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>language-picker.tsx</t>
+          <t>parsing-warning.tsx</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>to_label</t>
+          <t>parsing_warning_text</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>To</t>
+          <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hacia</t>
+          <t>El análisis puede cometer errores con formatos inusuales. Para mejores resultados, prueba subir una foto en su lugar.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vers</t>
+          <t>L'analyse peut faire des erreurs avec une mise en forme inhabituelle. Pour de meilleurs résultats, essaie plutôt d'importer une photo.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Replaces "I'm learning" — same reasoning</t>
+          <t>Contains an inline link to Share a Picture</t>
         </is>
       </c>
     </row>
@@ -4332,24 +4335,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>language-picker.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>language_names</t>
+          <t>trend_improving_a_lot</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>English / Spanish / French</t>
+          <t>5 message variants — 'Great progress! Your scores are climbing fast...' etc.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Design decision: show in UI language or always native form (Español, Français)?</t>
+          <t>See file directly, too long to list individually</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4364,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>parsing-warning.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>parsing_warning_text</t>
+          <t>trend_improving</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>El análisis puede cometer errores con formatos inusuales. Para mejores resultados, prueba subir una foto en su lugar.</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>L'analyse peut faire des erreurs avec une mise en forme inhabituelle. Pour de meilleurs résultats, essaie plutôt d'importer une photo.</t>
-        </is>
-      </c>
+          <t>5 message variants — 'You're improving steadily on this list.' etc.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Contains an inline link to Share a Picture</t>
+          <t>See file directly</t>
         </is>
       </c>
     </row>
@@ -4403,19 +4398,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot</t>
+          <t>trend_steady</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5 message variants — 'Great progress! Your scores are climbing fast...' etc.</t>
+          <t>5 message variants — 'Your scores are holding steady...' etc.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>See file directly, too long to list individually</t>
+          <t>See file directly</t>
         </is>
       </c>
     </row>
@@ -4432,12 +4427,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>trend_improving</t>
+          <t>trend_declining</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5 message variants — 'You're improving steadily on this list.' etc.</t>
+          <t>5 message variants — 'Your scores dipped a bit recently...' etc.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4461,12 +4456,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>trend_steady</t>
+          <t>trend_declining_a_lot</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5 message variants — 'Your scores are holding steady...' etc.</t>
+          <t>5 message variants — 'Your scores dropped noticeably...' etc.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4485,24 +4480,24 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>quiz-feedback.ts</t>
+          <t>backend (api errors)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>trend_declining</t>
+          <t>backend_error_text</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5 message variants — 'Your scores dipped a bit recently...' etc.</t>
+          <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>See file directly</t>
+          <t>Needs its own translation strategy — see Notes tab</t>
         </is>
       </c>
     </row>
@@ -4514,26 +4509,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>quiz-feedback.ts</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot</t>
+          <t>sample_lists_title</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5 message variants — 'Your scores dropped noticeably...' etc.</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>See file directly</t>
-        </is>
-      </c>
+          <t>Sample Lists</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Listas de ejemplo</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Listes types</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4543,26 +4542,30 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>backend (api errors)</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>backend_error_text</t>
+          <t>sample_lists_hint</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Needs its own translation strategy — see Notes tab</t>
-        </is>
-      </c>
+          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4577,25 +4580,29 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sample_lists_title</t>
+          <t>sample_list_name_template</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sample Lists</t>
+          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Listas de ejemplo</t>
+          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Listes types</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Template — used as both display label and saved list name</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4610,25 +4617,29 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>sample_lists_hint</t>
+          <t>sample_list_type_vocab</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
+          <t>Vocab</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
+          <t>Vocabulario</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
+          <t>Vocabulaire</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Reused label under each sample list row</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4643,27 +4654,27 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>sample_list_name_template</t>
+          <t>sample_list_type_verbs</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
+          <t>Verbs</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
+          <t>Verbos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
+          <t>Verbes</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Template — used as both display label and saved list name</t>
+          <t>Reused label under each sample list row</t>
         </is>
       </c>
     </row>
@@ -4680,29 +4691,25 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>sample_list_type_vocab</t>
+          <t>sample_list_add</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Añadir</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Reused label under each sample list row</t>
-        </is>
-      </c>
+          <t>Ajouter</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4717,29 +4724,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>sample_list_type_verbs</t>
+          <t>sample_list_adding</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Verbs</t>
+          <t>Adding…</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Verbos</t>
+          <t>Añadiendo…</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Verbes</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Reused label under each sample list row</t>
-        </is>
-      </c>
+          <t>Ajout en cours…</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4754,25 +4757,29 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>sample_list_add</t>
+          <t>sample_list_added</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Añadir</t>
+          <t>Añadido</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ajouter</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr"/>
+          <t>Ajouté</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4787,22 +4794,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>sample_list_adding</t>
+          <t>error_adding_sample</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Adding…</t>
+          <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Añadiendo…</t>
+          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ajout en cours…</t>
+          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -4815,34 +4822,30 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>sample_list_added</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Añadido</t>
+          <t>Omitir</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ajouté</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
-        </is>
-      </c>
+          <t>Passer</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4852,27 +4855,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>error_adding_sample</t>
+          <t>back</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Something went wrong adding that sample list.</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+          <t>Retour</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -4890,22 +4893,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Omitir</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Passer</t>
+          <t>Suivant</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -4923,22 +4926,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>get_started</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Get Started</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Empezar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Retour</t>
+          <t>Commencer</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -4956,22 +4959,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>slide1_headline</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Build Your List</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Crea tu lista</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Suivant</t>
+          <t>Crée ta liste</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -4989,22 +4992,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>get_started</t>
+          <t>slide1_body</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Get Started</t>
+          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Empezar</t>
+          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Commencer</t>
+          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -5022,22 +5025,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>slide1_headline</t>
+          <t>slide2_headline</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Build Your List</t>
+          <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Crea tu lista</t>
+          <t>Practica con cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Crée ta liste</t>
+          <t>Entraîne-toi avec des quiz adaptatifs</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -5055,22 +5058,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>slide1_body</t>
+          <t>slide2_body</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5088,22 +5091,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>slide2_headline</t>
+          <t>slide3_headline</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Practice With Adaptive Quizzes</t>
+          <t>Watch Your Progress</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Practica con cuestionarios adaptativos</t>
+          <t>Observa tu progreso</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Entraîne-toi avec des quiz adaptatifs</t>
+          <t>Suis ta progression</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -5121,22 +5124,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>slide2_body</t>
+          <t>slide3_body</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
+          <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
+          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
+          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -5149,30 +5152,34 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>slide3_headline</t>
+          <t>about_langreps_link</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Watch Your Progress</t>
+          <t>About LangReps</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Observa tu progreso</t>
+          <t>Acerca de LangReps</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Suis ta progression</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
+          <t>À propos de LangReps</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Links to /onboarding to replay it manually</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5182,27 +5189,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>slide3_body</t>
+          <t>sort_by_label</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>See your scores improve over time, list by list.</t>
+          <t>Sort by</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
+          <t>Ordenar por</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
+          <t>Trier par</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5215,34 +5222,30 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>about_langreps_link</t>
+          <t>sort_by_date</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>About LangReps</t>
+          <t>Last Uploaded</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Acerca de LangReps</t>
+          <t>Última subida</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>À propos de LangReps</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Links to /onboarding to replay it manually</t>
-        </is>
-      </c>
+          <t>Dernier import</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5257,22 +5260,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>sort_by_label</t>
+          <t>sort_by_name</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ordenar por</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Trier par</t>
+          <t>Nom</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -5290,25 +5293,29 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>sort_by_date</t>
+          <t>last_uploaded_template</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Last Uploaded</t>
+          <t>Last uploaded: {date}</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Última subida</t>
+          <t>Última subida: {date}</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dernier import</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
+          <t>Dernier import : {date}</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5323,25 +5330,29 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sort_by_name</t>
+          <t>sample_list_name_template_v2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
+          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Superseded template — replaces the old arrow-notation naming</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5356,27 +5367,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>last_uploaded_template</t>
+          <t>sample_list_card_title</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Last uploaded: {date}</t>
+          <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Última subida: {date}</t>
+          <t>Vocabulario {count} / Verbo {count}</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dernier import : {date}</t>
+          <t>Vocabulaire {count} / Verbe {count}</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Sample-list catalog card title, replaces the old full name display</t>
         </is>
       </c>
     </row>
@@ -5393,27 +5404,27 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>sample_list_name_template_v2</t>
+          <t>sample_list_card_flags</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Superseded template — replaces the old arrow-notation naming</t>
+          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
     </row>
@@ -5425,34 +5436,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>index.tsx</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>sample_list_card_title</t>
+          <t>signup_incentive_hint</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Vocab {count} / Verb {count}</t>
+          <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vocabulario {count} / Verbo {count}</t>
+          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vocabulaire {count} / Verbe {count}</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Sample-list catalog card title, replaces the old full name display</t>
-        </is>
-      </c>
+          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5462,32 +5469,32 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>sample_list_card_flags</t>
+          <t>default_level_title</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Default Level</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Nivel predeterminado</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Niveau par défaut</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
+          <t>New section title for Settings redesign (bold title + description layout)</t>
         </is>
       </c>
     </row>
@@ -5499,30 +5506,34 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>index.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>signup_incentive_hint</t>
+          <t>auto_delete_title</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Sign up to save your lists and track your progress over time</t>
+          <t>Auto-Delete Old Quizzes</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
+          <t>Eliminar automáticamente cuestionarios antiguos</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr"/>
+          <t>Suppression automatique des anciens quiz</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>New section title</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5537,27 +5548,27 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>default_level_title</t>
+          <t>auto_delete_desc</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Default Level</t>
+          <t>Completed quizzes are removed after 30 days</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nivel predeterminado</t>
+          <t>Los cuestionarios completados se eliminan después de 30 días</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Niveau par défaut</t>
+          <t>Les quiz terminés sont supprimés après 30 jours</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>New section title for Settings redesign (bold title + description layout)</t>
+          <t>Description moved under the bold title</t>
         </is>
       </c>
     </row>
@@ -5574,22 +5585,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>auto_delete_title</t>
+          <t>adaptive_quizzes_title</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Auto-Delete Old Quizzes</t>
+          <t>Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Eliminar automáticamente cuestionarios antiguos</t>
+          <t>Cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Suppression automatique des anciens quiz</t>
+          <t>Quiz adaptatifs</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5611,22 +5622,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>auto_delete_desc</t>
+          <t>adaptive_quizzes_desc</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Completed quizzes are removed after 30 days</t>
+          <t>Get feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Los cuestionarios completados se eliminan después de 30 días</t>
+          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Les quiz terminés sont supprimés après 30 jours</t>
+          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5648,27 +5659,27 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_title</t>
+          <t>require_accents_title</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Adaptive Quizzes</t>
+          <t>Require Diacritics</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cuestionarios adaptativos</t>
+          <t>Exigir diacríticos</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Quiz adaptatifs</t>
+          <t>Exiger les diacritiques</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>New section title</t>
+          <t>New toggle — renamed from "Require Accents"</t>
         </is>
       </c>
     </row>
@@ -5685,27 +5696,27 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_desc</t>
+          <t>require_accents_desc</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Get feedback on patterns you struggle with, and an option to target them</t>
+          <t>Off accepts "cafe" for "café"</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+          <t>Desactivado acepta "cafe" en lugar de "café"</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+          <t>Désactivé accepte "cafe" pour "café"</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Description moved under the bold title</t>
+          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5728,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>require_accents_title</t>
+          <t>your_lists_section_title</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Require Diacritics</t>
+          <t>Your Lists</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Exigir diacríticos</t>
+          <t>Tus listas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Exiger les diacritiques</t>
+          <t>Tes listes</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>New toggle — renamed from "Require Accents"</t>
+          <t>New section title alongside bulk-select controls</t>
         </is>
       </c>
     </row>
@@ -5754,32 +5765,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>require_accents_desc</t>
+          <t>bulk_select_toggle</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Off accepts "cafe" for "café"</t>
+          <t>Select / Done</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Desactivado acepta "cafe" en lugar de "café"</t>
+          <t>Seleccionar / Listo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Désactivé accepte "cafe" pour "café"</t>
+          <t>Sélectionner / Terminé</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
+          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
         </is>
       </c>
     </row>
@@ -5796,27 +5807,32 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>your_lists_section_title</t>
+          <t>bulk_select_all</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Your Lists</t>
+          <t>Select All / Deselect All</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tus listas</t>
+          <t>Seleccionar todo / Deseleccionar todo</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tes listes</t>
+          <t>Tout sélectionner / Tout désélectionner</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>New section title alongside bulk-select controls</t>
+          <t>Shared pattern</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -5833,27 +5849,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>bulk_select_toggle</t>
+          <t>bulk_delete_selected_template</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Select / Done</t>
+          <t>Delete ({count})</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Seleccionar / Listo</t>
+          <t>Eliminar ({count})</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sélectionner / Terminé</t>
+          <t>Supprimer ({count})</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
+          <t>Shared pattern</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -5870,22 +5891,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>bulk_select_all</t>
+          <t>bulk_deleting</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Select All / Deselect All</t>
+          <t>Deleting…</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Seleccionar todo / Deseleccionar todo</t>
+          <t>Eliminando…</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tout sélectionner / Tout désélectionner</t>
+          <t>Suppression…</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5912,34 +5933,25 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>bulk_delete_selected_template</t>
+          <t>bulk_delete_lists_alert_title</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Delete ({count})</t>
+          <t>Delete Lists</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Eliminar ({count})</t>
+          <t>Eliminar listas</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Supprimer ({count})</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Shared pattern</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Supprimer les listes</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5954,34 +5966,25 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>bulk_deleting</t>
+          <t>bulk_delete_lists_alert_message_template</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Deleting…</t>
+          <t>Delete {count} list(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Eliminando…</t>
+          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Suppression…</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Shared pattern</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5991,27 +5994,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_title</t>
+          <t>quizzes_in_progress_count_template</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Delete Lists</t>
+          <t>{count} in progress</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Eliminar listas</t>
+          <t>{count} en curso</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Supprimer les listes</t>
+          <t>{count} en cours</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -6024,27 +6027,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_message_template</t>
+          <t>bulk_delete_quizzes_alert_title</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Delete {count} list(s)? This can't be undone.</t>
+          <t>Delete Quizzes</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
+          <t>Eliminar cuestionarios</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+          <t>Supprimer les quiz</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -6062,22 +6065,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>quizzes_in_progress_count_template</t>
+          <t>bulk_delete_quizzes_alert_message_template</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{count} in progress</t>
+          <t>Delete {count} quiz(zes)? This can't be undone.</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>{count} en curso</t>
+          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>{count} en cours</t>
+          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -6095,25 +6098,29 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_title</t>
+          <t>sort_by_last_updated</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Delete Quizzes</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Eliminar cuestionarios</t>
+          <t>Última actualización</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Supprimer les quiz</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>Dernière mise à jour</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6128,25 +6135,29 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_message_template</t>
+          <t>last_updated_template</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Delete {count} quiz(zes)? This can't be undone.</t>
+          <t>Last updated: {date}</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
+          <t>Última actualización: {date}</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr"/>
+          <t>Dernière mise à jour : {date}</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6161,27 +6172,27 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>sort_by_last_updated</t>
+          <t>quiz_type_badge_vocab</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Last Updated</t>
+          <t>Vocab</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Última actualización</t>
+          <t>Vocabulario</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dernière mise à jour</t>
+          <t>Vocabulaire</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
         </is>
       </c>
     </row>
@@ -6198,27 +6209,27 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>last_updated_template</t>
+          <t>quiz_type_badge_verb</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Last updated: {date}</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Última actualización: {date}</t>
+          <t>Verbo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dernière mise à jour : {date}</t>
+          <t>Verbe</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Small badge next to the quiz row title</t>
         </is>
       </c>
     </row>
@@ -6230,32 +6241,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>quiz_type_badge_vocab</t>
+          <t>canned_feedback_mastery</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
+          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
+          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6278,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>quiz_type_badge_verb</t>
+          <t>canned_feedback_solid</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Verbo</t>
+          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Verbe</t>
+          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title</t>
+          <t>70-89% correct</t>
         </is>
       </c>
     </row>
@@ -6309,27 +6320,27 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>canned_feedback_mastery</t>
+          <t>canned_feedback_building</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
+          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
+          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
+          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
+          <t>40-69% correct</t>
         </is>
       </c>
     </row>
@@ -6346,27 +6357,27 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>canned_feedback_solid</t>
+          <t>canned_feedback_struggling</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
+          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
+          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
+          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>70-89% correct</t>
+          <t>Below 40% correct</t>
         </is>
       </c>
     </row>
@@ -6378,32 +6389,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>canned_feedback_building</t>
+          <t>cefr_info_alert_title</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
+          <t>CEFR Levels</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
+          <t>Niveles del MCER</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
+          <t>Niveaux du CECR</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>40-69% correct</t>
+          <t>Alert title triggered by new info icon next to the Level label</t>
         </is>
       </c>
     </row>
@@ -6415,34 +6426,30 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>canned_feedback_struggling</t>
+          <t>cefr_a1_explanation</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
+          <t>Breakthrough — basic words and phrases for everyday needs.</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
+          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Below 40% correct</t>
-        </is>
-      </c>
+          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6457,29 +6464,25 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>cefr_info_alert_title</t>
+          <t>cefr_a2_explanation</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>CEFR Levels</t>
+          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Niveles del MCER</t>
+          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Niveaux du CECR</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Alert title triggered by new info icon next to the Level label</t>
-        </is>
-      </c>
+          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6494,22 +6497,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>cefr_a1_explanation</t>
+          <t>cefr_b1_explanation</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Breakthrough — basic words and phrases for everyday needs.</t>
+          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
+          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
@@ -6527,22 +6530,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>cefr_a2_explanation</t>
+          <t>cefr_b2_explanation</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
+          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
+          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -6560,22 +6563,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>cefr_b1_explanation</t>
+          <t>cefr_c1_explanation</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
+          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
+          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
+          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
@@ -6593,22 +6596,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>cefr_b2_explanation</t>
+          <t>cefr_c2_explanation</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
+          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
+          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
+          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -6621,30 +6624,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>cefr_c1_explanation</t>
+          <t>splash_title</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr"/>
+          <t>LangReps</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6654,27 +6653,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>cefr_c2_explanation</t>
+          <t>splash_tagline</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
+          <t>Language reps that stick.</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
+          <t>Repeticiones de idiomas que se quedan.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
+          <t>Des répétitions de langue qui restent.</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -6692,19 +6691,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>splash_title</t>
+          <t>splash_copyright</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LangReps</t>
+          <t>© 2026 MarApps Development</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+          <t>Pinned bottom-right corner</t>
         </is>
       </c>
     </row>
@@ -6716,30 +6715,34 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>splash_tagline</t>
+          <t>see_full_results</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Language reps that stick.</t>
+          <t>See Full Results</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Repeticiones de idiomas que se quedan.</t>
+          <t>Ver resultados completos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Des répétitions de langue qui restent.</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
+          <t>Voir les résultats complets</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6749,26 +6752,30 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>splash_copyright</t>
+          <t>full_results_title</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>© 2026 MarApps Development</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Pinned bottom-right corner</t>
-        </is>
-      </c>
+          <t>Full Results</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Resultados completos</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Résultats complets</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6778,34 +6785,30 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>see_full_results</t>
+          <t>no_recorded_answers</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>See Full Results</t>
+          <t>No recorded answers for this quiz.</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ver resultados completos</t>
+          <t>No hay respuestas registradas para este cuestionario.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Voir les résultats complets</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
-        </is>
-      </c>
+          <t>Aucune réponse enregistrée pour ce quiz.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6820,22 +6823,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>full_results_title</t>
+          <t>your_answer_label</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Full Results</t>
+          <t>Your answer:</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Resultados completos</t>
+          <t>Tu respuesta:</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Résultats complets</t>
+          <t>Ta réponse :</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -6853,25 +6856,29 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>no_recorded_answers</t>
+          <t>correct_answer_label</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>No recorded answers for this quiz.</t>
+          <t>Correct answer:</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>No hay respuestas registradas para este cuestionario.</t>
+          <t>Respuesta correcta:</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Aucune réponse enregistrée pour ce quiz.</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
+          <t>Bonne réponse :</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Shown only for incorrect rows</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6886,25 +6893,29 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>your_answer_label</t>
+          <t>blank_answer_fallback</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Your answer:</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tu respuesta:</t>
+          <t>(en blanco)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ta réponse :</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr"/>
+          <t>(vide)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Shown when a skipped/empty answer was recorded</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6919,29 +6930,25 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>correct_answer_label</t>
+          <t>error_loading_results</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Correct answer:</t>
+          <t>Something went wrong loading results.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Respuesta correcta:</t>
+          <t>Algo salió mal al cargar los resultados.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bonne réponse :</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Shown only for incorrect rows</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6951,32 +6958,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>blank_answer_fallback</t>
+          <t>list_type_info_alert_title</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>List Types</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(en blanco)</t>
+          <t>Tipos de lista</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>(vide)</t>
+          <t>Types de liste</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Shown when a skipped/empty answer was recorded</t>
+          <t>New info icon next to the List type label</t>
         </is>
       </c>
     </row>
@@ -6988,27 +6995,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>error_loading_results</t>
+          <t>list_type_info_vocab</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Something went wrong loading results.</t>
+          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar los resultados.</t>
+          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
         </is>
       </c>
       <c r="G192" t="inlineStr"/>
@@ -7026,29 +7033,25 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>list_type_info_alert_title</t>
+          <t>list_type_info_verb</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>List Types</t>
+          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Tipos de lista</t>
+          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Types de liste</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>New info icon next to the List type label</t>
-        </is>
-      </c>
+          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7063,25 +7066,29 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>list_type_info_vocab</t>
+          <t>save_input_placeholder_new</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
+          <t>Name this list</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
+          <t>Nombra esta lista</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr"/>
+          <t>Nomme cette liste</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7096,25 +7103,29 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>list_type_info_verb</t>
+          <t>save_input_placeholder_update</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
+          <t>List name (updates it)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
+          <t>Nombre de la lista (la actualiza)</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+          <t>Nom de la liste (la met à jour)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Placeholder shown once the list is already saved — shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7124,32 +7135,20 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>constants/styles.ts</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>save_input_placeholder_new</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Name this list</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Nombra esta lista</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Nomme cette liste</t>
-        </is>
-      </c>
+          <t>placeholder_color_note</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
+          <t>Not a UI string — new colors.placeholder token (#8C7F63) applied via placeholderTextColor to every TextInput app-wide; RN's default placeholder gray had poor contrast on the parchment background and was nearly invisible</t>
         </is>
       </c>
     </row>
@@ -7161,32 +7160,32 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>save_input_placeholder_update</t>
+          <t>edit_list_link</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>List name (updates it)</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Nombre de la lista (la actualiza)</t>
+          <t>Editar</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nom de la liste (la met à jour)</t>
+          <t>Modifier</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Placeholder shown once the list is already saved — shortened to fit</t>
+          <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
         </is>
       </c>
     </row>
@@ -7198,20 +7197,32 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>constants/styles.ts</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>placeholder_color_note</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+          <t>remove_word_icon</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Not a UI string — new colors.placeholder token (#8C7F63) applied via placeholderTextColor to every TextInput app-wide; RN's default placeholder gray had poor contrast on the parchment background and was nearly invisible</t>
+          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
         </is>
       </c>
     </row>
@@ -7223,32 +7234,33 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>edit_list_link</t>
+          <t>translate_prompt_template</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>{n} line(s) looked like single word(s)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Editar</t>
+          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Modifier</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
+          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
         </is>
       </c>
     </row>
@@ -7260,34 +7272,30 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>remove_word_icon</t>
+          <t>translate_button</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Traducir</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
-        </is>
-      </c>
+          <t>Traduire</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7302,30 +7310,25 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>translate_prompt_template</t>
+          <t>translating_ellipsis</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>{n} line(s) looked like single word(s)</t>
+          <t>Translating…</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
+          <t>Traduciendo…</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
+          <t>Traduction en cours…</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7340,22 +7343,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>translate_button</t>
+          <t>error_translating</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Something went wrong translating those words.</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Traducir</t>
+          <t>Algo salió mal al traducir esas palabras.</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Traduire</t>
+          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
         </is>
       </c>
       <c r="G202" t="inlineStr"/>
@@ -7368,30 +7371,34 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>translating_ellipsis</t>
+          <t>slide1_body_updated</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Translating…</t>
+          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Traduciendo…</t>
+          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Traduction en cours…</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr"/>
+          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7401,30 +7408,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>error_translating</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Something went wrong translating those words.</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Algo salió mal al traducir esas palabras.</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr"/>
+          <t>saved_list_heading</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Not new text — shows the list's own saved name prominently at the top of PairsReview once saved (Edit flow especially), styled like Generate Quiz's list-name heading</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7434,32 +7433,32 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>slide1_body_updated</t>
+          <t>rename_link</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>Cambiar nombre</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+          <t>Renommer</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+          <t>New — separates renaming an already-saved list from saving its pairs</t>
         </is>
       </c>
     </row>
@@ -7476,15 +7475,27 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>saved_list_heading</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+          <t>rename_save_button</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Guardar</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Enregistrer</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Not new text — shows the list's own saved name prominently at the top of PairsReview once saved (Edit flow especially), styled like Generate Quiz's list-name heading</t>
+          <t>Inline rename confirm button</t>
         </is>
       </c>
     </row>
@@ -7501,27 +7512,27 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>rename_link</t>
+          <t>rename_cancel_button</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cambiar nombre</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Renommer</t>
+          <t>Annuler</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>New — separates renaming an already-saved list from saving its pairs</t>
+          <t>Inline rename cancel button</t>
         </is>
       </c>
     </row>
@@ -7538,29 +7549,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>rename_save_button</t>
+          <t>error_renaming</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Something went wrong renaming.</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Guardar</t>
+          <t>Algo salió mal al cambiar el nombre.</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Enregistrer</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Inline rename confirm button</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du renommage.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7575,27 +7582,27 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>rename_cancel_button</t>
+          <t>save_changes_button</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Save Changes</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Guardar cambios</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Enregistrer les modifications</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Inline rename cancel button</t>
+          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
         </is>
       </c>
     </row>
@@ -7612,25 +7619,29 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>error_renaming</t>
+          <t>list_type_locked_label</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Something went wrong renaming.</t>
+          <t>List type (locked)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Algo salió mal al cambiar el nombre.</t>
+          <t>Tipo de lista (bloqueado)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du renommage.</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr"/>
+          <t>Type de liste (verrouillé)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Appended to the label once a list is saved — type can't change after first save</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7645,27 +7656,27 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>save_changes_button</t>
+          <t>list_type_locked_explanation</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Save Changes</t>
+          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Guardar cambios</t>
+          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Enregistrer les modifications</t>
+          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
+          <t>Appended to the existing List Types info alert once locked</t>
         </is>
       </c>
     </row>
@@ -7677,32 +7688,37 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>list_type_locked_label</t>
+          <t>past_quizzes_section_title</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>List type (locked)</t>
+          <t>Past Quizzes</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Tipo de lista (bloqueado)</t>
+          <t>Cuestionarios anteriores</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Type de liste (verrouillé)</t>
+          <t>Quiz précédents</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Appended to the label once a list is saved — type can't change after first save</t>
+          <t>New section showing completed quiz history</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> fetched from GET /quiz-sessions/completed</t>
         </is>
       </c>
     </row>
@@ -7714,34 +7730,30 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>list_type_locked_explanation</t>
+          <t>no_completed_quizzes</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
+          <t>No completed quizzes yet.</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
+          <t>Aún no hay cuestionarios completados.</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Appended to the existing List Types info alert once locked</t>
-        </is>
-      </c>
+          <t>Aucun quiz terminé pour l'instant.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7756,32 +7768,27 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>past_quizzes_section_title</t>
+          <t>past_quiz_score_template</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Past Quizzes</t>
+          <t>{correct}/{total} correct ({pct}%)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Cuestionarios anteriores</t>
+          <t>{correct}/{total} correctas ({pct}%)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Quiz précédents</t>
+          <t>{correct}/{total} correctes ({pct} %)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>New section showing completed quiz history</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> fetched from GET /quiz-sessions/completed</t>
+          <t>Template</t>
         </is>
       </c>
     </row>
@@ -7798,25 +7805,29 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>no_completed_quizzes</t>
+          <t>deleted_list_fallback</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>No completed quizzes yet.</t>
+          <t>Deleted list</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aún no hay cuestionarios completados.</t>
+          <t>Lista eliminada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Aucun quiz terminé pour l'instant.</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr"/>
+          <t>Liste supprimée</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Shown when a past quiz's list no longer exists</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7826,32 +7837,32 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>past_quiz_score_template</t>
+          <t>discard_unsaved_alert_title</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>{correct}/{total} correct ({pct}%)</t>
+          <t>Discard unsaved words?</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctas ({pct}%)</t>
+          <t>¿Descartar palabras sin guardar?</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctes ({pct} %)</t>
+          <t>Abandonner les mots non enregistrés ?</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
         </is>
       </c>
     </row>
@@ -7863,34 +7874,30 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>deleted_list_fallback</t>
+          <t>discard_unsaved_alert_message</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Deleted list</t>
+          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lista eliminada</t>
+          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Liste supprimée</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Shown when a past quiz's list no longer exists</t>
-        </is>
-      </c>
+          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7905,27 +7912,27 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_title</t>
+          <t>leave_without_saving</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Discard unsaved words?</t>
+          <t>Leave Without Saving</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>¿Descartar palabras sin guardar?</t>
+          <t>Salir sin guardar</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Abandonner les mots non enregistrés ?</t>
+          <t>Quitter sans enregistrer</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
+          <t>Destructive confirm action</t>
         </is>
       </c>
     </row>
@@ -7937,30 +7944,34 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>language-order-confirm.tsx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_message</t>
+          <t>order_confirm_prompt_template</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
+          <t>Detected {first} and {second}. Which one do you already know?</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
+          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
+          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7970,32 +7981,37 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>language-order-confirm.tsx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>leave_without_saving</t>
+          <t>order_confirm_option_template</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Leave Without Saving</t>
+          <t>I know {language}</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Salir sin guardar</t>
+          <t>Ya sé {language}</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Quitter sans enregistrer</t>
+          <t>Je connais déjà {language}</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Destructive confirm action</t>
+          <t>Two buttons</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> one per detected language</t>
         </is>
       </c>
     </row>
@@ -8007,32 +8023,32 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>add-words.tsx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>order_confirm_prompt_template</t>
+          <t>source_word_placeholder_dynamic</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Detected {first} and {second}. Which one do you already know?</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
+          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
         </is>
       </c>
     </row>
@@ -8044,109 +8060,30 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>add-words.tsx</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>order_confirm_option_template</t>
+          <t>target_word_placeholder_dynamic</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>I know {language}</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ya sé {language}</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Je connais déjà {language}</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
-        <is>
-          <t>Two buttons</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> one per detected language</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>add-words.tsx</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>source_word_placeholder_dynamic</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Word in {language}</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Palabra en {language}</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Mot en {language}</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>add-words.tsx</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>target_word_placeholder_dynamic</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Word in {language}</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Palabra en {language}</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Mot en {language}</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
         <is>
           <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
         </is>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,50 +413,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>File / Component</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>English (source)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Spanish</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>French</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -469,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,7 +494,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,7 +560,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,7 +593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -634,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -667,7 +663,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -704,7 +700,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -737,7 +733,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -770,7 +766,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,7 +799,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +832,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -869,7 +865,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,7 +898,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -939,7 +935,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +972,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1013,7 +1009,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1050,7 +1046,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1087,7 +1083,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1124,7 +1120,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1157,7 +1153,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1190,7 +1186,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1223,7 +1219,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1252,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1289,7 +1285,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,7 +1318,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1351,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1384,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1421,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1454,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1491,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1524,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1561,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1602,7 +1598,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1631,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1664,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1701,7 +1697,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1734,7 +1730,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1771,7 +1767,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1804,7 +1800,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1837,7 +1833,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1874,7 +1870,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1907,7 +1903,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1940,7 +1936,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1973,7 +1969,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2006,7 +2002,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2039,7 +2035,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2072,7 +2068,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2109,7 +2105,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2146,7 +2142,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,7 +2175,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2216,7 +2212,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2249,7 +2245,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2282,7 +2278,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2319,7 +2315,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2356,7 +2352,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2389,7 +2385,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2422,7 +2418,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2455,7 +2451,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2488,7 +2484,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2521,7 +2517,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2554,7 +2550,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2591,7 +2587,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2624,7 +2620,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2661,7 +2657,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2694,7 +2690,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2727,7 +2723,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2760,7 +2756,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2793,7 +2789,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2826,7 +2822,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2859,7 +2855,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2896,7 +2892,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2929,7 +2925,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2966,7 +2962,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2999,7 +2995,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3032,7 +3028,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3069,7 +3065,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3102,7 +3098,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3139,7 +3135,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3172,7 +3168,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3205,7 +3201,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3220,25 +3216,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Default level for new quizzes — you can still change it for any single quiz when generating it.</t>
+          <t>Used for new quizzes — you can still change it for any single quiz when generating it.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nivel predeterminado para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
+          <t>Se usa para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Niveau par défaut pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>Utilisé pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Wording synced to match current app text exactly</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3304,7 +3304,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3436,7 +3436,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3539,7 +3539,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3576,7 +3576,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3609,7 +3609,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3675,7 +3675,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3712,7 +3712,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3778,7 +3778,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3811,7 +3811,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3844,7 +3844,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3943,7 +3943,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3976,7 +3976,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4042,7 +4042,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4079,7 +4079,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4116,7 +4116,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4153,7 +4153,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4227,7 +4227,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4264,7 +4264,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4279,21 +4279,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>English / Spanish / French</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+          <t>English / Español / Français</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>English / Español / Français</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>English / Español / Français</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Design decision: show in UI language or always native form (Español, Français)?</t>
+          <t>Decided: always shown in each language's own native form, regardless of current UI language (matches iOS Settings/Duolingo convention) — not translated per UI language, so all three columns are identical on purpose</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4330,7 +4338,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4340,26 +4348,34 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot</t>
+          <t>trend_improving_a_lot_1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5 message variants — 'Great progress! Your scores are climbing fast...' etc.</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>Great progress! Your scores are climbing fast — keep it up.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>¡Gran progreso! Tus puntuaciones están subiendo rápido — sigue así.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Beaux progrès ! Tes scores grimpent rapidement — continue comme ça.</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>See file directly, too long to list individually</t>
+          <t>5 message variants, picked at random each screen load</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4369,26 +4385,30 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>trend_improving</t>
+          <t>trend_improving_a_lot_2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5 message variants — 'You're improving steadily on this list.' etc.</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>See file directly</t>
-        </is>
-      </c>
+          <t>You're on a roll — your recent scores are way up from where you started.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Estás en racha — tus puntuaciones recientes están muy por encima de donde empezaste.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Tu es en pleine lancée — tes scores récents sont bien au-dessus de ton point de départ.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4398,26 +4418,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>trend_steady</t>
+          <t>trend_improving_a_lot_3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5 message variants — 'Your scores are holding steady...' etc.</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>See file directly</t>
-        </is>
-      </c>
+          <t>Big jump in your scores lately. Whatever you're doing, keep doing it.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Gran salto en tus puntuaciones últimamente. Sigue haciendo lo que estás haciendo.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Gros bond dans tes scores dernièrement. Continue comme ça, quoi que tu fasses.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4427,26 +4451,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>trend_declining</t>
+          <t>trend_improving_a_lot_4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5 message variants — 'Your scores dipped a bit recently...' etc.</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>See file directly</t>
-        </is>
-      </c>
+          <t>Your accuracy has shot up recently — this list is really clicking.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Tu precisión ha subido mucho últimamente — esta lista te está funcionando de verdad.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ta précision a beaucoup augmenté récemment — cette liste porte vraiment ses fruits.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4456,80 +4484,92 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot</t>
+          <t>trend_improving_a_lot_5</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5 message variants — 'Your scores dropped noticeably...' etc.</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>See file directly</t>
-        </is>
-      </c>
+          <t>Strong improvement here — you've clearly been putting in the reps.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Gran mejora aquí — claramente has estado practicando bastante.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Belle amélioration ici — on voit que tu t'es beaucoup entraîné.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>backend (api errors)</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>backend_error_text</t>
+          <t>trend_improving_1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+          <t>You're improving steadily on this list.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Estás mejorando de forma constante en esta lista.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Tu progresses régulièrement sur cette liste.</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Needs its own translation strategy — see Notes tab</t>
+          <t>5 message variants, picked at random each screen load</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>sample_lists_title</t>
+          <t>trend_improving_2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sample Lists</t>
+          <t>Nice — your scores are trending upward little by little.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Listas de ejemplo</t>
+          <t>Bien — tus puntuaciones van subiendo poco a poco.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Listes types</t>
+          <t>Bien joué — tes scores augmentent petit à petit.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -4537,32 +4577,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>sample_lists_hint</t>
+          <t>trend_improving_3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
+          <t>Steady gains here. Keep at it and it'll keep paying off.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
+          <t>Avances constantes aquí. Sigue así y seguirá dando resultado.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
+          <t>Des progrès constants ici. Continue et ça continuera à payer.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -4570,143 +4610,135 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sample_list_name_template</t>
+          <t>trend_improving_4</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
+          <t>You're getting a bit better each time you quiz this list.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
+          <t>Vas mejorando un poco cada vez que haces el cuestionario de esta lista.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Template — used as both display label and saved list name</t>
-        </is>
-      </c>
+          <t>Tu t'améliores un peu à chaque fois que tu fais le quiz sur cette liste.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>sample_list_type_vocab</t>
+          <t>trend_improving_5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>Solid upward trend — the practice is paying off.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Tendencia claramente positiva — la práctica está dando resultado.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Reused label under each sample list row</t>
-        </is>
-      </c>
+          <t>Tendance clairement à la hausse — l'entraînement porte ses fruits.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>sample_list_type_verbs</t>
+          <t>trend_steady_1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Verbs</t>
+          <t>Your scores are holding steady. Try focusing on the words you keep missing.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Verbos</t>
+          <t>Tus puntuaciones se mantienen estables. Intenta enfocarte en las palabras que sigues fallando.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Verbes</t>
+          <t>Tes scores restent stables. Essaie de te concentrer sur les mots que tu rates encore.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Reused label under each sample list row</t>
+          <t>5 message variants, picked at random each screen load</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>sample_list_add</t>
+          <t>trend_steady_2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>You're consistent on this list — a few more reps on the tricky words could push you higher.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Añadir</t>
+          <t>Eres constante en esta lista — unas repeticiones más en las palabras difíciles podrían subirte el nivel.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ajouter</t>
+          <t>Tu es régulier sur cette liste — quelques répétitions de plus sur les mots difficiles pourraient te faire progresser.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -4714,32 +4746,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>sample_list_adding</t>
+          <t>trend_steady_3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Adding…</t>
+          <t>Not much movement lately. Worth a look at which specific words trip you up.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Añadiendo…</t>
+          <t>No ha habido mucho cambio últimamente. Vale la pena ver qué palabras concretas te cuestan.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ajout en cours…</t>
+          <t>Pas beaucoup de changement dernièrement. Ça vaut le coup de voir quels mots précis te posent problème.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -4747,69 +4779,65 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>sample_list_added</t>
+          <t>trend_steady_4</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Holding steady for now — try mixing in the word list reveal less to really test recall.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Añadido</t>
+          <t>Se mantiene estable por ahora — intenta usar menos la lista de palabras visible para poner a prueba tu memoria de verdad.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ajouté</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
-        </is>
-      </c>
+          <t>Ça reste stable pour l'instant — essaie de moins t'appuyer sur la liste de mots visible pour vraiment tester ta mémoire.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>error_adding_sample</t>
+          <t>trend_steady_5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Something went wrong adding that sample list.</t>
+          <t>Your scores are level. A quick review of your weaker words might get things moving again.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
+          <t>Tus puntuaciones están estables. Un repaso rápido de tus palabras más débiles podría hacer que avances de nuevo.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+          <t>Tes scores sont stables. Une petite révision de tes mots les plus faibles pourrait relancer ta progression.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -4817,65 +4845,69 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>trend_declining_1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Your scores dipped a bit recently — might be worth a quick refresher.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Omitir</t>
+          <t>Tus puntuaciones han bajado un poco últimamente — podría valer la pena un repaso rápido.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Passer</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+          <t>Tes scores ont légèrement baissé récemment — un petit rappel pourrait être utile.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>5 message variants, picked at random each screen load</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>trend_declining_2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>A small dip lately. Nothing major, just revisit this list when you get a chance.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Una pequeña bajada últimamente. Nada grave, solo repasa esta lista cuando puedas.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Retour</t>
+          <t>Une petite baisse dernièrement. Rien de grave, revois juste cette liste quand tu as l'occasion.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -4883,32 +4915,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>trend_declining_3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Scores have slipped slightly — could be worth slowing down on your next attempt.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Las puntuaciones han bajado un poco — podría valer la pena ir más despacio en tu próximo intento.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Suivant</t>
+          <t>Les scores ont légèrement chuté — ça pourrait valoir le coup de ralentir lors de ta prochaine tentative.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -4916,32 +4948,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>get_started</t>
+          <t>trend_declining_4</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Get Started</t>
+          <t>A bit of a dip recently. Happens — a short review session should help.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Empezar</t>
+          <t>Una pequeña bajada recientemente. Pasa a veces — una sesión corta de repaso debería ayudar.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Commencer</t>
+          <t>Une petite baisse récemment. Ça arrive — une courte session de révision devrait aider.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -4949,32 +4981,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>slide1_headline</t>
+          <t>trend_declining_5</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Build Your List</t>
+          <t>Your recent scores are a little lower than before — maybe a refresher is due.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crea tu lista</t>
+          <t>Tus puntuaciones recientes son un poco más bajas que antes — quizás toca un repaso.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crée ta liste</t>
+          <t>Tes scores récents sont un peu plus bas qu'avant — un petit rappel serait peut-être utile.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -4982,65 +5014,69 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>slide1_body</t>
+          <t>trend_declining_a_lot_1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>Your scores dropped noticeably. Consider going back through this list before your next quiz.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>Tus puntuaciones han bajado notablemente. Considera repasar esta lista antes de tu próximo cuestionario.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
+          <t>Tes scores ont nettement baissé. Pense à revoir cette liste avant ton prochain quiz.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>5 message variants, picked at random each screen load</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>slide2_headline</t>
+          <t>trend_declining_a_lot_2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Practice With Adaptive Quizzes</t>
+          <t>A bigger drop than usual — this list might need a real refresher before your next attempt.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Practica con cuestionarios adaptativos</t>
+          <t>Una bajada mayor de lo habitual — esta lista podría necesitar un repaso serio antes de tu próximo intento.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Entraîne-toi avec des quiz adaptatifs</t>
+          <t>Une baisse plus importante que d'habitude — cette liste aurait peut-être besoin d'une vraie révision avant ta prochaine tentative.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -5048,32 +5084,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>slide2_body</t>
+          <t>trend_declining_a_lot_3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
+          <t>Scores have fallen off quite a bit. Worth reviewing the list from scratch.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
+          <t>Las puntuaciones han bajado bastante. Vale la pena repasar la lista desde cero.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
+          <t>Les scores ont pas mal chuté. Ça vaut le coup de revoir la liste depuis le début.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5081,32 +5117,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>slide3_headline</t>
+          <t>trend_declining_a_lot_4</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Watch Your Progress</t>
+          <t>That's a steep dip — might help to slow down and review before quizzing again.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Observa tu progreso</t>
+          <t>Es una caída pronunciada — podría ayudar ir más despacio y repasar antes de volver a hacer el cuestionario.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Suis ta progression</t>
+          <t>C'est une chute assez marquée — ralentir et réviser avant de refaire le quiz pourrait aider.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -5114,32 +5150,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>slide3_body</t>
+          <t>trend_declining_a_lot_5</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>See your scores improve over time, list by list.</t>
+          <t>A significant drop here. Don't worry, just revisit the list before jumping back in.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
+          <t>Una bajada importante aquí. No te preocupes, solo repasa la lista antes de volver a intentarlo.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
+          <t>Une baisse importante ici. Pas de souci, revois juste la liste avant de t'y remettre.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -5147,44 +5183,36 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>backend (api errors)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>about_langreps_link</t>
+          <t>backend_error_text</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>About LangReps</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Acerca de LangReps</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>À propos de LangReps</t>
-        </is>
-      </c>
+          <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Links to /onboarding to replay it manually</t>
+          <t>Decided: stays English-only — these are dev-facing/edge-case errors (malformed requests, validation failures), not normal user-facing copy</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5194,22 +5222,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sort_by_label</t>
+          <t>sample_lists_title</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Sample Lists</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ordenar por</t>
+          <t>Listas de ejemplo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Trier par</t>
+          <t>Listes types</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5217,7 +5245,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5227,22 +5255,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>sort_by_date</t>
+          <t>sample_lists_hint</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Last Uploaded</t>
+          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Última subida</t>
+          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dernier import</t>
+          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -5250,7 +5278,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5260,30 +5288,34 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>sort_by_name</t>
+          <t>sample_list_name_template</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr"/>
+          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Template — used as both display label and saved list name</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5293,34 +5325,34 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>last_uploaded_template</t>
+          <t>sample_list_type_vocab</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Last uploaded: {date}</t>
+          <t>Vocab</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Última subida: {date}</t>
+          <t>Vocabulario</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dernier import : {date}</t>
+          <t>Vocabulaire</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Reused label under each sample list row</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5330,34 +5362,34 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sample_list_name_template_v2</t>
+          <t>sample_list_type_verbs</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
+          <t>Verbs</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
+          <t>Verbos</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+          <t>Verbes</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Superseded template — replaces the old arrow-notation naming</t>
+          <t>Reused label under each sample list row</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5367,34 +5399,30 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sample_list_card_title</t>
+          <t>sample_list_add</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Vocab {count} / Verb {count}</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vocabulario {count} / Verbo {count}</t>
+          <t>Añadir</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vocabulaire {count} / Verbe {count}</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Sample-list catalog card title, replaces the old full name display</t>
-        </is>
-      </c>
+          <t>Ajouter</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5404,526 +5432,467 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>sample_list_card_flags</t>
+          <t>sample_list_adding</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Adding…</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Añadiendo…</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
-        </is>
-      </c>
+          <t>Ajout en cours…</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>index.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>signup_incentive_hint</t>
+          <t>sample_list_added</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Sign up to save your lists and track your progress over time</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
+          <t>Añadido</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>Ajouté</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>default_level_title</t>
+          <t>error_adding_sample</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Default Level</t>
+          <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nivel predeterminado</t>
+          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Niveau par défaut</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>New section title for Settings redesign (bold title + description layout)</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>auto_delete_title</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Auto-Delete Old Quizzes</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eliminar automáticamente cuestionarios antiguos</t>
+          <t>Omitir</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Suppression automatique des anciens quiz</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>New section title</t>
-        </is>
-      </c>
+          <t>Passer</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>auto_delete_desc</t>
+          <t>back</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Completed quizzes are removed after 30 days</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Los cuestionarios completados se eliminan después de 30 días</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Les quiz terminés sont supprimés après 30 jours</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Description moved under the bold title</t>
-        </is>
-      </c>
+          <t>Retour</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_title</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Adaptive Quizzes</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cuestionarios adaptativos</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Quiz adaptatifs</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>New section title</t>
-        </is>
-      </c>
+          <t>Suivant</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_desc</t>
+          <t>get_started</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Get feedback on patterns you struggle with, and an option to target them</t>
+          <t>Get Started</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+          <t>Empezar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Description moved under the bold title</t>
-        </is>
-      </c>
+          <t>Commencer</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>require_accents_title</t>
+          <t>slide1_headline</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Require Diacritics</t>
+          <t>Build Your List</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Exigir diacríticos</t>
+          <t>Crea tu lista</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Exiger les diacritiques</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>New toggle — renamed from "Require Accents"</t>
-        </is>
-      </c>
+          <t>Crée ta liste</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>require_accents_desc</t>
+          <t>slide1_body</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Off accepts "cafe" for "café"</t>
+          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Desactivado acepta "cafe" en lugar de "café"</t>
+          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Désactivé accepte "cafe" pour "café"</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
-        </is>
-      </c>
+          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>your_lists_section_title</t>
+          <t>slide2_headline</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Your Lists</t>
+          <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tus listas</t>
+          <t>Practica con cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tes listes</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>New section title alongside bulk-select controls</t>
-        </is>
-      </c>
+          <t>Entraîne-toi avec des quiz adaptatifs</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>bulk_select_toggle</t>
+          <t>slide2_body</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Select / Done</t>
+          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Seleccionar / Listo</t>
+          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sélectionner / Terminé</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
-        </is>
-      </c>
+          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>bulk_select_all</t>
+          <t>slide3_headline</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Select All / Deselect All</t>
+          <t>Watch Your Progress</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Seleccionar todo / Deseleccionar todo</t>
+          <t>Observa tu progreso</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tout sélectionner / Tout désélectionner</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Shared pattern</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Suis ta progression</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>bulk_delete_selected_template</t>
+          <t>slide3_body</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Delete ({count})</t>
+          <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Eliminar ({count})</t>
+          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Supprimer ({count})</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Shared pattern</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>bulk_deleting</t>
+          <t>about_langreps_link</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Deleting…</t>
+          <t>About LangReps</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Eliminando…</t>
+          <t>Acerca de LangReps</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Suppression…</t>
+          <t>À propos de LangReps</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Shared pattern</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> My Lists and My Quizzes</t>
+          <t>Links to /onboarding to replay it manually</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5933,22 +5902,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_title</t>
+          <t>sort_by_label</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Delete Lists</t>
+          <t>Sort by</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Eliminar listas</t>
+          <t>Ordenar por</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Supprimer les listes</t>
+          <t>Trier par</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -5956,7 +5925,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5966,22 +5935,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_message_template</t>
+          <t>sort_by_date</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Delete {count} list(s)? This can't be undone.</t>
+          <t>Last Uploaded</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
+          <t>Última subida</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+          <t>Dernier import</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -5989,32 +5958,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>quizzes_in_progress_count_template</t>
+          <t>sort_by_name</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{count} in progress</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>{count} en curso</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>{count} en cours</t>
+          <t>Nom</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -6022,658 +5991,690 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_title</t>
+          <t>last_uploaded_template</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Delete Quizzes</t>
+          <t>Last uploaded: {date}</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Eliminar cuestionarios</t>
+          <t>Última subida: {date}</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Supprimer les quiz</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr"/>
+          <t>Dernier import : {date}</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_message_template</t>
+          <t>sample_list_name_template_v2</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Delete {count} quiz(zes)? This can't be undone.</t>
+          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
+          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
+          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Superseded template — replaces the old arrow-notation naming</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>sort_by_last_updated</t>
+          <t>sample_list_card_title</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Last Updated</t>
+          <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Última actualización</t>
+          <t>Vocabulario {count} / Verbo {count}</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dernière mise à jour</t>
+          <t>Vocabulaire {count} / Verbe {count}</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+          <t>Sample-list catalog card title, replaces the old full name display</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>last_updated_template</t>
+          <t>sample_list_card_flags</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Last updated: {date}</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Última actualización: {date}</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dernière mise à jour : {date}</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>index.tsx</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>quiz_type_badge_vocab</t>
+          <t>signup_incentive_hint</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
-        </is>
-      </c>
+          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>quiz_type_badge_verb</t>
+          <t>default_level_title</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Default Level</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Verbo</t>
+          <t>Nivel predeterminado</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Verbe</t>
+          <t>Niveau par défaut</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title</t>
+          <t>New section title for Settings redesign (bold title + description layout)</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>canned_feedback_mastery</t>
+          <t>auto_delete_title</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
+          <t>Auto-Delete Old Quizzes</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
+          <t>Eliminar automáticamente cuestionarios antiguos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
+          <t>Suppression automatique des anciens quiz</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
+          <t>New section title</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>canned_feedback_solid</t>
+          <t>auto_delete_desc</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
+          <t>Completed quizzes are removed after 30 days</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
+          <t>Los cuestionarios completados se eliminan después de 30 días</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
+          <t>Les quiz terminés sont supprimés après 30 jours</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>70-89% correct</t>
+          <t>Description moved under the bold title</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>canned_feedback_building</t>
+          <t>adaptive_quizzes_title</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
+          <t>Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
+          <t>Cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
+          <t>Quiz adaptatifs</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>40-69% correct</t>
+          <t>New section title</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>canned_feedback_struggling</t>
+          <t>adaptive_quizzes_desc</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
+          <t>Get feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
+          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
+          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Below 40% correct</t>
+          <t>Description moved under the bold title</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>cefr_info_alert_title</t>
+          <t>require_accents_title</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>CEFR Levels</t>
+          <t>Require Diacritics</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Niveles del MCER</t>
+          <t>Exigir diacríticos</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Niveaux du CECR</t>
+          <t>Exiger les diacritiques</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alert title triggered by new info icon next to the Level label</t>
+          <t>New toggle — renamed from "Require Accents"</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>cefr_a1_explanation</t>
+          <t>require_accents_desc</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Breakthrough — basic words and phrases for everyday needs.</t>
+          <t>Off accepts "cafe" for "café"</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
+          <t>Desactivado acepta "cafe" en lugar de "café"</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
+          <t>Désactivé accepte "cafe" pour "café"</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>cefr_a2_explanation</t>
+          <t>your_lists_section_title</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
+          <t>Your Lists</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
+          <t>Tus listas</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
+          <t>Tes listes</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>New section title alongside bulk-select controls</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>cefr_b1_explanation</t>
+          <t>bulk_select_toggle</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
+          <t>Select / Done</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
+          <t>Seleccionar / Listo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr"/>
+          <t>Sélectionner / Terminé</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>cefr_b2_explanation</t>
+          <t>bulk_select_all</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
+          <t>Select All / Deselect All</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
+          <t>Seleccionar todo / Deseleccionar todo</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
+          <t>Tout sélectionner / Tout désélectionner</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>cefr_c1_explanation</t>
+          <t>bulk_delete_selected_template</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
+          <t>Delete ({count})</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
+          <t>Eliminar ({count})</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
+          <t>Supprimer ({count})</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>cefr_c2_explanation</t>
+          <t>bulk_deleting</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
+          <t>Deleting…</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
+          <t>Eliminando…</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
+          <t>Suppression…</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>splash_title</t>
+          <t>bulk_delete_lists_alert_title</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LangReps</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
-        </is>
-      </c>
+          <t>Delete Lists</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Eliminar listas</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Supprimer les listes</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>splash_tagline</t>
+          <t>bulk_delete_lists_alert_message_template</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Language reps that stick.</t>
+          <t>Delete {count} list(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Repeticiones de idiomas que se quedan.</t>
+          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Des répétitions de langue qui restent.</t>
+          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -6681,98 +6682,98 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>splash_copyright</t>
+          <t>quizzes_in_progress_count_template</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>© 2026 MarApps Development</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Pinned bottom-right corner</t>
-        </is>
-      </c>
+          <t>{count} in progress</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>{count} en curso</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>{count} en cours</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>see_full_results</t>
+          <t>bulk_delete_quizzes_alert_title</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>See Full Results</t>
+          <t>Delete Quizzes</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ver resultados completos</t>
+          <t>Eliminar cuestionarios</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Voir les résultats complets</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
-        </is>
-      </c>
+          <t>Supprimer les quiz</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>full_results_title</t>
+          <t>bulk_delete_quizzes_alert_message_template</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Full Results</t>
+          <t>Delete {count} quiz(zes)? This can't be undone.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Resultados completos</t>
+          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Résultats complets</t>
+          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
@@ -6780,519 +6781,530 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>no_recorded_answers</t>
+          <t>sort_by_last_updated</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>No recorded answers for this quiz.</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>No hay respuestas registradas para este cuestionario.</t>
+          <t>Última actualización</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Aucune réponse enregistrée pour ce quiz.</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr"/>
+          <t>Dernière mise à jour</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>your_answer_label</t>
+          <t>last_updated_template</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Your answer:</t>
+          <t>Last updated: {date}</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Tu respuesta:</t>
+          <t>Última actualización: {date}</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ta réponse :</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr"/>
+          <t>Dernière mise à jour : {date}</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>correct_answer_label</t>
+          <t>quiz_type_badge_vocab</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Correct answer:</t>
+          <t>Vocab</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Respuesta correcta:</t>
+          <t>Vocabulario</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bonne réponse :</t>
+          <t>Vocabulaire</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Shown only for incorrect rows</t>
+          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>blank_answer_fallback</t>
+          <t>quiz_type_badge_verb</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(en blanco)</t>
+          <t>Verbo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>(vide)</t>
+          <t>Verbe</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Shown when a skipped/empty answer was recorded</t>
+          <t>Small badge next to the quiz row title</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>error_loading_results</t>
+          <t>canned_feedback_mastery</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Something went wrong loading results.</t>
+          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar los resultados.</t>
+          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement des résultats.</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr"/>
+          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>list_type_info_alert_title</t>
+          <t>canned_feedback_solid</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>List Types</t>
+          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Tipos de lista</t>
+          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Types de liste</t>
+          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>New info icon next to the List type label</t>
+          <t>70-89% correct</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>list_type_info_vocab</t>
+          <t>canned_feedback_building</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
+          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
+          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
+          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>40-69% correct</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>list_type_info_verb</t>
+          <t>canned_feedback_struggling</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
+          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
+          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Below 40% correct</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>save_input_placeholder_new</t>
+          <t>cefr_info_alert_title</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Name this list</t>
+          <t>CEFR Levels</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Nombra esta lista</t>
+          <t>Niveles del MCER</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Nomme cette liste</t>
+          <t>Niveaux du CECR</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
+          <t>Alert title triggered by new info icon next to the Level label</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>save_input_placeholder_update</t>
+          <t>cefr_a1_explanation</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>List name (updates it)</t>
+          <t>Breakthrough — basic words and phrases for everyday needs.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Nombre de la lista (la actualiza)</t>
+          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Nom de la liste (la met à jour)</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Placeholder shown once the list is already saved — shortened to fit</t>
-        </is>
-      </c>
+          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>195</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>constants/styles.ts</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>placeholder_color_note</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Not a UI string — new colors.placeholder token (#8C7F63) applied via placeholderTextColor to every TextInput app-wide; RN's default placeholder gray had poor contrast on the parchment background and was nearly invisible</t>
-        </is>
-      </c>
+          <t>cefr_a2_explanation</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>edit_list_link</t>
+          <t>cefr_b1_explanation</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Editar</t>
+          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Modifier</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
-        </is>
-      </c>
+          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>remove_word_icon</t>
+          <t>cefr_b2_explanation</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
-        </is>
-      </c>
+          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>translate_prompt_template</t>
+          <t>cefr_c1_explanation</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>{n} line(s) looked like single word(s)</t>
+          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
+          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
+          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
         </is>
       </c>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>translate_button</t>
+          <t>cefr_c2_explanation</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Traducir</t>
+          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Traduire</t>
+          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
         </is>
       </c>
       <c r="G200" t="inlineStr"/>
@@ -7300,353 +7312,349 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>translating_ellipsis</t>
+          <t>splash_title</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Translating…</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Traduciendo…</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Traduction en cours…</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr"/>
+          <t>LangReps</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>error_translating</t>
+          <t>splash_tagline</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Something went wrong translating those words.</t>
+          <t>Flex your language muscles.</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Algo salió mal al traducir esas palabras.</t>
+          <t>Dale músculo a tus idiomas.</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr"/>
+          <t>Muscle tes langues.</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Replaces "Language reps that stick." ES/FR use the same fitness idiom naturally — "dar músculo a"/"muscler" both mean "to strengthen/build up" and are used metaphorically for skills (French "musclez votre anglais" is an established phrase), not just literal muscle</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>slide1_body_updated</t>
+          <t>splash_copyright</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
-        </is>
-      </c>
+          <t>© 2026 MarApps Development</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+          <t>Pinned bottom-right corner</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>saved_list_heading</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+          <t>see_full_results</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>See Full Results</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Ver resultados completos</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Voir les résultats complets</t>
+        </is>
+      </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Not new text — shows the list's own saved name prominently at the top of PairsReview once saved (Edit flow especially), styled like Generate Quiz's list-name heading</t>
+          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>rename_link</t>
+          <t>full_results_title</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Full Results</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Cambiar nombre</t>
+          <t>Resultados</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Renommer</t>
+          <t>Résultats</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>New — separates renaming an already-saved list from saving its pairs</t>
+          <t>Dropped "completo(s)"/"complets" — redundant, the screen itself already shows the complete breakdown</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>rename_save_button</t>
+          <t>no_recorded_answers</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>No recorded answers for this quiz.</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Guardar</t>
+          <t>No hay respuestas registradas para este cuestionario.</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Enregistrer</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Inline rename confirm button</t>
-        </is>
-      </c>
+          <t>Aucune réponse enregistrée pour ce quiz.</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>rename_cancel_button</t>
+          <t>your_answer_label</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Your answer:</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Tu respuesta:</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Annuler</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Inline rename cancel button</t>
-        </is>
-      </c>
+          <t>Ta réponse :</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>error_renaming</t>
+          <t>correct_answer_label</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Something went wrong renaming.</t>
+          <t>Correct answer:</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Algo salió mal al cambiar el nombre.</t>
+          <t>Respuesta correcta:</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du renommage.</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr"/>
+          <t>Bonne réponse :</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Shown only for incorrect rows</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>save_changes_button</t>
+          <t>blank_answer_fallback</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Save Changes</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Guardar cambios</t>
+          <t>(en blanco)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Enregistrer les modifications</t>
+          <t>(vide)</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
+          <t>Shown when a skipped/empty answer was recorded</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>list_type_locked_label</t>
+          <t>error_loading_results</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>List type (locked)</t>
+          <t>Something went wrong loading results.</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Tipo de lista (bloqueado)</t>
+          <t>Algo salió mal al cargar los resultados.</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Type de liste (verrouillé)</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Appended to the label once a list is saved — type can't change after first save</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7656,101 +7664,92 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>list_type_locked_explanation</t>
+          <t>list_type_info_alert_title</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
+          <t>List Types</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
+          <t>Tipos de lista</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+          <t>Types de liste</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Appended to the existing List Types info alert once locked</t>
+          <t>New info icon next to the List type label</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>past_quizzes_section_title</t>
+          <t>list_type_info_vocab</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Past Quizzes</t>
+          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Cuestionarios anteriores</t>
+          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Quiz précédents</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>New section showing completed quiz history</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> fetched from GET /quiz-sessions/completed</t>
-        </is>
-      </c>
+          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>no_completed_quizzes</t>
+          <t>list_type_info_verb</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>No completed quizzes yet.</t>
+          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aún no hay cuestionarios completados.</t>
+          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Aucun quiz terminé pour l'instant.</t>
+          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
         </is>
       </c>
       <c r="G213" t="inlineStr"/>
@@ -7758,336 +7757,1718 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>past_quiz_score_template</t>
+          <t>save_input_placeholder_new</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>{correct}/{total} correct ({pct}%)</t>
+          <t>Name this list</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctas ({pct}%)</t>
+          <t>Nombra esta lista</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctes ({pct} %)</t>
+          <t>Nomme cette liste</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>deleted_list_fallback</t>
+          <t>save_input_placeholder_update</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Deleted list</t>
+          <t>List name (updates it)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lista eliminada</t>
+          <t>Nombre de la lista (la actualiza)</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Liste supprimée</t>
+          <t>Nom de la liste (la met à jour)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Shown when a past quiz's list no longer exists</t>
+          <t>Placeholder shown once the list is already saved — shortened to fit</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_title</t>
+          <t>edit_list_link</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Discard unsaved words?</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>¿Descartar palabras sin guardar?</t>
+          <t>Editar</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Abandonner les mots non enregistrés ?</t>
+          <t>Modifier</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
+          <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_message</t>
+          <t>remove_word_icon</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr"/>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>leave_without_saving</t>
+          <t>translate_prompt_template</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Leave Without Saving</t>
+          <t>{n} line(s) looked like single word(s), not pairs — translate into:</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Salir sin guardar</t>
+          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Quitter sans enregistrer</t>
+          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Destructive confirm action</t>
+          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>order_confirm_prompt_template</t>
+          <t>translate_button</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Detected {first} and {second}. Which one do you already know?</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
+          <t>Traducir</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
-        </is>
-      </c>
+          <t>Traduire</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>order_confirm_option_template</t>
+          <t>translating_ellipsis</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>I know {language}</t>
+          <t>Translating…</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ya sé {language}</t>
+          <t>Traduciendo…</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Je connais déjà {language}</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Two buttons</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> one per detected language</t>
-        </is>
-      </c>
+          <t>Traduction en cours…</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>source_word_placeholder_dynamic</t>
+          <t>error_translating</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Word in {language}</t>
+          <t>Something went wrong translating those words.</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Palabra en {language}</t>
+          <t>Algo salió mal al traducir esas palabras.</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mot en {language}</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>slide1_body_updated</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>rename_link</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Cambiar nombre</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Renommer</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>New — separates renaming an already-saved list from saving its pairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>rename_save_button</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Guardar</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Enregistrer</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Inline rename confirm button</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>rename_cancel_button</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Cancelar</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Annuler</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Inline rename cancel button</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>error_renaming</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Something went wrong renaming.</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Algo salió mal al cambiar el nombre.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors du renommage.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>save_changes_button</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Save Changes</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Guardar cambios</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Enregistrer les modifications</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>list_type_locked_label</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>List type (locked)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Tipo de lista (bloqueado)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Type de liste (verrouillé)</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Appended to the label once a list is saved — type can't change after first save</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>list_type_locked_explanation</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Appended to the existing List Types info alert once locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>past_quizzes_section_title</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Past Quizzes</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Cuestionarios anteriores</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Quiz précédents</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>New section showing completed quiz history, fetched from GET /quiz-sessions/completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>no_past_quizzes</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>No completed quizzes yet.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Aún no hay cuestionarios completados.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Aucun quiz terminé pour l'instant.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Renamed from no_completed_quizzes — collided with list-history.tsx's key of the same name</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>past_quiz_score_template</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>{correct}/{total} correct ({pct}%)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>{correct}/{total} correctas ({pct}%)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>{correct}/{total} correctes ({pct} %)</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>deleted_list_fallback</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Deleted list</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Lista eliminada</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Liste supprimée</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Shown when a past quiz's list no longer exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>back-button.tsx</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>discard_unsaved_alert_title</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Discard unsaved words?</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>¿Descartar palabras sin guardar?</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Abandonner les mots non enregistrés ?</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>back-button.tsx</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>discard_unsaved_alert_message</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>back-button.tsx</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>leave_without_saving</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Leave Without Saving</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Salir sin guardar</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Quitter sans enregistrer</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Destructive confirm action</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>language-order-confirm.tsx</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>order_confirm_prompt_template</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Detected {first} and {second}. Which one do you already know?</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>language-order-confirm.tsx</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>order_confirm_option_template</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>I know {language}</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Ya sé {language}</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Je connais déjà {language}</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Two buttons, one per detected language</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
         <is>
           <t>add-words.tsx</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>source_word_placeholder_dynamic</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Word in {language}</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Palabra en {language}</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Mot en {language}</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>add-words.tsx</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>target_word_placeholder_dynamic</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>Word in {language}</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>Palabra en {language}</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>Mot en {language}</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
         </is>
       </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>app_language_title</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>App Language</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Idioma de la app</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Langue de l'application</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>New — the UI locale picker itself, part of building the actual i18n layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>list_type_label</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>List type</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Tipo de lista</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Type de liste</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>select_label</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Seleccionar</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Sélectionner</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>done_label</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Listo</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Terminé</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>select_all_label</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Select All</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Seleccionar todo</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Tout sélectionner</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>deselect_all_label</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Deselect All</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Deseleccionar todo</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Tout désélectionner</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>sample_list_type_verb_singular</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Verbo</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Verbe</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Singular form for the sample-list card title ("Verb {count}"), distinct from sample_list_type_verbs ("Verbs", used elsewhere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>error_deleting_lists_bulk</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Something went wrong deleting those lists.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Algo salió mal al eliminar esas listas.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>error_deleting_quizzes_bulk</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Something went wrong deleting those quizzes.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Algo salió mal al eliminar esos cuestionarios.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>loading_ellipsis</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Loading…</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Cargando…</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Chargement…</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Reused wherever a screen shows a generic loading state</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>login.tsx</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>forgot_password_link</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Forgot password?</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>¿Olvidaste tu contraseña?</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Mot de passe oublié ?</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>forgot_password_title</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Forgot Password</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Contraseña olvidada</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Mot de passe oublié</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>forgot_password_sent_message</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>forgot_password_instructions</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Enter your email and we'll send you a link to reset your password.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>sending_ellipsis</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Sending…</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Enviando…</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Envoi en cours…</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>send_reset_link</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Send Reset Link</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Enviar enlace de restablecimiento</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Envoyer le lien de réinitialisation</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>reset-password.tsx</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>reset_password_title</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Reset Password</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Restablecer contraseña</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Réinitialiser le mot de passe</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>reset-password.tsx</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>reset_link_invalid_message</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>reset-password.tsx</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>set_new_password_title</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Set a New Password</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Establece una nueva contraseña</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Définis un nouveau mot de passe</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>reset-password.tsx</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>new_password_placeholder</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>New password</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Nueva contraseña</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Nouveau mot de passe</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>reset-password.tsx</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>save_new_password</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Save New Password</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Guardar nueva contraseña</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Enregistrer le nouveau mot de passe</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1356,30 +1356,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>add_words_title</t>
+          <t>list_details_title</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Add Words</t>
+          <t>List Details</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Añadir palabras</t>
+          <t>Detalles de la lista</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajouter des mots</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Détails de la liste</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Renamed from add_words_title/Add Words — screen now also used to view/manage an existing saved list, not just build a new one</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1389,7 +1393,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5325,29 +5329,25 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>sample_list_type_vocab</t>
+          <t>sample_list_add</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Añadir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Reused label under each sample list row</t>
-        </is>
-      </c>
+          <t>Ajouter</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5362,29 +5362,25 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sample_list_type_verbs</t>
+          <t>sample_list_adding</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Verbs</t>
+          <t>Adding…</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Verbos</t>
+          <t>Añadiendo…</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Verbes</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Reused label under each sample list row</t>
-        </is>
-      </c>
+          <t>Ajout en cours…</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5399,25 +5395,29 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sample_list_add</t>
+          <t>sample_list_added</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Añadir</t>
+          <t>Añadido</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ajouter</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
+          <t>Ajouté</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5432,22 +5432,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>sample_list_adding</t>
+          <t>error_adding_sample</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Adding…</t>
+          <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Añadiendo…</t>
+          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ajout en cours…</t>
+          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -5460,34 +5460,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>sample_list_added</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Añadido</t>
+          <t>Omitir</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ajouté</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
-        </is>
-      </c>
+          <t>Passer</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5497,27 +5493,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>error_adding_sample</t>
+          <t>back</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Something went wrong adding that sample list.</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+          <t>Retour</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -5535,22 +5531,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Omitir</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Passer</t>
+          <t>Suivant</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -5568,22 +5564,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>get_started</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Get Started</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Empezar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Retour</t>
+          <t>Commencer</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -5601,22 +5597,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>slide1_headline</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Build Your List</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Crea tu lista</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Suivant</t>
+          <t>Crée ta liste</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -5634,22 +5630,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>get_started</t>
+          <t>slide1_body</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Get Started</t>
+          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Empezar</t>
+          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Commencer</t>
+          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -5667,22 +5663,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>slide1_headline</t>
+          <t>slide2_headline</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Build Your List</t>
+          <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Crea tu lista</t>
+          <t>Practica con cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Crée ta liste</t>
+          <t>Entraîne-toi avec des quiz adaptatifs</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -5700,22 +5696,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>slide1_body</t>
+          <t>slide2_body</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -5733,22 +5729,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>slide2_headline</t>
+          <t>slide3_headline</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Practice With Adaptive Quizzes</t>
+          <t>Watch Your Progress</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Practica con cuestionarios adaptativos</t>
+          <t>Observa tu progreso</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Entraîne-toi avec des quiz adaptatifs</t>
+          <t>Suis ta progression</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -5766,22 +5762,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>slide2_body</t>
+          <t>slide3_body</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
+          <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
+          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
+          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -5794,30 +5790,34 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>slide3_headline</t>
+          <t>about_langreps_link</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Watch Your Progress</t>
+          <t>About LangReps</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Observa tu progreso</t>
+          <t>Acerca de LangReps</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Suis ta progression</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
+          <t>À propos de LangReps</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Links to /onboarding to replay it manually</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5827,27 +5827,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>slide3_body</t>
+          <t>sort_by_label</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>See your scores improve over time, list by list.</t>
+          <t>Sort by</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
+          <t>Ordenar por</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
+          <t>Trier par</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -5860,34 +5860,30 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>about_langreps_link</t>
+          <t>sort_by_date</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>About LangReps</t>
+          <t>Last Uploaded</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Acerca de LangReps</t>
+          <t>Última subida</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>À propos de LangReps</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Links to /onboarding to replay it manually</t>
-        </is>
-      </c>
+          <t>Dernier import</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5902,22 +5898,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>sort_by_label</t>
+          <t>sort_by_name</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ordenar por</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trier par</t>
+          <t>Nom</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -5935,25 +5931,29 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>sort_by_date</t>
+          <t>last_uploaded_template</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Last Uploaded</t>
+          <t>Last uploaded: {date}</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Última subida</t>
+          <t>Última subida: {date}</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dernier import</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
+          <t>Dernier import : {date}</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5968,25 +5968,29 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>sort_by_name</t>
+          <t>sample_list_name_template_v2</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr"/>
+          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Superseded template — replaces the old arrow-notation naming</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6001,27 +6005,27 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>last_uploaded_template</t>
+          <t>sample_list_card_title</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Last uploaded: {date}</t>
+          <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Última subida: {date}</t>
+          <t>Vocabulario {count} / Verbo {count}</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dernier import : {date}</t>
+          <t>Vocabulaire {count} / Verbe {count}</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Sample-list catalog card title, replaces the old full name display</t>
         </is>
       </c>
     </row>
@@ -6038,27 +6042,27 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>sample_list_name_template_v2</t>
+          <t>sample_list_card_flags</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Superseded template — replaces the old arrow-notation naming</t>
+          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
     </row>
@@ -6070,34 +6074,30 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>index.tsx</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>sample_list_card_title</t>
+          <t>signup_incentive_hint</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Vocab {count} / Verb {count}</t>
+          <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vocabulario {count} / Verbo {count}</t>
+          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vocabulaire {count} / Verbe {count}</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Sample-list catalog card title, replaces the old full name display</t>
-        </is>
-      </c>
+          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>sample_list_card_flags</t>
+          <t>default_level_title</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Default Level</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Nivel predeterminado</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Niveau par défaut</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
+          <t>New section title for Settings redesign (bold title + description layout)</t>
         </is>
       </c>
     </row>
@@ -6144,30 +6144,34 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>index.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>signup_incentive_hint</t>
+          <t>auto_delete_title</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sign up to save your lists and track your progress over time</t>
+          <t>Auto-Delete Old Quizzes</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
+          <t>Eliminar automáticamente cuestionarios antiguos</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr"/>
+          <t>Suppression automatique des anciens quiz</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>New section title</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6182,27 +6186,27 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>default_level_title</t>
+          <t>auto_delete_desc</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Default Level</t>
+          <t>Completed quizzes are removed after 30 days</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Nivel predeterminado</t>
+          <t>Los cuestionarios completados se eliminan después de 30 días</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Niveau par défaut</t>
+          <t>Les quiz terminés sont supprimés après 30 jours</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>New section title for Settings redesign (bold title + description layout)</t>
+          <t>Description moved under the bold title</t>
         </is>
       </c>
     </row>
@@ -6219,22 +6223,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>auto_delete_title</t>
+          <t>adaptive_quizzes_title</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Auto-Delete Old Quizzes</t>
+          <t>Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Eliminar automáticamente cuestionarios antiguos</t>
+          <t>Cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Suppression automatique des anciens quiz</t>
+          <t>Quiz adaptatifs</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6256,22 +6260,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>auto_delete_desc</t>
+          <t>adaptive_quizzes_desc</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Completed quizzes are removed after 30 days</t>
+          <t>Get feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Los cuestionarios completados se eliminan después de 30 días</t>
+          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Les quiz terminés sont supprimés après 30 jours</t>
+          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6293,27 +6297,27 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_title</t>
+          <t>require_accents_title</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Adaptive Quizzes</t>
+          <t>Require Diacritics</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Cuestionarios adaptativos</t>
+          <t>Exigir diacríticos</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Quiz adaptatifs</t>
+          <t>Exiger les diacritiques</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>New section title</t>
+          <t>New toggle — renamed from "Require Accents"</t>
         </is>
       </c>
     </row>
@@ -6330,27 +6334,27 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_desc</t>
+          <t>require_accents_desc</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Get feedback on patterns you struggle with, and an option to target them</t>
+          <t>Off accepts "cafe" for "café"</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+          <t>Desactivado acepta "cafe" en lugar de "café"</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+          <t>Désactivé accepte "cafe" pour "café"</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Description moved under the bold title</t>
+          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
         </is>
       </c>
     </row>
@@ -6362,32 +6366,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>require_accents_title</t>
+          <t>your_lists_section_title</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Require Diacritics</t>
+          <t>Your Lists</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Exigir diacríticos</t>
+          <t>Tus listas</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Exiger les diacritiques</t>
+          <t>Tes listes</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>New toggle — renamed from "Require Accents"</t>
+          <t>New section title alongside bulk-select controls</t>
         </is>
       </c>
     </row>
@@ -6399,32 +6403,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>require_accents_desc</t>
+          <t>bulk_select_toggle</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Off accepts "cafe" for "café"</t>
+          <t>Select / Done</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Desactivado acepta "cafe" en lugar de "café"</t>
+          <t>Seleccionar / Listo</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Désactivé accepte "cafe" pour "café"</t>
+          <t>Sélectionner / Terminé</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
+          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
         </is>
       </c>
     </row>
@@ -6441,27 +6445,27 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>your_lists_section_title</t>
+          <t>bulk_select_all</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Your Lists</t>
+          <t>Select All / Deselect All</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tus listas</t>
+          <t>Seleccionar todo / Deseleccionar todo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tes listes</t>
+          <t>Tout sélectionner / Tout désélectionner</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>New section title alongside bulk-select controls</t>
+          <t>Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -6478,27 +6482,27 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>bulk_select_toggle</t>
+          <t>bulk_delete_selected_template</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Select / Done</t>
+          <t>Delete ({count})</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Seleccionar / Listo</t>
+          <t>Eliminar ({count})</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sélectionner / Terminé</t>
+          <t>Supprimer ({count})</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
+          <t>Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -6515,22 +6519,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>bulk_select_all</t>
+          <t>bulk_deleting</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Select All / Deselect All</t>
+          <t>Deleting…</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Seleccionar todo / Deseleccionar todo</t>
+          <t>Eliminando…</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tout sélectionner / Tout désélectionner</t>
+          <t>Suppression…</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6552,29 +6556,25 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>bulk_delete_selected_template</t>
+          <t>bulk_delete_lists_alert_title</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Delete ({count})</t>
+          <t>Delete Lists</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Eliminar ({count})</t>
+          <t>Eliminar listas</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Supprimer ({count})</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Shared pattern, My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Supprimer les listes</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6589,29 +6589,25 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>bulk_deleting</t>
+          <t>bulk_delete_lists_alert_message_template</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Deleting…</t>
+          <t>Delete {count} list(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Eliminando…</t>
+          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Suppression…</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Shared pattern, My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6621,27 +6617,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_title</t>
+          <t>quizzes_in_progress_count_template</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Delete Lists</t>
+          <t>{count} in progress</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Eliminar listas</t>
+          <t>{count} en curso</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Supprimer les listes</t>
+          <t>{count} en cours</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -6654,27 +6650,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_message_template</t>
+          <t>bulk_delete_quizzes_alert_title</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Delete {count} list(s)? This can't be undone.</t>
+          <t>Delete Quizzes</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
+          <t>Eliminar cuestionarios</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+          <t>Supprimer les quiz</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -6692,22 +6688,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>quizzes_in_progress_count_template</t>
+          <t>bulk_delete_quizzes_alert_message_template</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>{count} in progress</t>
+          <t>Delete {count} quiz(zes)? This can't be undone.</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>{count} en curso</t>
+          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>{count} en cours</t>
+          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
@@ -6725,25 +6721,29 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_title</t>
+          <t>sort_by_last_updated</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Delete Quizzes</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Eliminar cuestionarios</t>
+          <t>Última actualización</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Supprimer les quiz</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
+          <t>Dernière mise à jour</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6758,25 +6758,29 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_message_template</t>
+          <t>last_updated_template</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Delete {count} quiz(zes)? This can't be undone.</t>
+          <t>Last updated: {date}</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
+          <t>Última actualización: {date}</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr"/>
+          <t>Dernière mise à jour : {date}</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6791,27 +6795,27 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>sort_by_last_updated</t>
+          <t>quiz_type_badge_vocab</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Last Updated</t>
+          <t>Vocab</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Última actualización</t>
+          <t>Vocabulario</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dernière mise à jour</t>
+          <t>Vocabulaire</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
         </is>
       </c>
     </row>
@@ -6828,27 +6832,27 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>last_updated_template</t>
+          <t>quiz_type_badge_verb</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Last updated: {date}</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Última actualización: {date}</t>
+          <t>Verbo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dernière mise à jour : {date}</t>
+          <t>Verbe</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Small badge next to the quiz row title</t>
         </is>
       </c>
     </row>
@@ -6860,32 +6864,32 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>quiz_type_badge_vocab</t>
+          <t>canned_feedback_mastery</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
+          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
+          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
         </is>
       </c>
     </row>
@@ -6897,32 +6901,32 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>quiz_type_badge_verb</t>
+          <t>canned_feedback_solid</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Verbo</t>
+          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Verbe</t>
+          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title</t>
+          <t>70-89% correct</t>
         </is>
       </c>
     </row>
@@ -6939,27 +6943,27 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>canned_feedback_mastery</t>
+          <t>canned_feedback_building</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
+          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
+          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
+          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
+          <t>40-69% correct</t>
         </is>
       </c>
     </row>
@@ -6976,27 +6980,27 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>canned_feedback_solid</t>
+          <t>canned_feedback_struggling</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
+          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
+          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
+          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>70-89% correct</t>
+          <t>Below 40% correct</t>
         </is>
       </c>
     </row>
@@ -7008,32 +7012,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>canned_feedback_building</t>
+          <t>cefr_info_alert_title</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
+          <t>CEFR Levels</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
+          <t>Niveles del MCER</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
+          <t>Niveaux du CECR</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>40-69% correct</t>
+          <t>Alert title triggered by new info icon next to the Level label</t>
         </is>
       </c>
     </row>
@@ -7045,34 +7049,30 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>canned_feedback_struggling</t>
+          <t>cefr_a1_explanation</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
+          <t>Breakthrough — basic words and phrases for everyday needs.</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
+          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Below 40% correct</t>
-        </is>
-      </c>
+          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7087,29 +7087,25 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>cefr_info_alert_title</t>
+          <t>cefr_a2_explanation</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>CEFR Levels</t>
+          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Niveles del MCER</t>
+          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Niveaux du CECR</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Alert title triggered by new info icon next to the Level label</t>
-        </is>
-      </c>
+          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7124,22 +7120,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>cefr_a1_explanation</t>
+          <t>cefr_b1_explanation</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Breakthrough — basic words and phrases for everyday needs.</t>
+          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
+          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
@@ -7157,22 +7153,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>cefr_a2_explanation</t>
+          <t>cefr_b2_explanation</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
+          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
+          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
         </is>
       </c>
       <c r="G196" t="inlineStr"/>
@@ -7190,22 +7186,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>cefr_b1_explanation</t>
+          <t>cefr_c1_explanation</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
+          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
+          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
+          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
         </is>
       </c>
       <c r="G197" t="inlineStr"/>
@@ -7223,22 +7219,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>cefr_b2_explanation</t>
+          <t>cefr_c2_explanation</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
+          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
+          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
+          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
         </is>
       </c>
       <c r="G198" t="inlineStr"/>
@@ -7251,30 +7247,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>cefr_c1_explanation</t>
+          <t>splash_title</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
+          <t>LangReps</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7284,30 +7276,34 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>cefr_c2_explanation</t>
+          <t>splash_tagline</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
+          <t>Flex your language muscles.</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
+          <t>Dale músculo a tus idiomas.</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr"/>
+          <t>Muscle tes langues.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Replaces "Language reps that stick." ES/FR use the same fitness idiom naturally — "dar músculo a"/"muscler" both mean "to strengthen/build up" and are used metaphorically for skills (French "musclez votre anglais" is an established phrase), not just literal muscle</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7322,19 +7318,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>splash_title</t>
+          <t>splash_copyright</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LangReps</t>
+          <t>© 2026 MarApps Development</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+          <t>Pinned bottom-right corner</t>
         </is>
       </c>
     </row>
@@ -7346,32 +7342,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>splash_tagline</t>
+          <t>see_full_results</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Flex your language muscles.</t>
+          <t>See Full Results</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Dale músculo a tus idiomas.</t>
+          <t>Ver resultados completos</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Muscle tes langues.</t>
+          <t>Voir les résultats complets</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Replaces "Language reps that stick." ES/FR use the same fitness idiom naturally — "dar músculo a"/"muscler" both mean "to strengthen/build up" and are used metaphorically for skills (French "musclez votre anglais" is an established phrase), not just literal muscle</t>
+          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
         </is>
       </c>
     </row>
@@ -7383,24 +7379,32 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>splash_copyright</t>
+          <t>full_results_title</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>© 2026 MarApps Development</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+          <t>Full Results</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Resultados</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Résultats</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Pinned bottom-right corner</t>
+          <t>Dropped "completo(s)"/"complets" — redundant, the screen itself already shows the complete breakdown</t>
         </is>
       </c>
     </row>
@@ -7412,34 +7416,30 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>see_full_results</t>
+          <t>no_recorded_answers</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>See Full Results</t>
+          <t>No recorded answers for this quiz.</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ver resultados completos</t>
+          <t>No hay respuestas registradas para este cuestionario.</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Voir les résultats complets</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
-        </is>
-      </c>
+          <t>Aucune réponse enregistrée pour ce quiz.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7454,29 +7454,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>full_results_title</t>
+          <t>your_answer_label</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Full Results</t>
+          <t>Your answer:</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Resultados</t>
+          <t>Tu respuesta:</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Résultats</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Dropped "completo(s)"/"complets" — redundant, the screen itself already shows the complete breakdown</t>
-        </is>
-      </c>
+          <t>Ta réponse :</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7491,25 +7487,29 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>no_recorded_answers</t>
+          <t>correct_answer_label</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>No recorded answers for this quiz.</t>
+          <t>Correct answer:</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>No hay respuestas registradas para este cuestionario.</t>
+          <t>Respuesta correcta:</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Aucune réponse enregistrée pour ce quiz.</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr"/>
+          <t>Bonne réponse :</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Shown only for incorrect rows</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7524,25 +7524,29 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>your_answer_label</t>
+          <t>blank_answer_fallback</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Your answer:</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Tu respuesta:</t>
+          <t>(en blanco)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ta réponse :</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr"/>
+          <t>(vide)</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Shown when a skipped/empty answer was recorded</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7557,29 +7561,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>correct_answer_label</t>
+          <t>error_loading_results</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Correct answer:</t>
+          <t>Something went wrong loading results.</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Respuesta correcta:</t>
+          <t>Algo salió mal al cargar los resultados.</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bonne réponse :</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Shown only for incorrect rows</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7589,32 +7589,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>blank_answer_fallback</t>
+          <t>list_type_info_alert_title</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>List Types</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(en blanco)</t>
+          <t>Tipos de lista</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>(vide)</t>
+          <t>Types de liste</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Shown when a skipped/empty answer was recorded</t>
+          <t>New info icon next to the List type label</t>
         </is>
       </c>
     </row>
@@ -7626,27 +7626,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>error_loading_results</t>
+          <t>list_type_info_vocab</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Something went wrong loading results.</t>
+          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar los resultados.</t>
+          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr"/>
@@ -7664,29 +7664,25 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>list_type_info_alert_title</t>
+          <t>list_type_info_verb</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>List Types</t>
+          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Tipos de lista</t>
+          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Types de liste</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>New info icon next to the List type label</t>
-        </is>
-      </c>
+          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7701,25 +7697,29 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>list_type_info_vocab</t>
+          <t>save_input_placeholder_new</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
+          <t>Name this list</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
+          <t>Nombra esta lista</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr"/>
+          <t>Nomme cette liste</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7734,25 +7734,29 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>list_type_info_verb</t>
+          <t>save_input_placeholder_update</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
+          <t>List name (updates it)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
+          <t>Nombre de la lista (la actualiza)</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr"/>
+          <t>Nom de la liste (la met à jour)</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Placeholder shown once the list is already saved — shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7767,27 +7771,27 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>save_input_placeholder_new</t>
+          <t>remove_word_icon</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Name this list</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Nombra esta lista</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Nomme cette liste</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
+          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
         </is>
       </c>
     </row>
@@ -7799,32 +7803,32 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>save_input_placeholder_update</t>
+          <t>translate_prompt_template</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>List name (updates it)</t>
+          <t>{n} line(s) looked like single word(s), not pairs — translate into:</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nombre de la lista (la actualiza)</t>
+          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Nom de la liste (la met à jour)</t>
+          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Placeholder shown once the list is already saved — shortened to fit</t>
+          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
         </is>
       </c>
     </row>
@@ -7836,34 +7840,30 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>edit_list_link</t>
+          <t>translate_button</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Editar</t>
+          <t>Traducir</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Modifier</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>New row action — loads the list into Add Words for editing instead of only Generate Quiz</t>
-        </is>
-      </c>
+          <t>Traduire</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7873,34 +7873,30 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>remove_word_icon</t>
+          <t>translating_ellipsis</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Translating…</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Traduciendo…</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
-        </is>
-      </c>
+          <t>Traduction en cours…</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7915,29 +7911,25 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>translate_prompt_template</t>
+          <t>error_translating</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>{n} line(s) looked like single word(s), not pairs — translate into:</t>
+          <t>Something went wrong translating those words.</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
+          <t>Algo salió mal al traducir esas palabras.</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7947,30 +7939,34 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>translate_button</t>
+          <t>slide1_body_updated</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Traducir</t>
+          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Traduire</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr"/>
+          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7980,30 +7976,34 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>translating_ellipsis</t>
+          <t>rename_link</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Translating…</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Traduciendo…</t>
+          <t>Cambiar nombre</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Traduction en cours…</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr"/>
+          <t>Renommer</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>New — separates renaming an already-saved list from saving its pairs</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8013,30 +8013,34 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>error_translating</t>
+          <t>rename_save_button</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Something went wrong translating those words.</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Algo salió mal al traducir esas palabras.</t>
+          <t>Guardar</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr"/>
+          <t>Enregistrer</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Inline rename confirm button</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8046,32 +8050,32 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>slide1_body_updated</t>
+          <t>rename_cancel_button</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+          <t>Annuler</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+          <t>Inline rename cancel button</t>
         </is>
       </c>
     </row>
@@ -8088,29 +8092,25 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>rename_link</t>
+          <t>error_renaming</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Something went wrong renaming.</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cambiar nombre</t>
+          <t>Algo salió mal al cambiar el nombre.</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Renommer</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>New — separates renaming an already-saved list from saving its pairs</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du renommage.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8125,27 +8125,27 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>rename_save_button</t>
+          <t>save_changes_button</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Save Changes</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Guardar</t>
+          <t>Guardar cambios</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Enregistrer</t>
+          <t>Enregistrer les modifications</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Inline rename confirm button</t>
+          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
         </is>
       </c>
     </row>
@@ -8162,27 +8162,27 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>rename_cancel_button</t>
+          <t>list_type_locked_label</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>List type (locked)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Tipo de lista (bloqueado)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Type de liste (verrouillé)</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Inline rename cancel button</t>
+          <t>Appended to the label once a list is saved — type can't change after first save</t>
         </is>
       </c>
     </row>
@@ -8199,25 +8199,29 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>error_renaming</t>
+          <t>list_type_locked_explanation</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Something went wrong renaming.</t>
+          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Algo salió mal al cambiar el nombre.</t>
+          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du renommage.</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr"/>
+          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Appended to the existing List Types info alert once locked</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8227,32 +8231,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>save_changes_button</t>
+          <t>past_quizzes_section_title</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Save Changes</t>
+          <t>Past Quizzes</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Guardar cambios</t>
+          <t>Cuestionarios anteriores</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Enregistrer les modifications</t>
+          <t>Quiz précédents</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
+          <t>New section showing completed quiz history, fetched from GET /quiz-sessions/completed</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8268,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>list_type_locked_label</t>
+          <t>no_past_quizzes</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>List type (locked)</t>
+          <t>No completed quizzes yet.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Tipo de lista (bloqueado)</t>
+          <t>Aún no hay cuestionarios completados.</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Type de liste (verrouillé)</t>
+          <t>Aucun quiz terminé pour l'instant.</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Appended to the label once a list is saved — type can't change after first save</t>
+          <t>Renamed from no_completed_quizzes — collided with list-history.tsx's key of the same name</t>
         </is>
       </c>
     </row>
@@ -8301,32 +8305,32 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>list_type_locked_explanation</t>
+          <t>past_quiz_score_template</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
+          <t>{correct}/{total} correct ({pct}%)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
+          <t>{correct}/{total} correctas ({pct}%)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+          <t>{correct}/{total} correctes ({pct} %)</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Appended to the existing List Types info alert once locked</t>
+          <t>Template</t>
         </is>
       </c>
     </row>
@@ -8343,27 +8347,27 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>past_quizzes_section_title</t>
+          <t>deleted_list_fallback</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Past Quizzes</t>
+          <t>Deleted list</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Cuestionarios anteriores</t>
+          <t>Lista eliminada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Quiz précédents</t>
+          <t>Liste supprimée</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>New section showing completed quiz history, fetched from GET /quiz-sessions/completed</t>
+          <t>Shown when a past quiz's list no longer exists</t>
         </is>
       </c>
     </row>
@@ -8375,32 +8379,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>no_past_quizzes</t>
+          <t>discard_unsaved_alert_title</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>No completed quizzes yet.</t>
+          <t>Discard unsaved words?</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aún no hay cuestionarios completados.</t>
+          <t>¿Descartar palabras sin guardar?</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Aucun quiz terminé pour l'instant.</t>
+          <t>Abandonner les mots non enregistrés ?</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Renamed from no_completed_quizzes — collided with list-history.tsx's key of the same name</t>
+          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
         </is>
       </c>
     </row>
@@ -8412,34 +8416,30 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>past_quiz_score_template</t>
+          <t>discard_unsaved_alert_message</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>{correct}/{total} correct ({pct}%)</t>
+          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctas ({pct}%)</t>
+          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctes ({pct} %)</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8449,32 +8449,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>deleted_list_fallback</t>
+          <t>leave_without_saving</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Deleted list</t>
+          <t>Leave Without Saving</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Lista eliminada</t>
+          <t>Salir sin guardar</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Liste supprimée</t>
+          <t>Quitter sans enregistrer</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Shown when a past quiz's list no longer exists</t>
+          <t>Destructive confirm action</t>
         </is>
       </c>
     </row>
@@ -8486,32 +8486,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>language-order-confirm.tsx</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_title</t>
+          <t>order_confirm_prompt_template</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Discard unsaved words?</t>
+          <t>Detected {first} and {second}. Which one do you already know?</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>¿Descartar palabras sin guardar?</t>
+          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Abandonner les mots non enregistrés ?</t>
+          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
+          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
         </is>
       </c>
     </row>
@@ -8523,30 +8523,34 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>language-order-confirm.tsx</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_message</t>
+          <t>order_confirm_option_template</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
+          <t>I know {language}</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
+          <t>Ya sé {language}</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr"/>
+          <t>Je connais déjà {language}</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Two buttons, one per detected language</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8556,32 +8560,32 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>leave_without_saving</t>
+          <t>source_word_placeholder_dynamic</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Leave Without Saving</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Salir sin guardar</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Quitter sans enregistrer</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Destructive confirm action</t>
+          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
         </is>
       </c>
     </row>
@@ -8593,32 +8597,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>order_confirm_prompt_template</t>
+          <t>target_word_placeholder_dynamic</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Detected {first} and {second}. Which one do you already know?</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
+          <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
         </is>
       </c>
     </row>
@@ -8630,32 +8634,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>order_confirm_option_template</t>
+          <t>app_language_title</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>I know {language}</t>
+          <t>App Language</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Ya sé {language}</t>
+          <t>Idioma de la app</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Je connais déjà {language}</t>
+          <t>Langue de l'application</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Two buttons, one per detected language</t>
+          <t>New — the UI locale picker itself, part of building the actual i18n layer</t>
         </is>
       </c>
     </row>
@@ -8667,32 +8671,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>source_word_placeholder_dynamic</t>
+          <t>list_type_label</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Word in {language}</t>
+          <t>List type</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Palabra en {language}</t>
+          <t>Tipo de lista</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mot en {language}</t>
+          <t>Type de liste</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
+          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
         </is>
       </c>
     </row>
@@ -8704,32 +8708,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>add-words.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>target_word_placeholder_dynamic</t>
+          <t>select_label</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Word in {language}</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Palabra en {language}</t>
+          <t>Seleccionar</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Mot en {language}</t>
+          <t>Sélectionner</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
+          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8741,32 +8745,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>app_language_title</t>
+          <t>done_label</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>App Language</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Idioma de la app</t>
+          <t>Listo</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Langue de l'application</t>
+          <t>Terminé</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>New — the UI locale picker itself, part of building the actual i18n layer</t>
+          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8778,32 +8782,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>list_type_label</t>
+          <t>select_all_label</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>List type</t>
+          <t>Select All</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Tipo de lista</t>
+          <t>Seleccionar todo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Type de liste</t>
+          <t>Tout sélectionner</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8820,27 +8824,27 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>select_label</t>
+          <t>deselect_all_label</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Deselect All</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Seleccionar</t>
+          <t>Deseleccionar todo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sélectionner</t>
+          <t>Tout désélectionner</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8857,27 +8861,27 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>done_label</t>
+          <t>error_deleting_lists_bulk</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Something went wrong deleting those lists.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Listo</t>
+          <t>Algo salió mal al eliminar esas listas.</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
+          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
         </is>
       </c>
     </row>
@@ -8889,32 +8893,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>select_all_label</t>
+          <t>error_deleting_quizzes_bulk</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Select All</t>
+          <t>Something went wrong deleting those quizzes.</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Seleccionar todo</t>
+          <t>Algo salió mal al eliminar esos cuestionarios.</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tout sélectionner</t>
+          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
         </is>
       </c>
     </row>
@@ -8931,27 +8935,27 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>deselect_all_label</t>
+          <t>loading_ellipsis</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Deselect All</t>
+          <t>Loading…</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deseleccionar todo</t>
+          <t>Cargando…</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tout désélectionner</t>
+          <t>Chargement…</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+          <t>Reused wherever a screen shows a generic loading state</t>
         </is>
       </c>
     </row>
@@ -8963,34 +8967,30 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>login.tsx</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>sample_list_type_verb_singular</t>
+          <t>forgot_password_link</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>Forgot password?</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Verbo</t>
+          <t>¿Olvidaste tu contraseña?</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Verbe</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Singular form for the sample-list card title ("Verb {count}"), distinct from sample_list_type_verbs ("Verbs", used elsewhere)</t>
-        </is>
-      </c>
+          <t>Mot de passe oublié ?</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9000,34 +9000,30 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>error_deleting_lists_bulk</t>
+          <t>forgot_password_title</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Something went wrong deleting those lists.</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esas listas.</t>
+          <t>Contraseña olvidada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
-        </is>
-      </c>
+          <t>Mot de passe oublié</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9037,32 +9033,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>error_deleting_quizzes_bulk</t>
+          <t>forgot_password_sent_message</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Something went wrong deleting those quizzes.</t>
+          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esos cuestionarios.</t>
+          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
+          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
+          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
         </is>
       </c>
     </row>
@@ -9074,34 +9070,30 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>loading_ellipsis</t>
+          <t>forgot_password_instructions</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Loading…</t>
+          <t>Enter your email and we'll send you a link to reset your password.</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cargando…</t>
+          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Chargement…</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Reused wherever a screen shows a generic loading state</t>
-        </is>
-      </c>
+          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9111,27 +9103,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>login.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>forgot_password_link</t>
+          <t>sending_ellipsis</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Forgot password?</t>
+          <t>Sending…</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>¿Olvidaste tu contraseña?</t>
+          <t>Enviando…</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mot de passe oublié ?</t>
+          <t>Envoi en cours…</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
@@ -9149,22 +9141,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>forgot_password_title</t>
+          <t>send_reset_link</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Send Reset Link</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Contraseña olvidada</t>
+          <t>Enviar enlace de restablecimiento</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Mot de passe oublié</t>
+          <t>Envoyer le lien de réinitialisation</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -9177,34 +9169,30 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>forgot_password_sent_message</t>
+          <t>reset_password_title</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
+          <t>Restablecer contraseña</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
-        </is>
-      </c>
+          <t>Réinitialiser le mot de passe</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9214,27 +9202,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>forgot_password_instructions</t>
+          <t>reset_link_invalid_message</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Enter your email and we'll send you a link to reset your password.</t>
+          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
+          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
+          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
@@ -9247,27 +9235,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>sending_ellipsis</t>
+          <t>set_new_password_title</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Sending…</t>
+          <t>Set a New Password</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Enviando…</t>
+          <t>Establece una nueva contraseña</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Envoi en cours…</t>
+          <t>Définis un nouveau mot de passe</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
@@ -9280,27 +9268,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>send_reset_link</t>
+          <t>new_password_placeholder</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Send Reset Link</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Enviar enlace de restablecimiento</t>
+          <t>Nueva contraseña</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Envoyer le lien de réinitialisation</t>
+          <t>Nouveau mot de passe</t>
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
@@ -9318,22 +9306,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>reset_password_title</t>
+          <t>save_new_password</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>Save New Password</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Restablecer contraseña</t>
+          <t>Guardar nueva contraseña</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Réinitialiser le mot de passe</t>
+          <t>Enregistrer le nouveau mot de passe</t>
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
@@ -9346,30 +9334,34 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>reset_link_invalid_message</t>
+          <t>sort_by_added_order</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
+          <t>Order Added</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
+          <t>Orden de añadido</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr"/>
+          <t>Ordre d'ajout</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Word-list sort option — mirrors My Lists' sort-by pattern; default order (insertion order)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9379,27 +9371,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>set_new_password_title</t>
+          <t>bulk_delete_words_alert_title</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Set a New Password</t>
+          <t>Delete Words</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Establece una nueva contraseña</t>
+          <t>Eliminar palabras</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Définis un nouveau mot de passe</t>
+          <t>Supprimer les mots</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
@@ -9412,30 +9404,34 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>new_password_placeholder</t>
+          <t>bulk_delete_words_alert_message_template</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Delete {count} word(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Nueva contraseña</t>
+          <t>¿Eliminar {count} palabra(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Nouveau mot de passe</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr"/>
+          <t>Supprimer {count} mot(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9445,30 +9441,281 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>save_new_password</t>
+          <t>sample_category_common_words</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Save New Password</t>
+          <t>Common Words</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Guardar nueva contraseña</t>
+          <t>Palabras comunes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Enregistrer le nouveau mot de passe</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr"/>
+          <t>Mots courants</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Sample-list category label</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sample_category_common_verbs</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Common Verbs</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Verbos comunes</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Verbes courants</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Sample-list category label</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>sample_category_irregular_verbs</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Irregular Verbs</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Verbos irregulares</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Verbes irréguliers</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Sample-list category label — new dedicated dataset, distinct from Common Verbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>sample_category_food</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Food Words</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Palabras de comida</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Mots de nourriture</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Sample-list category label — new dedicated dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>learning_pair_title</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>What are you learning?</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>¿Qué estás aprendiendo?</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Qu'apprends-tu ?</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>learning_pair_hint</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Sets your default language pair and unlocks a few ready-made starter lists.</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Establece tu par de idiomas por defecto y desbloquea algunas listas iniciales ya preparadas.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Définit ta paire de langues par défaut et débloque quelques listes de départ prêtes à l'emploi.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>generating_starter_lists</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Setting up your starter lists…</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Preparando tus listas iniciales…</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Préparation de tes listes de départ…</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Shown while the first-time PATCH /me/profile call is generating sample lists via Gemini</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>starter_lists_ready_message</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Your starter lists are ready — check My Lists!</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>¡Tus listas iniciales ya están listas — échales un vistazo en Mis listas!</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Tes listes de départ sont prêtes — jette un œil dans Mes listes !</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3215,29 +3215,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>default_level_hint</t>
+          <t>auto_delete_toggle</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Used for new quizzes — you can still change it for any single quiz when generating it.</t>
+          <t>Auto-delete completed quizzes after 30 days</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Se usa para nuevos cuestionarios — puedes cambiarlo para cualquier cuestionario individual al generarlo.</t>
+          <t>Eliminar automáticamente los cuestionarios completados después de 30 días</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Utilisé pour les nouveaux quiz — tu peux toujours le modifier pour un quiz donné au moment de le générer.</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Wording synced to match current app text exactly</t>
-        </is>
-      </c>
+          <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3252,22 +3248,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>auto_delete_toggle</t>
+          <t>adaptive_quizzes_toggle</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Auto-delete completed quizzes after 30 days</t>
+          <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eliminar automáticamente los cuestionarios completados después de 30 días</t>
+          <t>Cuestionarios adaptativos — comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
+          <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -3280,27 +3276,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>quiz.tsx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_toggle</t>
+          <t>your_answer_placeholder</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Adaptive quizzes — feedback on patterns you struggle with, and an option to target them</t>
+          <t>Your answer</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cuestionarios adaptativos — comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+          <t>Tu respuesta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+          <t>Ta réponse</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3318,22 +3314,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>your_answer_placeholder</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Your answer</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tu respuesta</t>
+          <t>Enviar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ta réponse</t>
+          <t>Valider</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3351,22 +3347,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>skip_question</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Skip this question</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Enviar</t>
+          <t>Saltar esta pregunta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Valider</t>
+          <t>Passer cette question</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3384,22 +3380,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>skip_question</t>
+          <t>hide_word_list</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Skip this question</t>
+          <t>Hide word list</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saltar esta pregunta</t>
+          <t>Ocultar lista de palabras</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Passer cette question</t>
+          <t>Masquer la liste de mots</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3417,22 +3413,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>hide_word_list</t>
+          <t>stuck_see_word_list</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Hide word list</t>
+          <t>Stuck? See the word list</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ocultar lista de palabras</t>
+          <t>¿Atascado? Consulta la lista de palabras</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Masquer la liste de mots</t>
+          <t>Bloqué ? Consulte la liste de mots</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -3450,25 +3446,29 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>stuck_see_word_list</t>
+          <t>your_answer_was</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Stuck? See the word list</t>
+          <t>Your answer: {answer}</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>¿Atascado? Consulta la lista de palabras</t>
+          <t>Tu respuesta: {answer}</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bloqué ? Consulte la liste de mots</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>Ta réponse : {answer}</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3483,29 +3483,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>your_answer_was</t>
+          <t>correct_feedback</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Your answer: {answer}</t>
+          <t>That's correct!</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tu respuesta: {answer}</t>
+          <t>¡Correcto!</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ta réponse : {answer}</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>C'est correct !</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3520,25 +3516,29 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>correct_feedback</t>
+          <t>incorrect_feedback</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>That's correct!</t>
+          <t>Sorry, that's incorrect. The answer was: {answer}</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>¡Correcto!</t>
+          <t>Lo siento, es incorrecto. La respuesta era: {answer}</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C'est correct !</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>Désolé, c'est incorrect. La réponse était : {answer}</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3553,29 +3553,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>incorrect_feedback</t>
+          <t>finish_quiz</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sorry, that's incorrect. The answer was: {answer}</t>
+          <t>Finish Quiz</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lo siento, es incorrecto. La respuesta era: {answer}</t>
+          <t>Finalizar cuestionario</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Désolé, c'est incorrect. La réponse était : {answer}</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Terminer le quiz</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3590,22 +3586,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>finish_quiz</t>
+          <t>next_question</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Finish Quiz</t>
+          <t>Next Question</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Finalizar cuestionario</t>
+          <t>Siguiente pregunta</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Terminer le quiz</t>
+          <t>Question suivante</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -3618,27 +3614,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>quiz.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>next_question</t>
+          <t>quiz_complete_title</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Next Question</t>
+          <t>Quiz Complete!</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Siguiente pregunta</t>
+          <t>¡Cuestionario completado!</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Question suivante</t>
+          <t>Quiz terminé !</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -3656,25 +3652,29 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>quiz_complete_title</t>
+          <t>score_correct</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Quiz Complete!</t>
+          <t>{n} / {total} correct</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>¡Cuestionario completado!</t>
+          <t>{n} / {total} correctas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Quiz terminé !</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>{n} / {total} correctes</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3689,29 +3689,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>score_correct</t>
+          <t>back_to_home</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{n} / {total} correct</t>
+          <t>Back to Home</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>{n} / {total} correctas</t>
+          <t>Volver al inicio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{n} / {total} correctes</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Retour à l'accueil</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3721,27 +3717,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>back_to_home</t>
+          <t>undo_last</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Back to Home</t>
+          <t>Undo last</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Volver al inicio</t>
+          <t>Deshacer última</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Retour à l'accueil</t>
+          <t>Annuler le dernier</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -3759,22 +3755,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>undo_last</t>
+          <t>clear_list</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Undo last</t>
+          <t>Clear list</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deshacer última</t>
+          <t>Vaciar lista</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Annuler le dernier</t>
+          <t>Vider la liste</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -3792,22 +3788,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>clear_list</t>
+          <t>no_words_added</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Clear list</t>
+          <t>No words added yet.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vaciar lista</t>
+          <t>Aún no has añadido palabras.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vider la liste</t>
+          <t>Aucun mot ajouté pour l'instant.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -3825,22 +3821,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>no_words_added</t>
+          <t>list_name_update_placeholder</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>No words added yet.</t>
+          <t>List name (saving updates it)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aún no has añadido palabras.</t>
+          <t>Nombre de la lista (al guardar se actualiza)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Aucun mot ajouté pour l'instant.</t>
+          <t>Nom de la liste (l'enregistrement la met à jour)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -3858,22 +3854,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>list_name_update_placeholder</t>
+          <t>list_name_placeholder</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>List name (saving updates it)</t>
+          <t>List name</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nombre de la lista (al guardar se actualiza)</t>
+          <t>Nombre de la lista</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nom de la liste (l'enregistrement la met à jour)</t>
+          <t>Nom de la liste</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -3891,22 +3887,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>list_name_placeholder</t>
+          <t>saving_ellipsis</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>List name</t>
+          <t>Saving…</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nombre de la lista</t>
+          <t>Guardando…</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nom de la liste</t>
+          <t>Enregistrement…</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -3924,22 +3920,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>saving_ellipsis</t>
+          <t>save_list</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Saving…</t>
+          <t>Save List</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Guardando…</t>
+          <t>Guardar lista</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Enregistrement…</t>
+          <t>Enregistrer la liste</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -3957,22 +3953,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>save_list</t>
+          <t>saved_message</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Save List</t>
+          <t>Saved!</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Guardar lista</t>
+          <t>¡Guardado!</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Enregistrer la liste</t>
+          <t>Enregistré !</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -3990,22 +3986,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>saved_message</t>
+          <t>error_saving</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Saved!</t>
+          <t>Something went wrong saving.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>¡Guardado!</t>
+          <t>Algo salió mal al guardar.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Enregistré !</t>
+          <t>Une erreur s'est produite lors de l'enregistrement.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -4023,25 +4019,29 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>error_saving</t>
+          <t>add_more_words_to_quiz</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Something went wrong saving.</t>
+          <t>Add {n} more word(s) to generate a quiz</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Algo salió mal al guardar.</t>
+          <t>Añade {n} palabra(s) más para generar un cuestionario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'enregistrement.</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+          <t>Ajoute {n} mot(s) de plus pour générer un quiz</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Template with pluralization</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4056,27 +4056,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>add_more_words_to_quiz</t>
+          <t>generate_quiz_button</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Add {n} more word(s) to generate a quiz</t>
+          <t>Generate Quiz</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Añade {n} palabra(s) más para generar un cuestionario</t>
+          <t>Generar cuestionario</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ajoute {n} mot(s) de plus pour générer un quiz</t>
+          <t>Générer un quiz</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Template with pluralization</t>
+          <t>Reused label</t>
         </is>
       </c>
     </row>
@@ -4093,22 +4093,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>generate_quiz_button</t>
+          <t>my_lists_link</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Generate Quiz</t>
+          <t>My Lists</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Generar cuestionario</t>
+          <t>Mis listas</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Générer un quiz</t>
+          <t>Mes listes</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4125,32 +4125,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>my_lists_link</t>
+          <t>level_label</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>My Lists</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mis listas</t>
+          <t>Nivel</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mes listes</t>
+          <t>Niveau</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Reused label</t>
+          <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>language-picker.tsx</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>level_label</t>
+          <t>from_label</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>From</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nivel</t>
+          <t>Desde</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Niveau</t>
+          <t>Depuis</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CEFR codes (A1, B2, etc.) are standard notation, not translated</t>
+          <t>Replaces "I already know" — short label translates cleanly, standard in translation-app pickers (Google Translate, Duolingo-style)</t>
         </is>
       </c>
     </row>
@@ -4204,27 +4204,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>from_label</t>
+          <t>to_label</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>From</t>
+          <t>To</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Desde</t>
+          <t>Hacia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Depuis</t>
+          <t>Vers</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Replaces "I already know" — short label translates cleanly, standard in translation-app pickers (Google Translate, Duolingo-style)</t>
+          <t>Replaces "I'm learning" — same reasoning</t>
         </is>
       </c>
     </row>
@@ -4241,27 +4241,27 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>to_label</t>
+          <t>language_names</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>To</t>
+          <t>English / Español / Français</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hacia</t>
+          <t>English / Español / Français</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vers</t>
+          <t>English / Español / Français</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Replaces "I'm learning" — same reasoning</t>
+          <t>Decided: always shown in each language's own native form, regardless of current UI language (matches iOS Settings/Duolingo convention) — not translated per UI language, so all three columns are identical on purpose</t>
         </is>
       </c>
     </row>
@@ -4273,32 +4273,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>language-picker.tsx</t>
+          <t>parsing-warning.tsx</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>language_names</t>
+          <t>parsing_warning_text</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>English / Español / Français</t>
+          <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>English / Español / Français</t>
+          <t>El análisis puede cometer errores con formatos inusuales. Para mejores resultados, prueba subir una foto en su lugar.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>English / Español / Français</t>
+          <t>L'analyse peut faire des erreurs avec une mise en forme inhabituelle. Pour de meilleurs résultats, essaie plutôt d'importer une photo.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Decided: always shown in each language's own native form, regardless of current UI language (matches iOS Settings/Duolingo convention) — not translated per UI language, so all three columns are identical on purpose</t>
+          <t>Contains an inline link to Share a Picture</t>
         </is>
       </c>
     </row>
@@ -4310,32 +4310,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>parsing-warning.tsx</t>
+          <t>quiz-feedback.ts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>parsing_warning_text</t>
+          <t>trend_improving_a_lot_1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Parsing can make mistakes with unusual formatting. For best results, try Share a Picture instead.</t>
+          <t>Great progress! Your scores are climbing fast — keep it up.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>El análisis puede cometer errores con formatos inusuales. Para mejores resultados, prueba subir una foto en su lugar.</t>
+          <t>¡Gran progreso! Tus puntuaciones están subiendo rápido — sigue así.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>L'analyse peut faire des erreurs avec une mise en forme inhabituelle. Pour de meilleurs résultats, essaie plutôt d'importer une photo.</t>
+          <t>Beaux progrès ! Tes scores grimpent rapidement — continue comme ça.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Contains an inline link to Share a Picture</t>
+          <t>5 message variants, picked at random each screen load</t>
         </is>
       </c>
     </row>
@@ -4352,29 +4352,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot_1</t>
+          <t>trend_improving_a_lot_2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Great progress! Your scores are climbing fast — keep it up.</t>
+          <t>You're on a roll — your recent scores are way up from where you started.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>¡Gran progreso! Tus puntuaciones están subiendo rápido — sigue así.</t>
+          <t>Estás en racha — tus puntuaciones recientes están muy por encima de donde empezaste.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Beaux progrès ! Tes scores grimpent rapidement — continue comme ça.</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>5 message variants, picked at random each screen load</t>
-        </is>
-      </c>
+          <t>Tu es en pleine lancée — tes scores récents sont bien au-dessus de ton point de départ.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4389,22 +4385,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot_2</t>
+          <t>trend_improving_a_lot_3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>You're on a roll — your recent scores are way up from where you started.</t>
+          <t>Big jump in your scores lately. Whatever you're doing, keep doing it.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Estás en racha — tus puntuaciones recientes están muy por encima de donde empezaste.</t>
+          <t>Gran salto en tus puntuaciones últimamente. Sigue haciendo lo que estás haciendo.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tu es en pleine lancée — tes scores récents sont bien au-dessus de ton point de départ.</t>
+          <t>Gros bond dans tes scores dernièrement. Continue comme ça, quoi que tu fasses.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -4422,22 +4418,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot_3</t>
+          <t>trend_improving_a_lot_4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Big jump in your scores lately. Whatever you're doing, keep doing it.</t>
+          <t>Your accuracy has shot up recently — this list is really clicking.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gran salto en tus puntuaciones últimamente. Sigue haciendo lo que estás haciendo.</t>
+          <t>Tu precisión ha subido mucho últimamente — esta lista te está funcionando de verdad.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gros bond dans tes scores dernièrement. Continue comme ça, quoi que tu fasses.</t>
+          <t>Ta précision a beaucoup augmenté récemment — cette liste porte vraiment ses fruits.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -4455,22 +4451,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot_4</t>
+          <t>trend_improving_a_lot_5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Your accuracy has shot up recently — this list is really clicking.</t>
+          <t>Strong improvement here — you've clearly been putting in the reps.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tu precisión ha subido mucho últimamente — esta lista te está funcionando de verdad.</t>
+          <t>Gran mejora aquí — claramente has estado practicando bastante.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ta précision a beaucoup augmenté récemment — cette liste porte vraiment ses fruits.</t>
+          <t>Belle amélioration ici — on voit que tu t'es beaucoup entraîné.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -4488,25 +4484,29 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>trend_improving_a_lot_5</t>
+          <t>trend_improving_1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Strong improvement here — you've clearly been putting in the reps.</t>
+          <t>You're improving steadily on this list.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gran mejora aquí — claramente has estado practicando bastante.</t>
+          <t>Estás mejorando de forma constante en esta lista.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Belle amélioration ici — on voit que tu t'es beaucoup entraîné.</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+          <t>Tu progresses régulièrement sur cette liste.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>5 message variants, picked at random each screen load</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4521,29 +4521,25 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>trend_improving_1</t>
+          <t>trend_improving_2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>You're improving steadily on this list.</t>
+          <t>Nice — your scores are trending upward little by little.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Estás mejorando de forma constante en esta lista.</t>
+          <t>Bien — tus puntuaciones van subiendo poco a poco.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tu progresses régulièrement sur cette liste.</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>5 message variants, picked at random each screen load</t>
-        </is>
-      </c>
+          <t>Bien joué — tes scores augmentent petit à petit.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4558,22 +4554,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>trend_improving_2</t>
+          <t>trend_improving_3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Nice — your scores are trending upward little by little.</t>
+          <t>Steady gains here. Keep at it and it'll keep paying off.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bien — tus puntuaciones van subiendo poco a poco.</t>
+          <t>Avances constantes aquí. Sigue así y seguirá dando resultado.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bien joué — tes scores augmentent petit à petit.</t>
+          <t>Des progrès constants ici. Continue et ça continuera à payer.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -4591,22 +4587,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>trend_improving_3</t>
+          <t>trend_improving_4</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Steady gains here. Keep at it and it'll keep paying off.</t>
+          <t>You're getting a bit better each time you quiz this list.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Avances constantes aquí. Sigue así y seguirá dando resultado.</t>
+          <t>Vas mejorando un poco cada vez que haces el cuestionario de esta lista.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Des progrès constants ici. Continue et ça continuera à payer.</t>
+          <t>Tu t'améliores un peu à chaque fois que tu fais le quiz sur cette liste.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -4624,22 +4620,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>trend_improving_4</t>
+          <t>trend_improving_5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>You're getting a bit better each time you quiz this list.</t>
+          <t>Solid upward trend — the practice is paying off.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vas mejorando un poco cada vez que haces el cuestionario de esta lista.</t>
+          <t>Tendencia claramente positiva — la práctica está dando resultado.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tu t'améliores un peu à chaque fois que tu fais le quiz sur cette liste.</t>
+          <t>Tendance clairement à la hausse — l'entraînement porte ses fruits.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -4657,25 +4653,29 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>trend_improving_5</t>
+          <t>trend_steady_1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Solid upward trend — the practice is paying off.</t>
+          <t>Your scores are holding steady. Try focusing on the words you keep missing.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tendencia claramente positiva — la práctica está dando resultado.</t>
+          <t>Tus puntuaciones se mantienen estables. Intenta enfocarte en las palabras que sigues fallando.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tendance clairement à la hausse — l'entraînement porte ses fruits.</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
+          <t>Tes scores restent stables. Essaie de te concentrer sur les mots que tu rates encore.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>5 message variants, picked at random each screen load</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4690,29 +4690,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>trend_steady_1</t>
+          <t>trend_steady_2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Your scores are holding steady. Try focusing on the words you keep missing.</t>
+          <t>You're consistent on this list — a few more reps on the tricky words could push you higher.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tus puntuaciones se mantienen estables. Intenta enfocarte en las palabras que sigues fallando.</t>
+          <t>Eres constante en esta lista — unas repeticiones más en las palabras difíciles podrían subirte el nivel.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tes scores restent stables. Essaie de te concentrer sur les mots que tu rates encore.</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>5 message variants, picked at random each screen load</t>
-        </is>
-      </c>
+          <t>Tu es régulier sur cette liste — quelques répétitions de plus sur les mots difficiles pourraient te faire progresser.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4727,22 +4723,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>trend_steady_2</t>
+          <t>trend_steady_3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>You're consistent on this list — a few more reps on the tricky words could push you higher.</t>
+          <t>Not much movement lately. Worth a look at which specific words trip you up.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Eres constante en esta lista — unas repeticiones más en las palabras difíciles podrían subirte el nivel.</t>
+          <t>No ha habido mucho cambio últimamente. Vale la pena ver qué palabras concretas te cuestan.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tu es régulier sur cette liste — quelques répétitions de plus sur les mots difficiles pourraient te faire progresser.</t>
+          <t>Pas beaucoup de changement dernièrement. Ça vaut le coup de voir quels mots précis te posent problème.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -4760,22 +4756,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>trend_steady_3</t>
+          <t>trend_steady_4</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Not much movement lately. Worth a look at which specific words trip you up.</t>
+          <t>Holding steady for now — try mixing in the word list reveal less to really test recall.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>No ha habido mucho cambio últimamente. Vale la pena ver qué palabras concretas te cuestan.</t>
+          <t>Se mantiene estable por ahora — intenta usar menos la lista de palabras visible para poner a prueba tu memoria de verdad.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pas beaucoup de changement dernièrement. Ça vaut le coup de voir quels mots précis te posent problème.</t>
+          <t>Ça reste stable pour l'instant — essaie de moins t'appuyer sur la liste de mots visible pour vraiment tester ta mémoire.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -4793,22 +4789,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>trend_steady_4</t>
+          <t>trend_steady_5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Holding steady for now — try mixing in the word list reveal less to really test recall.</t>
+          <t>Your scores are level. A quick review of your weaker words might get things moving again.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Se mantiene estable por ahora — intenta usar menos la lista de palabras visible para poner a prueba tu memoria de verdad.</t>
+          <t>Tus puntuaciones están estables. Un repaso rápido de tus palabras más débiles podría hacer que avances de nuevo.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ça reste stable pour l'instant — essaie de moins t'appuyer sur la liste de mots visible pour vraiment tester ta mémoire.</t>
+          <t>Tes scores sont stables. Une petite révision de tes mots les plus faibles pourrait relancer ta progression.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -4826,25 +4822,29 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>trend_steady_5</t>
+          <t>trend_declining_1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Your scores are level. A quick review of your weaker words might get things moving again.</t>
+          <t>Your scores dipped a bit recently — might be worth a quick refresher.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tus puntuaciones están estables. Un repaso rápido de tus palabras más débiles podría hacer que avances de nuevo.</t>
+          <t>Tus puntuaciones han bajado un poco últimamente — podría valer la pena un repaso rápido.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tes scores sont stables. Une petite révision de tes mots les plus faibles pourrait relancer ta progression.</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>Tes scores ont légèrement baissé récemment — un petit rappel pourrait être utile.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>5 message variants, picked at random each screen load</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4859,29 +4859,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>trend_declining_1</t>
+          <t>trend_declining_2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Your scores dipped a bit recently — might be worth a quick refresher.</t>
+          <t>A small dip lately. Nothing major, just revisit this list when you get a chance.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tus puntuaciones han bajado un poco últimamente — podría valer la pena un repaso rápido.</t>
+          <t>Una pequeña bajada últimamente. Nada grave, solo repasa esta lista cuando puedas.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tes scores ont légèrement baissé récemment — un petit rappel pourrait être utile.</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>5 message variants, picked at random each screen load</t>
-        </is>
-      </c>
+          <t>Une petite baisse dernièrement. Rien de grave, revois juste cette liste quand tu as l'occasion.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4896,22 +4892,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>trend_declining_2</t>
+          <t>trend_declining_3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>A small dip lately. Nothing major, just revisit this list when you get a chance.</t>
+          <t>Scores have slipped slightly — could be worth slowing down on your next attempt.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Una pequeña bajada últimamente. Nada grave, solo repasa esta lista cuando puedas.</t>
+          <t>Las puntuaciones han bajado un poco — podría valer la pena ir más despacio en tu próximo intento.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Une petite baisse dernièrement. Rien de grave, revois juste cette liste quand tu as l'occasion.</t>
+          <t>Les scores ont légèrement chuté — ça pourrait valoir le coup de ralentir lors de ta prochaine tentative.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -4929,22 +4925,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>trend_declining_3</t>
+          <t>trend_declining_4</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Scores have slipped slightly — could be worth slowing down on your next attempt.</t>
+          <t>A bit of a dip recently. Happens — a short review session should help.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Las puntuaciones han bajado un poco — podría valer la pena ir más despacio en tu próximo intento.</t>
+          <t>Una pequeña bajada recientemente. Pasa a veces — una sesión corta de repaso debería ayudar.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Les scores ont légèrement chuté — ça pourrait valoir le coup de ralentir lors de ta prochaine tentative.</t>
+          <t>Une petite baisse récemment. Ça arrive — une courte session de révision devrait aider.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -4962,22 +4958,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>trend_declining_4</t>
+          <t>trend_declining_5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>A bit of a dip recently. Happens — a short review session should help.</t>
+          <t>Your recent scores are a little lower than before — maybe a refresher is due.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Una pequeña bajada recientemente. Pasa a veces — una sesión corta de repaso debería ayudar.</t>
+          <t>Tus puntuaciones recientes son un poco más bajas que antes — quizás toca un repaso.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Une petite baisse récemment. Ça arrive — une courte session de révision devrait aider.</t>
+          <t>Tes scores récents sont un peu plus bas qu'avant — un petit rappel serait peut-être utile.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -4995,25 +4991,29 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>trend_declining_5</t>
+          <t>trend_declining_a_lot_1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Your recent scores are a little lower than before — maybe a refresher is due.</t>
+          <t>Your scores dropped noticeably. Consider going back through this list before your next quiz.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tus puntuaciones recientes son un poco más bajas que antes — quizás toca un repaso.</t>
+          <t>Tus puntuaciones han bajado notablemente. Considera repasar esta lista antes de tu próximo cuestionario.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tes scores récents sont un peu plus bas qu'avant — un petit rappel serait peut-être utile.</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
+          <t>Tes scores ont nettement baissé. Pense à revoir cette liste avant ton prochain quiz.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>5 message variants, picked at random each screen load</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5028,29 +5028,25 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot_1</t>
+          <t>trend_declining_a_lot_2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Your scores dropped noticeably. Consider going back through this list before your next quiz.</t>
+          <t>A bigger drop than usual — this list might need a real refresher before your next attempt.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tus puntuaciones han bajado notablemente. Considera repasar esta lista antes de tu próximo cuestionario.</t>
+          <t>Una bajada mayor de lo habitual — esta lista podría necesitar un repaso serio antes de tu próximo intento.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tes scores ont nettement baissé. Pense à revoir cette liste avant ton prochain quiz.</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>5 message variants, picked at random each screen load</t>
-        </is>
-      </c>
+          <t>Une baisse plus importante que d'habitude — cette liste aurait peut-être besoin d'une vraie révision avant ta prochaine tentative.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5065,22 +5061,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot_2</t>
+          <t>trend_declining_a_lot_3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>A bigger drop than usual — this list might need a real refresher before your next attempt.</t>
+          <t>Scores have fallen off quite a bit. Worth reviewing the list from scratch.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Una bajada mayor de lo habitual — esta lista podría necesitar un repaso serio antes de tu próximo intento.</t>
+          <t>Las puntuaciones han bajado bastante. Vale la pena repasar la lista desde cero.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Une baisse plus importante que d'habitude — cette liste aurait peut-être besoin d'une vraie révision avant ta prochaine tentative.</t>
+          <t>Les scores ont pas mal chuté. Ça vaut le coup de revoir la liste depuis le début.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -5098,22 +5094,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot_3</t>
+          <t>trend_declining_a_lot_4</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Scores have fallen off quite a bit. Worth reviewing the list from scratch.</t>
+          <t>That's a steep dip — might help to slow down and review before quizzing again.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Las puntuaciones han bajado bastante. Vale la pena repasar la lista desde cero.</t>
+          <t>Es una caída pronunciada — podría ayudar ir más despacio y repasar antes de volver a hacer el cuestionario.</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Les scores ont pas mal chuté. Ça vaut le coup de revoir la liste depuis le début.</t>
+          <t>C'est une chute assez marquée — ralentir et réviser avant de refaire le quiz pourrait aider.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5131,22 +5127,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot_4</t>
+          <t>trend_declining_a_lot_5</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>That's a steep dip — might help to slow down and review before quizzing again.</t>
+          <t>A significant drop here. Don't worry, just revisit the list before jumping back in.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Es una caída pronunciada — podría ayudar ir más despacio y repasar antes de volver a hacer el cuestionario.</t>
+          <t>Una bajada importante aquí. No te preocupes, solo repasa la lista antes de volver a intentarlo.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C'est une chute assez marquée — ralentir et réviser avant de refaire le quiz pourrait aider.</t>
+          <t>Une baisse importante ici. Pas de souci, revois juste la liste avant de t'y remettre.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -5159,30 +5155,26 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>quiz-feedback.ts</t>
+          <t>backend (api errors)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>trend_declining_a_lot_5</t>
+          <t>backend_error_text</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>A significant drop here. Don't worry, just revisit the list before jumping back in.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Una bajada importante aquí. No te preocupes, solo repasa la lista antes de volver a intentarlo.</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Une baisse importante ici. Pas de souci, revois juste la liste avant de t'y remettre.</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
+          <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Decided: stays English-only — these are dev-facing/edge-case errors (malformed requests, validation failures), not normal user-facing copy</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5192,26 +5184,30 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>backend (api errors)</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>backend_error_text</t>
+          <t>sample_lists_title</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Decided: stays English-only — these are dev-facing/edge-case errors (malformed requests, validation failures), not normal user-facing copy</t>
-        </is>
-      </c>
+          <t>Sample Lists</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Listas de ejemplo</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Listes types</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5226,22 +5222,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sample_lists_title</t>
+          <t>sample_lists_hint</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sample Lists</t>
+          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Listas de ejemplo</t>
+          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Listes types</t>
+          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5259,25 +5255,29 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>sample_lists_hint</t>
+          <t>sample_list_name_template</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
+          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
+          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr"/>
+          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Template — used as both display label and saved list name</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5292,29 +5292,25 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>sample_list_name_template</t>
+          <t>sample_list_add</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocab / {source} → {target} Verbs</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocabulario / {source} → {target} Verbos</t>
+          <t>Añadir</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>{source} → {target} Vocabulaire / {source} → {target} Verbes</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Template — used as both display label and saved list name</t>
-        </is>
-      </c>
+          <t>Ajouter</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5329,22 +5325,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>sample_list_add</t>
+          <t>sample_list_adding</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Adding…</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Añadir</t>
+          <t>Añadiendo…</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ajouter</t>
+          <t>Ajout en cours…</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -5362,25 +5358,29 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sample_list_adding</t>
+          <t>sample_list_added</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Adding…</t>
+          <t>Added</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Añadiendo…</t>
+          <t>Añadido</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ajout en cours…</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
+          <t>Ajouté</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5395,29 +5395,25 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sample_list_added</t>
+          <t>error_adding_sample</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Something went wrong adding that sample list.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Añadido</t>
+          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ajouté</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Shown once a list with the same name already exists; still tappable to re-sync</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5427,27 +5423,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>error_adding_sample</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Something went wrong adding that sample list.</t>
+          <t>Skip</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Algo salió mal al añadir esa lista de ejemplo.</t>
+          <t>Omitir</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
+          <t>Passer</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -5465,22 +5461,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>back</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Omitir</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Passer</t>
+          <t>Retour</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -5498,22 +5494,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Next</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Retour</t>
+          <t>Suivant</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -5531,22 +5527,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>get_started</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Get Started</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Empezar</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Suivant</t>
+          <t>Commencer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -5564,22 +5560,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>get_started</t>
+          <t>slide1_headline</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Get Started</t>
+          <t>Build Your List</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Empezar</t>
+          <t>Crea tu lista</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Commencer</t>
+          <t>Crée ta liste</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -5597,22 +5593,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>slide1_headline</t>
+          <t>slide1_body</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Build Your List</t>
+          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Crea tu lista</t>
+          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Crée ta liste</t>
+          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -5630,22 +5626,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>slide1_body</t>
+          <t>slide2_headline</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Type words, paste a list, upload a file, or snap a photo — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>Practice With Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista, sube un archivo o toma una foto — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>Practica con cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+          <t>Entraîne-toi avec des quiz adaptatifs</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -5663,22 +5659,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>slide2_headline</t>
+          <t>slide2_body</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Practice With Adaptive Quizzes</t>
+          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Practica con cuestionarios adaptativos</t>
+          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Entraîne-toi avec des quiz adaptatifs</t>
+          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -5696,22 +5692,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>slide2_body</t>
+          <t>slide3_headline</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AI generates real sentences to test you — and the more you practice, the more it targets what you're actually struggling with.</t>
+          <t>Watch Your Progress</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>La IA genera frases reales para ponerte a prueba — y cuanto más practiques, más se enfocará en lo que realmente te cuesta.</t>
+          <t>Observa tu progreso</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
+          <t>Suis ta progression</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -5729,22 +5725,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>slide3_headline</t>
+          <t>slide3_body</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Watch Your Progress</t>
+          <t>See your scores improve over time, list by list.</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Observa tu progreso</t>
+          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Suis ta progression</t>
+          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -5757,30 +5753,34 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>slide3_body</t>
+          <t>about_langreps_link</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>See your scores improve over time, list by list.</t>
+          <t>About LangReps</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Observa cómo mejoran tus resultados con el tiempo, lista por lista.</t>
+          <t>Acerca de LangReps</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
+          <t>À propos de LangReps</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Links to /onboarding to replay it manually</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5790,34 +5790,30 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>about_langreps_link</t>
+          <t>sort_by_label</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>About LangReps</t>
+          <t>Sort by</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Acerca de LangReps</t>
+          <t>Ordenar por</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>À propos de LangReps</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Links to /onboarding to replay it manually</t>
-        </is>
-      </c>
+          <t>Trier par</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5832,22 +5828,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>sort_by_label</t>
+          <t>sort_by_date</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Last Uploaded</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ordenar por</t>
+          <t>Última subida</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trier par</t>
+          <t>Dernier import</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -5865,22 +5861,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>sort_by_date</t>
+          <t>sort_by_name</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Last Uploaded</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Última subida</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dernier import</t>
+          <t>Nom</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -5898,25 +5894,29 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>sort_by_name</t>
+          <t>last_uploaded_template</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Last uploaded: {date}</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Última subida: {date}</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
+          <t>Dernier import : {date}</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5931,27 +5931,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>last_uploaded_template</t>
+          <t>sample_list_name_template_v2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Last uploaded: {date}</t>
+          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Última subida: {date}</t>
+          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dernier import : {date}</t>
+          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Superseded template — replaces the old arrow-notation naming</t>
         </is>
       </c>
     </row>
@@ -5968,27 +5968,27 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>sample_list_name_template_v2</t>
+          <t>sample_list_card_title</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{target} Vocabulary (from {source}) / {target} Verbs (from {source})</t>
+          <t>Vocab {count} / Verb {count}</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vocabulario de {target} (desde {source}) / Verbos de {target} (desde {source})</t>
+          <t>Vocabulario {count} / Verbo {count}</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vocabulaire {target} (depuis {source}) / Verbes {target} (depuis {source})</t>
+          <t>Vocabulaire {count} / Verbe {count}</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Superseded template — replaces the old arrow-notation naming</t>
+          <t>Sample-list catalog card title, replaces the old full name display</t>
         </is>
       </c>
     </row>
@@ -6005,27 +6005,27 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>sample_list_card_title</t>
+          <t>sample_list_card_flags</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Vocab {count} / Verb {count}</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Vocabulario {count} / Verbo {count}</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vocabulaire {count} / Verbe {count}</t>
+          <t>{flag} -&gt; {flag}</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sample-list catalog card title, replaces the old full name display</t>
+          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
         </is>
       </c>
     </row>
@@ -6037,34 +6037,30 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>index.tsx</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>sample_list_card_flags</t>
+          <t>signup_incentive_hint</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Sign up to save your lists and track your progress over time</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
+          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>{flag} -&gt; {flag}</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Flag emoji pair instead of spelled-out language names — sidesteps capitalization inconsistency entirely</t>
-        </is>
-      </c>
+          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6074,30 +6070,34 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>index.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>signup_incentive_hint</t>
+          <t>auto_delete_title</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sign up to save your lists and track your progress over time</t>
+          <t>Auto-Delete Old Quizzes</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Regístrate para guardar tus listas y seguir tu progreso a lo largo del tiempo</t>
+          <t>Eliminar automáticamente cuestionarios antiguos</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>Suppression automatique des anciens quiz</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>New section title</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6112,27 +6112,27 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>default_level_title</t>
+          <t>auto_delete_desc</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Default Level</t>
+          <t>Completed quizzes are removed after 30 days</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Nivel predeterminado</t>
+          <t>Los cuestionarios completados se eliminan después de 30 días</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Niveau par défaut</t>
+          <t>Les quiz terminés sont supprimés après 30 jours</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>New section title for Settings redesign (bold title + description layout)</t>
+          <t>Description moved under the bold title</t>
         </is>
       </c>
     </row>
@@ -6149,22 +6149,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>auto_delete_title</t>
+          <t>adaptive_quizzes_title</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Auto-Delete Old Quizzes</t>
+          <t>Adaptive Quizzes</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Eliminar automáticamente cuestionarios antiguos</t>
+          <t>Cuestionarios adaptativos</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Suppression automatique des anciens quiz</t>
+          <t>Quiz adaptatifs</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6186,22 +6186,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>auto_delete_desc</t>
+          <t>adaptive_quizzes_desc</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Completed quizzes are removed after 30 days</t>
+          <t>Get feedback on patterns you struggle with, and an option to target them</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Los cuestionarios completados se eliminan después de 30 días</t>
+          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Les quiz terminés sont supprimés après 30 jours</t>
+          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6223,27 +6223,27 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_title</t>
+          <t>require_accents_title</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Adaptive Quizzes</t>
+          <t>Require Diacritics</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cuestionarios adaptativos</t>
+          <t>Exigir diacríticos</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Quiz adaptatifs</t>
+          <t>Exiger les diacritiques</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>New section title</t>
+          <t>New toggle — renamed from "Require Accents"</t>
         </is>
       </c>
     </row>
@@ -6255,32 +6255,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>adaptive_quizzes_desc</t>
+          <t>your_lists_section_title</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Get feedback on patterns you struggle with, and an option to target them</t>
+          <t>Your Lists</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recibe comentarios sobre los patrones con los que tienes dificultades, y la opción de enfocarte en ellos</t>
+          <t>Tus listas</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Reçois un retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
+          <t>Tes listes</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Description moved under the bold title</t>
+          <t>New section title alongside bulk-select controls</t>
         </is>
       </c>
     </row>
@@ -6292,32 +6292,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>require_accents_title</t>
+          <t>bulk_select_toggle</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Require Diacritics</t>
+          <t>Select / Done</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Exigir diacríticos</t>
+          <t>Seleccionar / Listo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Exiger les diacritiques</t>
+          <t>Sélectionner / Terminé</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>New toggle — renamed from "Require Accents"</t>
+          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
         </is>
       </c>
     </row>
@@ -6329,32 +6329,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>require_accents_desc</t>
+          <t>bulk_select_all</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Off accepts "cafe" for "café"</t>
+          <t>Select All / Deselect All</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Desactivado acepta "cafe" en lugar de "café"</t>
+          <t>Seleccionar todo / Deseleccionar todo</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Désactivé accepte "cafe" pour "café"</t>
+          <t>Tout sélectionner / Tout désélectionner</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Off by default — grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
+          <t>Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -6371,27 +6371,27 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>your_lists_section_title</t>
+          <t>bulk_delete_selected_template</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Your Lists</t>
+          <t>Delete ({count})</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tus listas</t>
+          <t>Eliminar ({count})</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tes listes</t>
+          <t>Supprimer ({count})</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>New section title alongside bulk-select controls</t>
+          <t>Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -6408,27 +6408,27 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>bulk_select_toggle</t>
+          <t>bulk_deleting</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Select / Done</t>
+          <t>Deleting…</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Seleccionar / Listo</t>
+          <t>Eliminando…</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sélectionner / Terminé</t>
+          <t>Suppression…</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Toggles bulk-select mode in the header row — rows keep their normal content, just gain a checkbox (shared pattern, My Lists and My Quizzes)</t>
+          <t>Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -6445,29 +6445,25 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>bulk_select_all</t>
+          <t>bulk_delete_lists_alert_title</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Select All / Deselect All</t>
+          <t>Delete Lists</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Seleccionar todo / Deseleccionar todo</t>
+          <t>Eliminar listas</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tout sélectionner / Tout désélectionner</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Shared pattern, My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Supprimer les listes</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6482,29 +6478,25 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>bulk_delete_selected_template</t>
+          <t>bulk_delete_lists_alert_message_template</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Delete ({count})</t>
+          <t>Delete {count} list(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Eliminar ({count})</t>
+          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Supprimer ({count})</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Shared pattern, My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6514,34 +6506,30 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>bulk_deleting</t>
+          <t>quizzes_in_progress_count_template</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Deleting…</t>
+          <t>{count} in progress</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Eliminando…</t>
+          <t>{count} en curso</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Suppression…</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Shared pattern, My Lists and My Quizzes</t>
-        </is>
-      </c>
+          <t>{count} en cours</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6551,27 +6539,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_title</t>
+          <t>bulk_delete_quizzes_alert_title</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Delete Lists</t>
+          <t>Delete Quizzes</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Eliminar listas</t>
+          <t>Eliminar cuestionarios</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Supprimer les listes</t>
+          <t>Supprimer les quiz</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
@@ -6584,27 +6572,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>bulk_delete_lists_alert_message_template</t>
+          <t>bulk_delete_quizzes_alert_message_template</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Delete {count} list(s)? This can't be undone.</t>
+          <t>Delete {count} quiz(zes)? This can't be undone.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} lista(s)? Esta acción no se puede deshacer.</t>
+          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
+          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -6622,25 +6610,29 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>quizzes_in_progress_count_template</t>
+          <t>sort_by_last_updated</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>{count} in progress</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>{count} en curso</t>
+          <t>Última actualización</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>{count} en cours</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr"/>
+          <t>Dernière mise à jour</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6655,25 +6647,29 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_title</t>
+          <t>last_updated_template</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Delete Quizzes</t>
+          <t>Last updated: {date}</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Eliminar cuestionarios</t>
+          <t>Última actualización: {date}</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Supprimer les quiz</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr"/>
+          <t>Dernière mise à jour : {date}</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6688,25 +6684,29 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>bulk_delete_quizzes_alert_message_template</t>
+          <t>quiz_type_badge_vocab</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Delete {count} quiz(zes)? This can't be undone.</t>
+          <t>Vocab</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} cuestionario(s)? Esta acción no se puede deshacer.</t>
+          <t>Vocabulario</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
+          <t>Vocabulaire</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6721,27 +6721,27 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>sort_by_last_updated</t>
+          <t>quiz_type_badge_verb</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Last Updated</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Última actualización</t>
+          <t>Verbo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dernière mise à jour</t>
+          <t>Verbe</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>New sort option — mirrors My Lists' "Last Uploaded" pattern</t>
+          <t>Small badge next to the quiz row title</t>
         </is>
       </c>
     </row>
@@ -6753,32 +6753,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>last_updated_template</t>
+          <t>canned_feedback_mastery</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Last updated: {date}</t>
+          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Última actualización: {date}</t>
+          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dernière mise à jour : {date}</t>
+          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Template — date formatting via toLocaleDateString(), varies by device locale</t>
+          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
         </is>
       </c>
     </row>
@@ -6790,32 +6790,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>quiz_type_badge_vocab</t>
+          <t>canned_feedback_solid</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Vocab</t>
+          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vocabulario</t>
+          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vocabulaire</t>
+          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title, shows the underlying list's list_type</t>
+          <t>70-89% correct</t>
         </is>
       </c>
     </row>
@@ -6827,32 +6827,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>quiz_type_badge_verb</t>
+          <t>canned_feedback_building</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Verbo</t>
+          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Verbe</t>
+          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Small badge next to the quiz row title</t>
+          <t>40-69% correct</t>
         </is>
       </c>
     </row>
@@ -6869,27 +6869,27 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>canned_feedback_mastery</t>
+          <t>canned_feedback_struggling</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>You show mastery of the material and a good understanding of the concepts. You recall these words well and have successfully added them to your vocabulary. Keep up the good work — we suggest upping the CEFR level or training on a new list.</t>
+          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Demuestras dominio del material y una buena comprensión de los conceptos. Recuerdas bien estas palabras y las has incorporado con éxito a tu vocabulario. Sigue así — te sugerimos subir el nivel CEFR o practicar con una lista nueva.</t>
+          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tu montres une bonne maîtrise du contenu et une bonne compréhension des concepts. Tu te souviens bien de ces mots et les as intégrés avec succès à ton vocabulaire. Continue comme ça — nous te suggérons d'augmenter le niveau CECR ou de t'entraîner sur une nouvelle liste.</t>
+          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Shown when there's not yet enough history for an AI pattern insight. 90%+ correct</t>
+          <t>Below 40% correct</t>
         </is>
       </c>
     </row>
@@ -6901,32 +6901,32 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>canned_feedback_solid</t>
+          <t>cefr_info_alert_title</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>You have a solid grasp of this list — most of these words are sticking. A few are still slipping through, so one more pass at this level should lock them in before you move up or take on a new list.</t>
+          <t>CEFR Levels</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tienes un buen dominio de esta lista — la mayoría de estas palabras se te quedan. Algunas todavía se te escapan, así que una repetición más en este nivel debería fijarlas antes de subir de nivel o empezar una lista nueva.</t>
+          <t>Niveles del MCER</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tu maîtrises bien cette liste — la plupart de ces mots restent en mémoire. Quelques-uns t'échappent encore, donc un tour supplémentaire à ce niveau devrait les ancrer avant de monter de niveau ou de passer à une nouvelle liste.</t>
+          <t>Niveaux du CECR</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>70-89% correct</t>
+          <t>Alert title triggered by new info icon next to the Level label</t>
         </is>
       </c>
     </row>
@@ -6938,34 +6938,30 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>canned_feedback_building</t>
+          <t>cefr_a1_explanation</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>You're recognizing some of these words, but a good chunk aren't sticking yet. That's normal at this stage — stick with this list at the same level for now rather than adding new words.</t>
+          <t>Breakthrough — basic words and phrases for everyday needs.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Reconoces algunas de estas palabras, pero una buena parte todavía no se te queda. Eso es normal en esta etapa — sigue con esta lista en el mismo nivel por ahora en lugar de añadir palabras nuevas.</t>
+          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tu reconnais certains de ces mots, mais une bonne partie ne reste pas encore en mémoire. C'est normal à ce stade — continue avec cette liste au même niveau pour l'instant plutôt que d'ajouter de nouveaux mots.</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>40-69% correct</t>
-        </is>
-      </c>
+          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6975,34 +6971,30 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>cefr-level-picker.tsx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>canned_feedback_struggling</t>
+          <t>cefr_a2_explanation</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>This list is still tripping you up more than not — that's useful information, not a setback. Try lowering the CEFR level or running a shorter, more focused quiz on just this list before moving on.</t>
+          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Esta lista todavía te resulta difícil más veces que no — eso es información útil, no un retroceso. Intenta bajar el nivel CEFR o hacer un cuestionario más corto y enfocado solo en esta lista antes de continuar.</t>
+          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Cette liste te met encore en difficulté plus souvent qu'autrement — c'est une information utile, pas un échec. Essaie de baisser le niveau CECR ou de faire un quiz plus court et plus ciblé sur cette liste avant de continuer.</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Below 40% correct</t>
-        </is>
-      </c>
+          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7017,29 +7009,25 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>cefr_info_alert_title</t>
+          <t>cefr_b1_explanation</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>CEFR Levels</t>
+          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Niveles del MCER</t>
+          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Niveaux du CECR</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Alert title triggered by new info icon next to the Level label</t>
-        </is>
-      </c>
+          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7054,22 +7042,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>cefr_a1_explanation</t>
+          <t>cefr_b2_explanation</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Breakthrough — basic words and phrases for everyday needs.</t>
+          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Nivel de acceso — palabras y frases básicas para necesidades cotidianas.</t>
+          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
+          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
@@ -7087,22 +7075,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>cefr_a2_explanation</t>
+          <t>cefr_c1_explanation</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Waystage — simple sentences about familiar topics like family and shopping.</t>
+          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Nivel intermedio inicial — frases sencillas sobre temas familiares como la familia y las compras.</t>
+          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
+          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
@@ -7120,22 +7108,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>cefr_b1_explanation</t>
+          <t>cefr_c2_explanation</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Threshold — comfortable with everyday situations, travel, and routine topics.</t>
+          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Nivel umbral — cómodo en situaciones cotidianas, viajes y temas habituales.</t>
+          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
+          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
@@ -7148,30 +7136,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>cefr_b2_explanation</t>
+          <t>splash_title</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Vantage — can discuss general and some abstract topics with varied vocabulary.</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Nivel avanzado — puede hablar de temas generales y algo abstractos con vocabulario variado.</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
+          <t>LangReps</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7181,30 +7165,34 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>cefr_c1_explanation</t>
+          <t>splash_tagline</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Advanced — fluent, spontaneous use for social, academic, or work purposes.</t>
+          <t>Flex your language muscles.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Nivel autónomo — uso fluido y espontáneo para fines sociales, académicos o laborales.</t>
+          <t>Dale músculo a tus idiomas.</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr"/>
+          <t>Muscle tes langues.</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Replaces "Language reps that stick." ES/FR use the same fitness idiom naturally — "dar músculo a"/"muscler" both mean "to strengthen/build up" and are used metaphorically for skills (French "musclez votre anglais" is an established phrase), not just literal muscle</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7214,30 +7202,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>cefr-level-picker.tsx</t>
+          <t>app-splash.tsx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>cefr_c2_explanation</t>
+          <t>splash_copyright</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Mastery — near-native fluency with precise, nuanced expression.</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Nivel de dominio — fluidez casi nativa con una expresión precisa y matizada.</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr"/>
+          <t>© 2026 MarApps Development</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Pinned bottom-right corner</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7247,24 +7231,32 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-complete.tsx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>splash_title</t>
+          <t>see_full_results</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LangReps</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
+          <t>See Full Results</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Ver resultados completos</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Voir les résultats complets</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
+          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
         </is>
       </c>
     </row>
@@ -7276,32 +7268,32 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>splash_tagline</t>
+          <t>full_results_title</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Flex your language muscles.</t>
+          <t>Full Results</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Dale músculo a tus idiomas.</t>
+          <t>Resultados</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Muscle tes langues.</t>
+          <t>Résultats</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Replaces "Language reps that stick." ES/FR use the same fitness idiom naturally — "dar músculo a"/"muscler" both mean "to strengthen/build up" and are used metaphorically for skills (French "musclez votre anglais" is an established phrase), not just literal muscle</t>
+          <t>Dropped "completo(s)"/"complets" — redundant, the screen itself already shows the complete breakdown</t>
         </is>
       </c>
     </row>
@@ -7313,26 +7305,30 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>app-splash.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>splash_copyright</t>
+          <t>no_recorded_answers</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>© 2026 MarApps Development</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Pinned bottom-right corner</t>
-        </is>
-      </c>
+          <t>No recorded answers for this quiz.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>No hay respuestas registradas para este cuestionario.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Aucune réponse enregistrée pour ce quiz.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7342,34 +7338,30 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>quiz-complete.tsx</t>
+          <t>quiz-results.tsx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>see_full_results</t>
+          <t>your_answer_label</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>See Full Results</t>
+          <t>Your answer:</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ver resultados completos</t>
+          <t>Tu respuesta:</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Voir les résultats complets</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Link to the new quiz-results.tsx screen, only shown for saved-list quizzes (a session exists)</t>
-        </is>
-      </c>
+          <t>Ta réponse :</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7384,27 +7376,27 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>full_results_title</t>
+          <t>correct_answer_label</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Full Results</t>
+          <t>Correct answer:</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Resultados</t>
+          <t>Respuesta correcta:</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Résultats</t>
+          <t>Bonne réponse :</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dropped "completo(s)"/"complets" — redundant, the screen itself already shows the complete breakdown</t>
+          <t>Shown only for incorrect rows</t>
         </is>
       </c>
     </row>
@@ -7421,25 +7413,29 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>no_recorded_answers</t>
+          <t>blank_answer_fallback</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>No recorded answers for this quiz.</t>
+          <t>(blank)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>No hay respuestas registradas para este cuestionario.</t>
+          <t>(en blanco)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Aucune réponse enregistrée pour ce quiz.</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr"/>
+          <t>(vide)</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Shown when a skipped/empty answer was recorded</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7454,22 +7450,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>your_answer_label</t>
+          <t>error_loading_results</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Your answer:</t>
+          <t>Something went wrong loading results.</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Tu respuesta:</t>
+          <t>Algo salió mal al cargar los resultados.</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ta réponse :</t>
+          <t>Une erreur s'est produite lors du chargement des résultats.</t>
         </is>
       </c>
       <c r="G205" t="inlineStr"/>
@@ -7482,32 +7478,32 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>correct_answer_label</t>
+          <t>list_type_info_alert_title</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Correct answer:</t>
+          <t>List Types</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Respuesta correcta:</t>
+          <t>Tipos de lista</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bonne réponse :</t>
+          <t>Types de liste</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Shown only for incorrect rows</t>
+          <t>New info icon next to the List type label</t>
         </is>
       </c>
     </row>
@@ -7519,34 +7515,30 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>blank_answer_fallback</t>
+          <t>list_type_info_vocab</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(en blanco)</t>
+          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>(vide)</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Shown when a skipped/empty answer was recorded</t>
-        </is>
-      </c>
+          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7556,27 +7548,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>quiz-results.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>error_loading_results</t>
+          <t>list_type_info_verb</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Something went wrong loading results.</t>
+          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Algo salió mal al cargar los resultados.</t>
+          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du chargement des résultats.</t>
+          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
         </is>
       </c>
       <c r="G208" t="inlineStr"/>
@@ -7594,27 +7586,27 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>list_type_info_alert_title</t>
+          <t>save_input_placeholder_new</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>List Types</t>
+          <t>Name this list</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Tipos de lista</t>
+          <t>Nombra esta lista</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Types de liste</t>
+          <t>Nomme cette liste</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>New info icon next to the List type label</t>
+          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
         </is>
       </c>
     </row>
@@ -7631,25 +7623,29 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>list_type_info_vocab</t>
+          <t>save_input_placeholder_update</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Vocab — plain word pairs (nouns, adjectives, etc.), tested as-is.</t>
+          <t>List name (updates it)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vocabulario — pares de palabras simples (sustantivos, adjetivos, etc.), evaluados tal cual.</t>
+          <t>Nombre de la lista (la actualiza)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr"/>
+          <t>Nom de la liste (la met à jour)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Placeholder shown once the list is already saved — shortened to fit</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7664,25 +7660,29 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>list_type_info_verb</t>
+          <t>remove_word_icon</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Verb — infinitives get conjugated in context on Generate Quiz, so you're tested on actual verb forms (e.g. "habla") instead of just recalling the infinitive ("hablar").</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Verbo — los infinitivos se conjugan en contexto al generar el cuestionario, así que se te evalúa con formas verbales reales (p. ej. "habla") en lugar de solo recordar el infinitivo ("hablar").</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr"/>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7692,32 +7692,32 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>save_input_placeholder_new</t>
+          <t>translate_prompt_template</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Name this list</t>
+          <t>{n} line(s) looked like single word(s), not pairs — translate into:</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Nombra esta lista</t>
+          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Nomme cette liste</t>
+          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Placeholder text — shortened from "Name this list to save it", didn't fit alongside the Save button</t>
+          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
         </is>
       </c>
     </row>
@@ -7729,34 +7729,30 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>save_input_placeholder_update</t>
+          <t>translate_button</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>List name (updates it)</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Nombre de la lista (la actualiza)</t>
+          <t>Traducir</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Nom de la liste (la met à jour)</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Placeholder shown once the list is already saved — shortened to fit</t>
-        </is>
-      </c>
+          <t>Traduire</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7766,34 +7762,30 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>translate-skipped-lines.tsx</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>remove_word_icon</t>
+          <t>translating_ellipsis</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Translating…</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>Traduciendo…</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>New per-word remove button in the word list, was append/undo-last/clear-all only before — icon glyph, same in every language</t>
-        </is>
-      </c>
+          <t>Traduction en cours…</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7808,29 +7800,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>translate_prompt_template</t>
+          <t>error_translating</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>{n} line(s) looked like single word(s), not pairs — translate into:</t>
+          <t>Something went wrong translating those words.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>{n} línea(s) parecían palabras sueltas, no pares — traducir a:</t>
+          <t>Algo salió mal al traducir esas palabras.</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>{n} ligne(s) semblaient être des mots isolés, pas des paires — traduire vers :</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>New — shown under a parse's "couldn't parse N lines" message on Upload File and Paste</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7840,30 +7828,34 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>onboarding.tsx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>translate_button</t>
+          <t>slide1_body_updated</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Traducir</t>
+          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Traduire</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr"/>
+          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7873,30 +7865,34 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>translating_ellipsis</t>
+          <t>rename_link</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Translating…</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Traduciendo…</t>
+          <t>Cambiar nombre</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Traduction en cours…</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr"/>
+          <t>Renommer</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>New — separates renaming an already-saved list from saving its pairs</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7906,30 +7902,34 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>translate-skipped-lines.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>error_translating</t>
+          <t>rename_save_button</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Something went wrong translating those words.</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Algo salió mal al traducir esas palabras.</t>
+          <t>Guardar</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr"/>
+          <t>Enregistrer</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Inline rename confirm button</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7939,32 +7939,32 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>onboarding.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>slide1_body_updated</t>
+          <t>rename_cancel_button</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Type words, paste a list, or upload a file — AI reads it for you. Or jump right in with a few ready-made sample lists in My Lists.</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Escribe palabras, pega una lista o sube un archivo — la IA la lee por ti. O empieza directamente con algunas listas de ejemplo ya preparadas en Mis listas.</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tape des mots, colle une liste ou importe un fichier — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
+          <t>Annuler</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Updated — removed "or snap a photo" since Upload Photo was tabled</t>
+          <t>Inline rename cancel button</t>
         </is>
       </c>
     </row>
@@ -7981,29 +7981,25 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>rename_link</t>
+          <t>error_renaming</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Something went wrong renaming.</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Cambiar nombre</t>
+          <t>Algo salió mal al cambiar el nombre.</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Renommer</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>New — separates renaming an already-saved list from saving its pairs</t>
-        </is>
-      </c>
+          <t>Une erreur s'est produite lors du renommage.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8018,27 +8014,27 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>rename_save_button</t>
+          <t>save_changes_button</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Save Changes</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Guardar</t>
+          <t>Guardar cambios</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Enregistrer</t>
+          <t>Enregistrer les modifications</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Inline rename confirm button</t>
+          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
         </is>
       </c>
     </row>
@@ -8055,27 +8051,27 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>rename_cancel_button</t>
+          <t>list_type_locked_label</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>List type (locked)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Tipo de lista (bloqueado)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Type de liste (verrouillé)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Inline rename cancel button</t>
+          <t>Appended to the label once a list is saved — type can't change after first save</t>
         </is>
       </c>
     </row>
@@ -8092,25 +8088,29 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>error_renaming</t>
+          <t>list_type_locked_explanation</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Something went wrong renaming.</t>
+          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Algo salió mal al cambiar el nombre.</t>
+          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors du renommage.</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr"/>
+          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Appended to the existing List Types info alert once locked</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8120,32 +8120,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>save_changes_button</t>
+          <t>past_quizzes_section_title</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Save Changes</t>
+          <t>Past Quizzes</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Guardar cambios</t>
+          <t>Cuestionarios anteriores</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Enregistrer les modifications</t>
+          <t>Quiz précédents</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Replaces "Save List"+name field once a list is already saved — updates pairs by id, no name field</t>
+          <t>New section showing completed quiz history, fetched from GET /quiz-sessions/completed</t>
         </is>
       </c>
     </row>
@@ -8157,32 +8157,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>list_type_locked_label</t>
+          <t>no_past_quizzes</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>List type (locked)</t>
+          <t>No completed quizzes yet.</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Tipo de lista (bloqueado)</t>
+          <t>Aún no hay cuestionarios completados.</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Type de liste (verrouillé)</t>
+          <t>Aucun quiz terminé pour l'instant.</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Appended to the label once a list is saved — type can't change after first save</t>
+          <t>Renamed from no_completed_quizzes — collided with list-history.tsx's key of the same name</t>
         </is>
       </c>
     </row>
@@ -8194,32 +8194,32 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>list_type_locked_explanation</t>
+          <t>past_quiz_score_template</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Can't be changed after a list is saved — quiz history is tied to how a word is tested, so switching types on an existing list would make its past results inconsistent. Save a new list instead if you need the other type.</t>
+          <t>{correct}/{total} correct ({pct}%)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>No se puede cambiar después de guardar una lista — el historial del cuestionario está vinculado a cómo se evalúa una palabra, así que cambiar el tipo en una lista existente haría que sus resultados anteriores fueran incoherentes. Guarda una lista nueva si necesitas el otro tipo.</t>
+          <t>{correct}/{total} correctas ({pct}%)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ne peut pas être modifié après l'enregistrement d'une liste — l'historique des quiz est lié à la façon dont un mot est testé, donc changer le type d'une liste existante rendrait ses résultats passés incohérents. Enregistre une nouvelle liste si tu as besoin de l'autre type.</t>
+          <t>{correct}/{total} correctes ({pct} %)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Appended to the existing List Types info alert once locked</t>
+          <t>Template</t>
         </is>
       </c>
     </row>
@@ -8236,27 +8236,27 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>past_quizzes_section_title</t>
+          <t>deleted_list_fallback</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Past Quizzes</t>
+          <t>Deleted list</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Cuestionarios anteriores</t>
+          <t>Lista eliminada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Quiz précédents</t>
+          <t>Liste supprimée</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>New section showing completed quiz history, fetched from GET /quiz-sessions/completed</t>
+          <t>Shown when a past quiz's list no longer exists</t>
         </is>
       </c>
     </row>
@@ -8268,32 +8268,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>no_past_quizzes</t>
+          <t>discard_unsaved_alert_title</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>No completed quizzes yet.</t>
+          <t>Discard unsaved words?</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aún no hay cuestionarios completados.</t>
+          <t>¿Descartar palabras sin guardar?</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Aucun quiz terminé pour l'instant.</t>
+          <t>Abandonner les mots non enregistrés ?</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Renamed from no_completed_quizzes — collided with list-history.tsx's key of the same name</t>
+          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
         </is>
       </c>
     </row>
@@ -8305,34 +8305,30 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>past_quiz_score_template</t>
+          <t>discard_unsaved_alert_message</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>{correct}/{total} correct ({pct}%)</t>
+          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctas ({pct}%)</t>
+          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>{correct}/{total} correctes ({pct} %)</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
+          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8342,32 +8338,32 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>back-button.tsx</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>deleted_list_fallback</t>
+          <t>leave_without_saving</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Deleted list</t>
+          <t>Leave Without Saving</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Lista eliminada</t>
+          <t>Salir sin guardar</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Liste supprimée</t>
+          <t>Quitter sans enregistrer</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Shown when a past quiz's list no longer exists</t>
+          <t>Destructive confirm action</t>
         </is>
       </c>
     </row>
@@ -8379,32 +8375,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>language-order-confirm.tsx</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_title</t>
+          <t>order_confirm_prompt_template</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Discard unsaved words?</t>
+          <t>Detected {first} and {second}. Which one do you already know?</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>¿Descartar palabras sin guardar?</t>
+          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Abandonner les mots non enregistrés ?</t>
+          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>New — shown when backing out of Add Words with 3+ unsaved words</t>
+          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
         </is>
       </c>
     </row>
@@ -8416,30 +8412,34 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>language-order-confirm.tsx</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>discard_unsaved_alert_message</t>
+          <t>order_confirm_option_template</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>You've added words that haven't been saved yet. Leaving now will lose them.</t>
+          <t>I know {language}</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Has añadido palabras que aún no se han guardado. Si sales ahora, se perderán.</t>
+          <t>Ya sé {language}</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr"/>
+          <t>Je connais déjà {language}</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Two buttons, one per detected language</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8449,32 +8449,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>back-button.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>leave_without_saving</t>
+          <t>source_word_placeholder_dynamic</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Leave Without Saving</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Salir sin guardar</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Quitter sans enregistrer</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Destructive confirm action</t>
+          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
         </is>
       </c>
     </row>
@@ -8486,32 +8486,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>order_confirm_prompt_template</t>
+          <t>target_word_placeholder_dynamic</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Detected {first} and {second}. Which one do you already know?</t>
+          <t>Word in {language}</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Detectamos {first} y {second}. ¿Cuál de los dos ya conoces?</t>
+          <t>Palabra en {language}</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nous avons détecté {first} et {second}. Lequel connais-tu déjà ?</t>
+          <t>Mot en {language}</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>New — shown once after a fresh parse/translation detects two languages, replaces blindly assuming column order = known-then-learning</t>
+          <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
         </is>
       </c>
     </row>
@@ -8523,32 +8523,32 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>language-order-confirm.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>order_confirm_option_template</t>
+          <t>app_language_title</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>I know {language}</t>
+          <t>App Language</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ya sé {language}</t>
+          <t>Idioma de la app</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Je connais déjà {language}</t>
+          <t>Langue de l'application</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Two buttons, one per detected language</t>
+          <t>New — the UI locale picker itself, part of building the actual i18n layer</t>
         </is>
       </c>
     </row>
@@ -8560,32 +8560,32 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>list-details.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>source_word_placeholder_dynamic</t>
+          <t>list_type_label</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Word in {language}</t>
+          <t>List type</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Palabra en {language}</t>
+          <t>Tipo de lista</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mot en {language}</t>
+          <t>Type de liste</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Simplified — dropped "(known)" qualifier, the From/To picker above already establishes direction</t>
+          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
         </is>
       </c>
     </row>
@@ -8597,32 +8597,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>list-details.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>target_word_placeholder_dynamic</t>
+          <t>select_label</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Word in {language}</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Palabra en {language}</t>
+          <t>Seleccionar</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mot en {language}</t>
+          <t>Sélectionner</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Simplified — dropped "(learning)" qualifier, same reasoning</t>
+          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8634,32 +8634,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>app_language_title</t>
+          <t>done_label</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>App Language</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Idioma de la app</t>
+          <t>Listo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Langue de l'application</t>
+          <t>Terminé</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>New — the UI locale picker itself, part of building the actual i18n layer</t>
+          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8671,32 +8671,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>list_type_label</t>
+          <t>select_all_label</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>List type</t>
+          <t>Select All</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Tipo de lista</t>
+          <t>Seleccionar todo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Type de liste</t>
+          <t>Tout sélectionner</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8713,27 +8713,27 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>select_label</t>
+          <t>deselect_all_label</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Deselect All</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Seleccionar</t>
+          <t>Deseleccionar todo</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Sélectionner</t>
+          <t>Tout désélectionner</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8750,27 +8750,27 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>done_label</t>
+          <t>error_deleting_lists_bulk</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Something went wrong deleting those lists.</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Listo</t>
+          <t>Algo salió mal al eliminar esas listas.</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
+          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
         </is>
       </c>
     </row>
@@ -8782,32 +8782,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>select_all_label</t>
+          <t>error_deleting_quizzes_bulk</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Select All</t>
+          <t>Something went wrong deleting those quizzes.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Seleccionar todo</t>
+          <t>Algo salió mal al eliminar esos cuestionarios.</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tout sélectionner</t>
+          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
         </is>
       </c>
     </row>
@@ -8824,27 +8824,27 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>deselect_all_label</t>
+          <t>loading_ellipsis</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Deselect All</t>
+          <t>Loading…</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Deseleccionar todo</t>
+          <t>Cargando…</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tout désélectionner</t>
+          <t>Chargement…</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+          <t>Reused wherever a screen shows a generic loading state</t>
         </is>
       </c>
     </row>
@@ -8856,34 +8856,30 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>login.tsx</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>error_deleting_lists_bulk</t>
+          <t>forgot_password_link</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Something went wrong deleting those lists.</t>
+          <t>Forgot password?</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esas listas.</t>
+          <t>¿Olvidaste tu contraseña?</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
-        </is>
-      </c>
+          <t>Mot de passe oublié ?</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8893,34 +8889,30 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>error_deleting_quizzes_bulk</t>
+          <t>forgot_password_title</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Something went wrong deleting those quizzes.</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esos cuestionarios.</t>
+          <t>Contraseña olvidada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
-        </is>
-      </c>
+          <t>Mot de passe oublié</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8930,32 +8922,32 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>loading_ellipsis</t>
+          <t>forgot_password_sent_message</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Loading…</t>
+          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cargando…</t>
+          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Chargement…</t>
+          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Reused wherever a screen shows a generic loading state</t>
+          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
         </is>
       </c>
     </row>
@@ -8967,27 +8959,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>login.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>forgot_password_link</t>
+          <t>forgot_password_instructions</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Forgot password?</t>
+          <t>Enter your email and we'll send you a link to reset your password.</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>¿Olvidaste tu contraseña?</t>
+          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mot de passe oublié ?</t>
+          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
@@ -9005,22 +8997,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>forgot_password_title</t>
+          <t>sending_ellipsis</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Sending…</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Contraseña olvidada</t>
+          <t>Enviando…</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mot de passe oublié</t>
+          <t>Envoi en cours…</t>
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
@@ -9038,29 +9030,25 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>forgot_password_sent_message</t>
+          <t>send_reset_link</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
+          <t>Send Reset Link</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
+          <t>Enviar enlace de restablecimiento</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
-        </is>
-      </c>
+          <t>Envoyer le lien de réinitialisation</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9070,27 +9058,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>forgot_password_instructions</t>
+          <t>reset_password_title</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Enter your email and we'll send you a link to reset your password.</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
+          <t>Restablecer contraseña</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
+          <t>Réinitialiser le mot de passe</t>
         </is>
       </c>
       <c r="G250" t="inlineStr"/>
@@ -9103,27 +9091,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>sending_ellipsis</t>
+          <t>reset_link_invalid_message</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Sending…</t>
+          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Enviando…</t>
+          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Envoi en cours…</t>
+          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
@@ -9136,27 +9124,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>send_reset_link</t>
+          <t>set_new_password_title</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Send Reset Link</t>
+          <t>Set a New Password</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Enviar enlace de restablecimiento</t>
+          <t>Establece una nueva contraseña</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Envoyer le lien de réinitialisation</t>
+          <t>Définis un nouveau mot de passe</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -9174,22 +9162,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>reset_password_title</t>
+          <t>new_password_placeholder</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Restablecer contraseña</t>
+          <t>Nueva contraseña</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Réinitialiser le mot de passe</t>
+          <t>Nouveau mot de passe</t>
         </is>
       </c>
       <c r="G253" t="inlineStr"/>
@@ -9207,22 +9195,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>reset_link_invalid_message</t>
+          <t>save_new_password</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
+          <t>Save New Password</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
+          <t>Guardar nueva contraseña</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
+          <t>Enregistrer le nouveau mot de passe</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
@@ -9235,30 +9223,34 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>set_new_password_title</t>
+          <t>sort_by_added_order</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Set a New Password</t>
+          <t>Order Added</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Establece una nueva contraseña</t>
+          <t>Orden de añadido</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Définis un nouveau mot de passe</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr"/>
+          <t>Ordre d'ajout</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Word-list sort option — mirrors My Lists' sort-by pattern; default order (insertion order)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9268,27 +9260,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>new_password_placeholder</t>
+          <t>bulk_delete_words_alert_title</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Delete Words</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Nueva contraseña</t>
+          <t>Eliminar palabras</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Nouveau mot de passe</t>
+          <t>Supprimer les mots</t>
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
@@ -9301,30 +9293,34 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>save_new_password</t>
+          <t>bulk_delete_words_alert_message_template</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Save New Password</t>
+          <t>Delete {count} word(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Guardar nueva contraseña</t>
+          <t>¿Eliminar {count} palabra(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Enregistrer le nouveau mot de passe</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr"/>
+          <t>Supprimer {count} mot(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9334,32 +9330,32 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>list-details.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>sort_by_added_order</t>
+          <t>sample_category_common_words</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Order Added</t>
+          <t>Common Words</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Orden de añadido</t>
+          <t>Palabras comunes</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ordre d'ajout</t>
+          <t>Mots courants</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Word-list sort option — mirrors My Lists' sort-by pattern; default order (insertion order)</t>
+          <t>Sample-list category label</t>
         </is>
       </c>
     </row>
@@ -9371,30 +9367,34 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>list-details.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>bulk_delete_words_alert_title</t>
+          <t>sample_category_common_verbs</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Delete Words</t>
+          <t>Common Verbs</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Eliminar palabras</t>
+          <t>Verbos comunes</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Supprimer les mots</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr"/>
+          <t>Verbes courants</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Sample-list category label</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9404,32 +9404,32 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>list-details.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>bulk_delete_words_alert_message_template</t>
+          <t>sample_category_irregular_verbs</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Delete {count} word(s)? This can't be undone.</t>
+          <t>Irregular Verbs</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} palabra(s)? Esta acción no se puede deshacer.</t>
+          <t>Verbos irregulares</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Supprimer {count} mot(s) ? Cette action est irréversible.</t>
+          <t>Verbes irréguliers</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Sample-list category label — new dedicated dataset, distinct from Common Verbs</t>
         </is>
       </c>
     </row>
@@ -9446,27 +9446,27 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>sample_category_common_words</t>
+          <t>sample_category_food</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Common Words</t>
+          <t>Food Words</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Palabras comunes</t>
+          <t>Palabras de comida</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Mots courants</t>
+          <t>Mots de nourriture</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Sample-list category label</t>
+          <t>Sample-list category label — new dedicated dataset</t>
         </is>
       </c>
     </row>
@@ -9478,34 +9478,30 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>sample_category_common_verbs</t>
+          <t>learning_pair_title</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Common Verbs</t>
+          <t>What are you learning?</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Verbos comunes</t>
+          <t>¿Qué estás aprendiendo?</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Verbes courants</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Sample-list category label</t>
-        </is>
-      </c>
+          <t>Qu'apprends-tu ?</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9515,32 +9511,32 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>sample_category_irregular_verbs</t>
+          <t>learning_pair_hint</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Irregular Verbs</t>
+          <t>Add every language you're learning — each gets its own level and starter lists.</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Verbos irregulares</t>
+          <t>Añade cada idioma que estás aprendiendo — cada uno tiene su propio nivel y sus propias listas iniciales.</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Verbes irréguliers</t>
+          <t>Ajoute chaque langue que tu apprends — chacune a son propre niveau et ses propres listes de départ.</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Sample-list category label — new dedicated dataset, distinct from Common Verbs</t>
+          <t>Updated for multi-language support — was singular ('your default pair'), now plural</t>
         </is>
       </c>
     </row>
@@ -9552,32 +9548,32 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>sample_category_food</t>
+          <t>generating_starter_lists</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Food Words</t>
+          <t>Setting up your starter lists…</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Palabras de comida</t>
+          <t>Preparando tus listas iniciales…</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mots de nourriture</t>
+          <t>Préparation de tes listes de départ…</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Sample-list category label — new dedicated dataset</t>
+          <t>Shown while the first-time PATCH /me/profile call is generating sample lists via Gemini</t>
         </is>
       </c>
     </row>
@@ -9594,22 +9590,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>learning_pair_title</t>
+          <t>starter_lists_ready_message</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>What are you learning?</t>
+          <t>Your starter lists are ready — check My Lists!</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>¿Qué estás aprendiendo?</t>
+          <t>¡Tus listas iniciales ya están listas — échales un vistazo en Mis listas!</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Qu'apprends-tu ?</t>
+          <t>Tes listes de départ sont prêtes — jette un œil dans Mes listes !</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -9627,22 +9623,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>learning_pair_hint</t>
+          <t>add_language_button</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Sets your default language pair and unlocks a few ready-made starter lists.</t>
+          <t>Add Language</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Establece tu par de idiomas por defecto y desbloquea algunas listas iniciales ya preparadas.</t>
+          <t>Añadir idioma</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Définit ta paire de langues par défaut et débloque quelques listes de départ prêtes à l'emploi.</t>
+          <t>Ajouter une langue</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
@@ -9660,29 +9656,25 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>generating_starter_lists</t>
+          <t>no_languages_added</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Setting up your starter lists…</t>
+          <t>No languages added yet — add one below to get started.</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Preparando tus listas iniciales…</t>
+          <t>Aún no has añadido ningún idioma — añade uno abajo para empezar.</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Préparation de tes listes de départ…</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Shown while the first-time PATCH /me/profile call is generating sample lists via Gemini</t>
-        </is>
-      </c>
+          <t>Tu n'as encore ajouté aucune langue — ajoutes-en une ci-dessous pour commencer.</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9697,25 +9689,66 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>starter_lists_ready_message</t>
+          <t>remove_language_confirm_title</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Your starter lists are ready — check My Lists!</t>
+          <t>Remove language?</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>¡Tus listas iniciales ya están listas — échales un vistazo en Mis listas!</t>
+          <t>¿Eliminar idioma?</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Tes listes de départ sont prêtes — jette un œil dans Mes listes !</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr"/>
+          <t>Supprimer la langue ?</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Alert title — does not delete any saved lists, just this pair's level/accent settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>remove_language_confirm_message</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>This removes {source} → {target} from your languages. Your saved lists aren't affected.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Esto elimina {source} → {target} de tus idiomas. Tus listas guardadas no se ven afectadas.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Cela supprime {source} → {target} de tes langues. Tes listes enregistrées ne sont pas affectées.</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -8523,32 +8523,32 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>settings.tsx</t>
+          <t>pairs-review.tsx</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>app_language_title</t>
+          <t>list_type_label</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>App Language</t>
+          <t>List type</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Idioma de la app</t>
+          <t>Tipo de lista</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Langue de l'application</t>
+          <t>Type de liste</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>New — the UI locale picker itself, part of building the actual i18n layer</t>
+          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
         </is>
       </c>
     </row>
@@ -8560,32 +8560,32 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>pairs-review.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>list_type_label</t>
+          <t>select_label</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>List type</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Tipo de lista</t>
+          <t>Seleccionar</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Type de liste</t>
+          <t>Sélectionner</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>New — plain unlocked label; list_type_locked_label is the separate (locked) variant</t>
+          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8602,27 +8602,27 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>select_label</t>
+          <t>done_label</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Seleccionar</t>
+          <t>Listo</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Sélectionner</t>
+          <t>Terminé</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Split from the old combined "Select / Done" doc row — separate key needed for actual t() usage. Shared pattern, My Lists and My Quizzes</t>
+          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8639,27 +8639,27 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>done_label</t>
+          <t>select_all_label</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Select All</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Listo</t>
+          <t>Seleccionar todo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Terminé</t>
+          <t>Tout sélectionner</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Split from "Select / Done". Shared pattern, My Lists and My Quizzes</t>
+          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
         </is>
       </c>
     </row>
@@ -8676,22 +8676,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>select_all_label</t>
+          <t>deselect_all_label</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Select All</t>
+          <t>Deselect All</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Seleccionar todo</t>
+          <t>Deseleccionar todo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tout sélectionner</t>
+          <t>Tout désélectionner</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -8713,27 +8713,27 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>deselect_all_label</t>
+          <t>error_deleting_lists_bulk</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Deselect All</t>
+          <t>Something went wrong deleting those lists.</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Deseleccionar todo</t>
+          <t>Algo salió mal al eliminar esas listas.</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tout désélectionner</t>
+          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Split from "Select All / Deselect All". Shared pattern, My Lists and My Quizzes</t>
+          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
         </is>
       </c>
     </row>
@@ -8745,32 +8745,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>my-quizzes.tsx</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>error_deleting_lists_bulk</t>
+          <t>error_deleting_quizzes_bulk</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Something went wrong deleting those lists.</t>
+          <t>Something went wrong deleting those quizzes.</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esas listas.</t>
+          <t>Algo salió mal al eliminar esos cuestionarios.</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ces listes.</t>
+          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Plural — bulk-delete error, distinct from error_deleting_list (singular)</t>
+          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
         </is>
       </c>
     </row>
@@ -8782,32 +8782,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>my-quizzes.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>error_deleting_quizzes_bulk</t>
+          <t>loading_ellipsis</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Something went wrong deleting those quizzes.</t>
+          <t>Loading…</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Algo salió mal al eliminar esos cuestionarios.</t>
+          <t>Cargando…</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Une erreur s'est produite lors de la suppression de ces quiz.</t>
+          <t>Chargement…</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Plural — bulk-delete error, distinct from error_deleting_quiz (singular)</t>
+          <t>Reused wherever a screen shows a generic loading state</t>
         </is>
       </c>
     </row>
@@ -8819,34 +8819,30 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>login.tsx</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>loading_ellipsis</t>
+          <t>forgot_password_link</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Loading…</t>
+          <t>Forgot password?</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Cargando…</t>
+          <t>¿Olvidaste tu contraseña?</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Chargement…</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Reused wherever a screen shows a generic loading state</t>
-        </is>
-      </c>
+          <t>Mot de passe oublié ?</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8856,27 +8852,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>login.tsx</t>
+          <t>forgot-password.tsx</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>forgot_password_link</t>
+          <t>forgot_password_title</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Forgot password?</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>¿Olvidaste tu contraseña?</t>
+          <t>Contraseña olvidada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mot de passe oublié ?</t>
+          <t>Mot de passe oublié</t>
         </is>
       </c>
       <c r="G244" t="inlineStr"/>
@@ -8894,25 +8890,29 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>forgot_password_title</t>
+          <t>forgot_password_sent_message</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Contraseña olvidada</t>
+          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Mot de passe oublié</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr"/>
+          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8927,29 +8927,25 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>forgot_password_sent_message</t>
+          <t>forgot_password_instructions</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>If an account exists for that email, we've sent a link to reset your password. Check your inbox.</t>
+          <t>Enter your email and we'll send you a link to reset your password.</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Si existe una cuenta con ese correo, te hemos enviado un enlace para restablecer tu contraseña. Revisa tu bandeja de entrada.</t>
+          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Si un compte existe pour cette adresse e-mail, nous t'avons envoyé un lien pour réinitialiser ton mot de passe. Vérifie ta boîte de réception.</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Deliberately non-revealing — matches backend's response regardless of whether the email has an account</t>
-        </is>
-      </c>
+          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8964,22 +8960,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>forgot_password_instructions</t>
+          <t>sending_ellipsis</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Enter your email and we'll send you a link to reset your password.</t>
+          <t>Sending…</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Introduce tu correo y te enviaremos un enlace para restablecer tu contraseña.</t>
+          <t>Enviando…</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
+          <t>Envoi en cours…</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
@@ -8997,22 +8993,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>sending_ellipsis</t>
+          <t>send_reset_link</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Sending…</t>
+          <t>Send Reset Link</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Enviando…</t>
+          <t>Enviar enlace de restablecimiento</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Envoi en cours…</t>
+          <t>Envoyer le lien de réinitialisation</t>
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
@@ -9025,27 +9021,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>forgot-password.tsx</t>
+          <t>reset-password.tsx</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>send_reset_link</t>
+          <t>reset_password_title</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Send Reset Link</t>
+          <t>Reset Password</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Enviar enlace de restablecimiento</t>
+          <t>Restablecer contraseña</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Envoyer le lien de réinitialisation</t>
+          <t>Réinitialiser le mot de passe</t>
         </is>
       </c>
       <c r="G249" t="inlineStr"/>
@@ -9063,22 +9059,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>reset_password_title</t>
+          <t>reset_link_invalid_message</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Reset Password</t>
+          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Restablecer contraseña</t>
+          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Réinitialiser le mot de passe</t>
+          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
         </is>
       </c>
       <c r="G250" t="inlineStr"/>
@@ -9096,22 +9092,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>reset_link_invalid_message</t>
+          <t>set_new_password_title</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>This link looks invalid or expired. Request a new reset link from the login screen.</t>
+          <t>Set a New Password</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Este enlace parece no válido o ha caducado. Solicita un nuevo enlace desde la pantalla de inicio de sesión.</t>
+          <t>Establece una nueva contraseña</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
+          <t>Définis un nouveau mot de passe</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
@@ -9129,22 +9125,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>set_new_password_title</t>
+          <t>new_password_placeholder</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Set a New Password</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Establece una nueva contraseña</t>
+          <t>Nueva contraseña</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Définis un nouveau mot de passe</t>
+          <t>Nouveau mot de passe</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -9162,22 +9158,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>new_password_placeholder</t>
+          <t>save_new_password</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Save New Password</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nueva contraseña</t>
+          <t>Guardar nueva contraseña</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Nouveau mot de passe</t>
+          <t>Enregistrer le nouveau mot de passe</t>
         </is>
       </c>
       <c r="G253" t="inlineStr"/>
@@ -9190,30 +9186,34 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>reset-password.tsx</t>
+          <t>list-details.tsx</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>save_new_password</t>
+          <t>sort_by_added_order</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Save New Password</t>
+          <t>Order Added</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Guardar nueva contraseña</t>
+          <t>Orden de añadido</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Enregistrer le nouveau mot de passe</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr"/>
+          <t>Ordre d'ajout</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Word-list sort option — mirrors My Lists' sort-by pattern; default order (insertion order)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9228,29 +9228,25 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>sort_by_added_order</t>
+          <t>bulk_delete_words_alert_title</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Order Added</t>
+          <t>Delete Words</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Orden de añadido</t>
+          <t>Eliminar palabras</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ordre d'ajout</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Word-list sort option — mirrors My Lists' sort-by pattern; default order (insertion order)</t>
-        </is>
-      </c>
+          <t>Supprimer les mots</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9265,25 +9261,29 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>bulk_delete_words_alert_title</t>
+          <t>bulk_delete_words_alert_message_template</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Delete Words</t>
+          <t>Delete {count} word(s)? This can't be undone.</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Eliminar palabras</t>
+          <t>¿Eliminar {count} palabra(s)? Esta acción no se puede deshacer.</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Supprimer les mots</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr"/>
+          <t>Supprimer {count} mot(s) ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9293,32 +9293,32 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>list-details.tsx</t>
+          <t>my-lists.tsx</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>bulk_delete_words_alert_message_template</t>
+          <t>sample_category_common_words</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Delete {count} word(s)? This can't be undone.</t>
+          <t>Common Words</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>¿Eliminar {count} palabra(s)? Esta acción no se puede deshacer.</t>
+          <t>Palabras comunes</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Supprimer {count} mot(s) ? Cette action est irréversible.</t>
+          <t>Mots courants</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Sample-list category label</t>
         </is>
       </c>
     </row>
@@ -9335,22 +9335,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>sample_category_common_words</t>
+          <t>sample_category_common_verbs</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Common Words</t>
+          <t>Common Verbs</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Palabras comunes</t>
+          <t>Verbos comunes</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mots courants</t>
+          <t>Verbes courants</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -9372,27 +9372,27 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>sample_category_common_verbs</t>
+          <t>sample_category_irregular_verbs</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Common Verbs</t>
+          <t>Irregular Verbs</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Verbos comunes</t>
+          <t>Verbos irregulares</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Verbes courants</t>
+          <t>Verbes irréguliers</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Sample-list category label</t>
+          <t>Sample-list category label — new dedicated dataset, distinct from Common Verbs</t>
         </is>
       </c>
     </row>
@@ -9409,27 +9409,27 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>sample_category_irregular_verbs</t>
+          <t>sample_category_food</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Irregular Verbs</t>
+          <t>Food Words</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Verbos irregulares</t>
+          <t>Palabras de comida</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Verbes irréguliers</t>
+          <t>Mots de nourriture</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Sample-list category label — new dedicated dataset, distinct from Common Verbs</t>
+          <t>Sample-list category label — new dedicated dataset</t>
         </is>
       </c>
     </row>
@@ -9441,34 +9441,30 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>my-lists.tsx</t>
+          <t>settings.tsx</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>sample_category_food</t>
+          <t>learning_pair_title</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Food Words</t>
+          <t>What are you learning?</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Palabras de comida</t>
+          <t>¿Qué estás aprendiendo?</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Mots de nourriture</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Sample-list category label — new dedicated dataset</t>
-        </is>
-      </c>
+          <t>Qu'apprends-tu ?</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9483,25 +9479,29 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>learning_pair_title</t>
+          <t>learning_pair_hint</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>What are you learning?</t>
+          <t>Add every language you're learning — each gets its own level and starter lists.</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>¿Qué estás aprendiendo?</t>
+          <t>Añade cada idioma que estás aprendiendo — cada uno tiene su propio nivel y sus propias listas iniciales.</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Qu'apprends-tu ?</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr"/>
+          <t>Ajoute chaque langue que tu apprends — chacune a son propre niveau et ses propres listes de départ.</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Updated for multi-language support — was singular ('your default pair'), now plural</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9516,27 +9516,27 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>learning_pair_hint</t>
+          <t>generating_starter_lists</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Add every language you're learning — each gets its own level and starter lists.</t>
+          <t>Setting up your starter lists…</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Añade cada idioma que estás aprendiendo — cada uno tiene su propio nivel y sus propias listas iniciales.</t>
+          <t>Preparando tus listas iniciales…</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ajoute chaque langue que tu apprends — chacune a son propre niveau et ses propres listes de départ.</t>
+          <t>Préparation de tes listes de départ…</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Updated for multi-language support — was singular ('your default pair'), now plural</t>
+          <t>Shown while the first-time PATCH /me/profile call is generating sample lists via Gemini</t>
         </is>
       </c>
     </row>
@@ -9553,29 +9553,25 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>generating_starter_lists</t>
+          <t>starter_lists_ready_message</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Setting up your starter lists…</t>
+          <t>Your starter lists are ready — check My Lists!</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Preparando tus listas iniciales…</t>
+          <t>¡Tus listas iniciales ya están listas — échales un vistazo en Mis listas!</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Préparation de tes listes de départ…</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Shown while the first-time PATCH /me/profile call is generating sample lists via Gemini</t>
-        </is>
-      </c>
+          <t>Tes listes de départ sont prêtes — jette un œil dans Mes listes !</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9590,22 +9586,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>starter_lists_ready_message</t>
+          <t>add_language_button</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Your starter lists are ready — check My Lists!</t>
+          <t>Add Language</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>¡Tus listas iniciales ya están listas — échales un vistazo en Mis listas!</t>
+          <t>Añadir idioma</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Tes listes de départ sont prêtes — jette un œil dans Mes listes !</t>
+          <t>Ajouter une langue</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -9623,22 +9619,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>add_language_button</t>
+          <t>no_languages_added</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Add Language</t>
+          <t>No languages added yet — add one below to get started.</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Añadir idioma</t>
+          <t>Aún no has añadido ningún idioma — añade uno abajo para empezar.</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Ajouter une langue</t>
+          <t>Tu n'as encore ajouté aucune langue — ajoutes-en une ci-dessous pour commencer.</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
@@ -9656,25 +9652,29 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>no_languages_added</t>
+          <t>remove_language_confirm_title</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>No languages added yet — add one below to get started.</t>
+          <t>Remove language?</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aún no has añadido ningún idioma — añade uno abajo para empezar.</t>
+          <t>¿Eliminar idioma?</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tu n'as encore ajouté aucune langue — ajoutes-en une ci-dessous pour commencer.</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr"/>
+          <t>Supprimer la langue ?</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Alert title — does not delete any saved lists, just this pair's level/accent settings</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9689,27 +9689,27 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>remove_language_confirm_title</t>
+          <t>remove_language_confirm_message</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Remove language?</t>
+          <t>This removes {source} → {target} from your languages. Your saved lists aren't affected.</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>¿Eliminar idioma?</t>
+          <t>Esto elimina {source} → {target} de tus idiomas. Tus listas guardadas no se ven afectadas.</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Supprimer la langue ?</t>
+          <t>Cela supprime {source} → {target} de tes langues. Tes listes enregistrées ne sont pas affectées.</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alert title — does not delete any saved lists, just this pair's level/accent settings</t>
+          <t>Template</t>
         </is>
       </c>
     </row>
@@ -9726,27 +9726,27 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>remove_language_confirm_message</t>
+          <t>require_accents_desc</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>This removes {source} → {target} from your languages. Your saved lists aren't affected.</t>
+          <t>Off accepts "cafe" for "café"</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Esto elimina {source} → {target} de tus idiomas. Tus listas guardadas no se ven afectadas.</t>
+          <t>Desactivado acepta "cafe" en lugar de "café"</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Cela supprime {source} → {target} de tes langues. Tes listes enregistrées ne sont pas affectées.</t>
+          <t>Désactivé accepte "cafe" pour "café"</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Template</t>
+          <t>Restored — off by default, grading strips accents; app is a reinforcement tool, not a strict teaching tool</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G269"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9750,6 +9750,43 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>generate-quiz.tsx</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>insight_examples_label</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>From your last quiz:</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>De tu último cuestionario:</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>De ton dernier quiz :</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Precedes the real 'typed → correct' examples shown under the tailored insight message</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2231,17 +2231,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How many questions?</t>
+          <t>No. Questions</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>¿Cuántas preguntas?</t>
+          <t>N.º de preguntas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Combien de questions ?</t>
+          <t>Nb de questions</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -9784,6 +9784,43 @@
       <c r="G270" t="inlineStr">
         <is>
           <t>Precedes the real 'typed → correct' examples shown under the tailored insight message</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>generate-quiz.tsx</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>feedback_title</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Commentaires</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Screen title used instead of Generate Quiz when the tailored feedback card is showing</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -483,8 +483,6 @@
           <t>LangReps</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Proper name — may stay untranslated</t>
@@ -522,7 +520,6 @@
           <t>Crée une liste de vocabulaire, puis laisse l'IA générer un quiz adaptatif pour toi.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,7 +552,6 @@
           <t>Paramètres</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,7 +584,6 @@
           <t>Se déconnecter</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -658,7 +653,6 @@
           <t>Se connecter / S'inscrire</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -728,7 +722,6 @@
           <t>Ajouter des mots manuellement</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -761,7 +754,6 @@
           <t>Coller une liste de vocabulaire</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -794,7 +786,6 @@
           <t>Importer un fichier</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -827,7 +818,6 @@
           <t>Importer une photo</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -860,7 +850,6 @@
           <t>Mes listes</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -893,7 +882,6 @@
           <t>Mes quiz</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1148,7 +1136,6 @@
           <t>E-mail</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1181,7 +1168,6 @@
           <t>Mot de passe</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1214,7 +1200,6 @@
           <t>Veuillez patienter…</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1247,7 +1232,6 @@
           <t>Pas de compte ? Inscris-toi</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1280,7 +1264,6 @@
           <t>Tu as déjà un compte ? Connecte-toi</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1313,7 +1296,6 @@
           <t>Vérifie tes e-mails pour confirmer, puis connecte-toi ci-dessous.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1346,7 +1328,6 @@
           <t>Compte créé — connecte-toi ci-dessous.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1453,7 +1434,6 @@
           <t>Coller une liste de vocabulaire</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1523,7 +1503,6 @@
           <t>Colle ici ta liste de vocabulaire</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1630,7 +1609,6 @@
           <t>Une erreur s'est produite lors de l'analyse de ce texte.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1663,7 +1641,6 @@
           <t>Importer un fichier</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1696,7 +1673,6 @@
           <t>Un fichier texte brut ou CSV, une paire par ligne — une tabulation, "-&gt;", ":", ou un symbole similaire entre chaque mot et sa traduction.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1729,7 +1705,6 @@
           <t>Choisir un fichier</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1799,7 +1774,6 @@
           <t>Une erreur s'est produite lors de l'analyse de ce fichier.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1832,7 +1806,6 @@
           <t>Importer une photo</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1902,7 +1875,6 @@
           <t>Prendre une photo</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1935,7 +1907,6 @@
           <t>Choisir depuis la galerie</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1968,7 +1939,6 @@
           <t>Lecture en cours…</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2001,7 +1971,6 @@
           <t>L'accès à l'appareil photo est nécessaire pour prendre une photo.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2034,7 +2003,6 @@
           <t>L'accès à la photothèque est nécessaire pour choisir une image.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2067,7 +2035,6 @@
           <t>Une erreur s'est produite lors de la lecture de cette image.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2174,7 +2141,6 @@
           <t>Il te faut au moins 3 mots pour générer un quiz.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2244,7 +2210,6 @@
           <t>Nb de questions</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2277,7 +2242,6 @@
           <t>Temps</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2384,7 +2348,6 @@
           <t>Génération de ton quiz…</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2417,7 +2380,6 @@
           <t>Cibler mes erreurs</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2450,7 +2412,6 @@
           <t>Générer un quiz similaire</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2483,7 +2444,6 @@
           <t>Une erreur s'est produite lors de la génération de ton quiz.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2516,7 +2476,6 @@
           <t>Mes listes</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2549,7 +2508,6 @@
           <t>Aucune liste enregistrée pour l'instant.</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2619,7 +2577,6 @@
           <t>Supprimer la liste</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2689,7 +2646,6 @@
           <t>Une erreur s'est produite lors du chargement de tes listes.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2722,7 +2678,6 @@
           <t>Une erreur s'est produite lors du chargement de cette liste.</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2755,7 +2710,6 @@
           <t>Une erreur s'est produite lors de la suppression de cette liste.</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2788,7 +2742,6 @@
           <t>Mes quiz</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2821,7 +2774,6 @@
           <t>Aucun quiz en cours.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2854,7 +2806,6 @@
           <t>Quiz en cours</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2924,7 +2875,6 @@
           <t>Supprimer le quiz</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2994,7 +2944,6 @@
           <t>Une erreur s'est produite lors du chargement de tes quiz.</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3027,7 +2976,6 @@
           <t>Une erreur s'est produite lors de la suppression de ce quiz.</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3097,7 +3045,6 @@
           <t>Aucun quiz terminé pour l'instant.</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3167,7 +3114,6 @@
           <t>Une erreur s'est produite lors du chargement de l'historique du quiz.</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3200,7 +3146,6 @@
           <t>Paramètres</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3233,7 +3178,6 @@
           <t>Supprimer automatiquement les quiz terminés après 30 jours</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3266,7 +3210,6 @@
           <t>Quiz adaptatifs — retour sur les schémas qui te posent des difficultés, avec la possibilité de les cibler</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3299,7 +3242,6 @@
           <t>Ta réponse</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3332,7 +3274,6 @@
           <t>Valider</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3365,7 +3306,6 @@
           <t>Passer cette question</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3398,7 +3338,6 @@
           <t>Masquer la liste de mots</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3431,7 +3370,6 @@
           <t>Bloqué ? Consulte la liste de mots</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3501,7 +3439,6 @@
           <t>C'est correct !</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3571,7 +3508,6 @@
           <t>Terminer le quiz</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3604,7 +3540,6 @@
           <t>Question suivante</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3637,7 +3572,6 @@
           <t>Quiz terminé !</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3707,7 +3641,6 @@
           <t>Retour à l'accueil</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3740,7 +3673,6 @@
           <t>Annuler le dernier</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3773,7 +3705,6 @@
           <t>Vider la liste</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3806,7 +3737,6 @@
           <t>Aucun mot ajouté pour l'instant.</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3839,7 +3769,6 @@
           <t>Nom de la liste (l'enregistrement la met à jour)</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3872,7 +3801,6 @@
           <t>Nom de la liste</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3905,7 +3833,6 @@
           <t>Enregistrement…</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3938,7 +3865,6 @@
           <t>Enregistrer la liste</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3971,7 +3897,6 @@
           <t>Enregistré !</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4004,7 +3929,6 @@
           <t>Une erreur s'est produite lors de l'enregistrement.</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4370,7 +4294,6 @@
           <t>Tu es en pleine lancée — tes scores récents sont bien au-dessus de ton point de départ.</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4403,7 +4326,6 @@
           <t>Gros bond dans tes scores dernièrement. Continue comme ça, quoi que tu fasses.</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4436,7 +4358,6 @@
           <t>Ta précision a beaucoup augmenté récemment — cette liste porte vraiment ses fruits.</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4469,7 +4390,6 @@
           <t>Belle amélioration ici — on voit que tu t'es beaucoup entraîné.</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4539,7 +4459,6 @@
           <t>Bien joué — tes scores augmentent petit à petit.</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4572,7 +4491,6 @@
           <t>Des progrès constants ici. Continue et ça continuera à payer.</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4605,7 +4523,6 @@
           <t>Tu t'améliores un peu à chaque fois que tu fais le quiz sur cette liste.</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4638,7 +4555,6 @@
           <t>Tendance clairement à la hausse — l'entraînement porte ses fruits.</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4708,7 +4624,6 @@
           <t>Tu es régulier sur cette liste — quelques répétitions de plus sur les mots difficiles pourraient te faire progresser.</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4741,7 +4656,6 @@
           <t>Pas beaucoup de changement dernièrement. Ça vaut le coup de voir quels mots précis te posent problème.</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4774,7 +4688,6 @@
           <t>Ça reste stable pour l'instant — essaie de moins t'appuyer sur la liste de mots visible pour vraiment tester ta mémoire.</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4807,7 +4720,6 @@
           <t>Tes scores sont stables. Une petite révision de tes mots les plus faibles pourrait relancer ta progression.</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4877,7 +4789,6 @@
           <t>Une petite baisse dernièrement. Rien de grave, revois juste cette liste quand tu as l'occasion.</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4910,7 +4821,6 @@
           <t>Les scores ont légèrement chuté — ça pourrait valoir le coup de ralentir lors de ta prochaine tentative.</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4943,7 +4853,6 @@
           <t>Une petite baisse récemment. Ça arrive — une courte session de révision devrait aider.</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4976,7 +4885,6 @@
           <t>Tes scores récents sont un peu plus bas qu'avant — un petit rappel serait peut-être utile.</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5046,7 +4954,6 @@
           <t>Une baisse plus importante que d'habitude — cette liste aurait peut-être besoin d'une vraie révision avant ta prochaine tentative.</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5079,7 +4986,6 @@
           <t>Les scores ont pas mal chuté. Ça vaut le coup de revoir la liste depuis le début.</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5112,7 +5018,6 @@
           <t>C'est une chute assez marquée — ralentir et réviser avant de refaire le quiz pourrait aider.</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5145,7 +5050,6 @@
           <t>Une baisse importante ici. Pas de souci, revois juste la liste avant de t'y remettre.</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5168,8 +5072,6 @@
           <t>Various FastAPI HTTPException / Pydantic validation messages surfaced via e.message</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>Decided: stays English-only — these are dev-facing/edge-case errors (malformed requests, validation failures), not normal user-facing copy</t>
@@ -5207,7 +5109,6 @@
           <t>Listes types</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5240,7 +5141,6 @@
           <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5310,7 +5210,6 @@
           <t>Ajouter</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5343,7 +5242,6 @@
           <t>Ajout en cours…</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5413,7 +5311,6 @@
           <t>Une erreur s'est produite lors de l'ajout de cette liste type.</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5446,7 +5343,6 @@
           <t>Passer</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5479,7 +5375,6 @@
           <t>Retour</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5512,7 +5407,6 @@
           <t>Suivant</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5545,7 +5439,6 @@
           <t>Commencer</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5578,7 +5471,6 @@
           <t>Crée ta liste</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5611,7 +5503,6 @@
           <t>Tape des mots, colle une liste, importe un fichier ou prends une photo — l'IA la lit pour toi. Ou commence directement avec quelques listes types déjà prêtes dans Mes listes.</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5644,7 +5535,6 @@
           <t>Entraîne-toi avec des quiz adaptatifs</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5677,7 +5567,6 @@
           <t>L'IA génère de vraies phrases pour te tester — et plus tu t'entraînes, plus elle cible ce qui te pose vraiment des difficultés.</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5710,7 +5599,6 @@
           <t>Suis ta progression</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5743,7 +5631,6 @@
           <t>Regarde tes scores s'améliorer au fil du temps, liste par liste.</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5813,7 +5700,6 @@
           <t>Trier par</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5846,7 +5732,6 @@
           <t>Dernier import</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5879,7 +5764,6 @@
           <t>Nom</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6060,7 +5944,6 @@
           <t>Inscris-toi pour enregistrer tes listes et suivre ta progression au fil du temps</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6463,7 +6346,6 @@
           <t>Supprimer les listes</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6496,7 +6378,6 @@
           <t>Supprimer {count} liste(s) ? Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6529,7 +6410,6 @@
           <t>{count} en cours</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6562,7 +6442,6 @@
           <t>Supprimer les quiz</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6595,7 +6474,6 @@
           <t>Supprimer {count} quiz ? Cette action est irréversible.</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6961,7 +6839,6 @@
           <t>Introductif — mots et phrases de base pour les besoins quotidiens.</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6994,7 +6871,6 @@
           <t>Intermédiaire élémentaire — phrases simples sur des sujets familiers comme la famille et les courses.</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7027,7 +6903,6 @@
           <t>Niveau seuil — à l'aise dans les situations quotidiennes, les voyages et les sujets courants.</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7060,7 +6935,6 @@
           <t>Avancé — capable de discuter de sujets généraux et parfois abstraits avec un vocabulaire varié.</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7093,7 +6967,6 @@
           <t>Autonome — usage fluide et spontané à des fins sociales, académiques ou professionnelles.</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7126,7 +6999,6 @@
           <t>Maîtrise — fluidité quasi native avec une expression précise et nuancée.</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7149,8 +7021,6 @@
           <t>LangReps</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>Animated splash shown on every app launch (not a navigable screen) — proper name, may stay untranslated</t>
@@ -7215,8 +7085,6 @@
           <t>© 2026 MarApps Development</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>Pinned bottom-right corner</t>
@@ -7328,7 +7196,6 @@
           <t>Aucune réponse enregistrée pour ce quiz.</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7361,7 +7228,6 @@
           <t>Ta réponse :</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7468,7 +7334,6 @@
           <t>Une erreur s'est produite lors du chargement des résultats.</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7538,7 +7403,6 @@
           <t>Vocabulaire — paires de mots simples (noms, adjectifs, etc.), testées telles quelles.</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7571,7 +7435,6 @@
           <t>Verbe — les infinitifs sont conjugués en contexte lors de la génération du quiz, donc tu es testé sur de vraies formes verbales (ex. « habla ») plutôt que de simplement retenir l'infinitif (« hablar »).</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7752,7 +7615,6 @@
           <t>Traduire</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7785,7 +7647,6 @@
           <t>Traduction en cours…</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7818,7 +7679,6 @@
           <t>Une erreur s'est produite lors de la traduction de ces mots.</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7999,7 +7859,6 @@
           <t>Une erreur s'est produite lors du renommage.</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8328,7 +8187,6 @@
           <t>Tu as ajouté des mots qui n'ont pas encore été enregistrés. Si tu quittes maintenant, tu les perdras.</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8842,7 +8700,6 @@
           <t>Mot de passe oublié ?</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8875,7 +8732,6 @@
           <t>Mot de passe oublié</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8945,7 +8801,6 @@
           <t>Entre ton e-mail et nous t'enverrons un lien pour réinitialiser ton mot de passe.</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8978,7 +8833,6 @@
           <t>Envoi en cours…</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9011,7 +8865,6 @@
           <t>Envoyer le lien de réinitialisation</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9044,7 +8897,6 @@
           <t>Réinitialiser le mot de passe</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9077,7 +8929,6 @@
           <t>Ce lien semble invalide ou expiré. Demande un nouveau lien depuis l'écran de connexion.</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9110,7 +8961,6 @@
           <t>Définis un nouveau mot de passe</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9143,7 +8993,6 @@
           <t>Nouveau mot de passe</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9176,7 +9025,6 @@
           <t>Enregistrer le nouveau mot de passe</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9246,7 +9094,6 @@
           <t>Supprimer les mots</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9464,7 +9311,6 @@
           <t>Qu'apprends-tu ?</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9571,7 +9417,6 @@
           <t>Tes listes de départ sont prêtes — jette un œil dans Mes listes !</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9604,7 +9449,6 @@
           <t>Ajouter une langue</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9637,7 +9481,6 @@
           <t>Tu n'as encore ajouté aucune langue — ajoutes-en une ci-dessous pour commencer.</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9823,6 +9666,37 @@
           <t>Screen title used instead of Generate Quiz when the tailored feedback card is showing</t>
         </is>
       </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>generate-quiz.tsx</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>generating_progress</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Writing questions… {done} of {total}</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Escribiendo preguntas… {done} de {total}</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Rédaction des questions… {done} sur {total}</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G272"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9696,7 +9696,41 @@
           <t>Rédaction des questions… {done} sur {total}</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>settings.tsx</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>account_section_title</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Compte</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Heading above Delete Account, moved here from Home</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G273"/>
+  <dimension ref="A1:G276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -869,17 +869,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>My Quizzes</t>
+          <t>Saved Quizzes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mis cuestionarios</t>
+          <t>Cuestionarios guardados</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mes quiz</t>
+          <t>Quiz enregistrés</t>
         </is>
       </c>
     </row>
@@ -2729,17 +2729,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>My Quizzes</t>
+          <t>Saved Quizzes</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mis cuestionarios</t>
+          <t>Cuestionarios guardados</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mes quiz</t>
+          <t>Quiz enregistrés</t>
         </is>
       </c>
     </row>
@@ -9729,6 +9729,101 @@
       <c r="G273" t="inlineStr">
         <is>
           <t>Heading above Delete Account, moved here from Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>no_quizzes_yet_title</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>No quizzes yet</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Aún no hay cuestionarios</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Aucun quiz pour l'instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>no_quizzes_yet_hint</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Build a list, then generate a quiz from it — it'll show up here.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Crea una lista y genera un cuestionario a partir de ella; aparecerá aquí.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Crée une liste, puis génère un quiz à partir de celle-ci — il apparaîtra ici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>browse_lists_button</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Browse Your Lists</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Ver tus listas</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Voir tes listes</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Links to My Lists, which also has ready-made Sample Lists</t>
         </is>
       </c>
     </row>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -2527,17 +2527,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Quiz History</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Historial de cuestionarios</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Progrès</t>
+          <t>Historique des quiz</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9827,6 +9827,41 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>generate-quiz.tsx</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>select_tenses_placeholder</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Select tenses</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Selecciona los tiempos verbales</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Sélectionne les temps</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Multi-select tense field's collapsed placeholder when nothing's picked (shouldn't normally happen — Generate is disabled with none selected)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G277"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9862,6 +9862,41 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>quiz.tsx</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>not_sure_which_tense</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Not sure which tense?</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>¿No sabes qué tiempo verbal es?</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Pas sûr du temps verbal ?</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Reveals just the tense label (e.g. "Preterite"), never the answer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9897,6 +9897,41 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>onboarding.tsx</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>dont_show_again</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Don't show this again</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>No volver a mostrar</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Ne plus afficher</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Checkbox on the intro screens — the only thing that permanently turns the intro off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/localization/ui_strings.xlsx
+++ b/localization/ui_strings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G279"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5128,17 +5128,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Add a ready-made 50-word list for any language pair — add as many as you want, whenever you want.</t>
+          <t>Add a ready-made list for any language pair — add as many as you want, whenever you want.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Añade una lista de 50 palabras ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
+          <t>Añade una lista ya preparada para cualquier par de idiomas — añade tantas como quieras, cuando quieras.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ajoute une liste de 50 mots prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
+          <t>Ajoute une liste prête à l'emploi pour n'importe quelle paire de langues — ajoutes-en autant que tu veux, quand tu veux.</t>
         </is>
       </c>
     </row>
@@ -9929,6 +9929,251 @@
       <c r="G279" t="inlineStr">
         <is>
           <t>Checkbox on the intro screens — the only thing that permanently turns the intro off</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>sample_category_subject_pronouns</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Subject Pronouns</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Pronombres de sujeto</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Pronoms sujets</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Grammar sample-list category label</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>sample_category_conjunctions</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Conjunctions</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Conjunciones</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Conjonctions</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Grammar sample-list category label</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>sample_category_prepositions</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Prepositions</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Preposiciones</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Prépositions</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Grammar sample-list category label</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>sample_group_everyday</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Everyday words</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Palabras cotidianas</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Mots du quotidien</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Section header on the Sample Lists tab, above the 50-word lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>my-lists.tsx</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>sample_group_grammar</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Grammar words</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Palabras gramaticales</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Mots grammaticaux</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Section header on the Sample Lists tab, above the grammar-word lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>pairs-review.tsx</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>list_type_info_grammar</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Grammar — function words (pronouns, prepositions, conjunctions, etc.), tested in context: each question gives you the sentence the word depends on.</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Gramática — palabras funcionales (pronombres, preposiciones, conjunciones, etc.), evaluadas en contexto: cada pregunta te da la frase de la que depende la palabra.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Grammaire — mots outils (pronoms, prépositions, conjonctions, etc.), testés en contexte : chaque question te donne la phrase dont dépend le mot.</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Third line of the list-type info alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>my-quizzes.tsx</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>quiz_type_badge_grammar</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Gramática</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Grammaire</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Small badge next to the quiz row title</t>
         </is>
       </c>
     </row>
